--- a/Results/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Ammonia/ammonia ionising radiation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02045048136733395</v>
+        <v>0.0204504813673337</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2792562633614043</v>
+        <v>0.2792562633614045</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03772069616208697</v>
+        <v>0.03772069616208687</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2888788523773538</v>
+        <v>0.2888788523773536</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2593524352641874</v>
+        <v>0.2593524352641873</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06368369368207956</v>
+        <v>0.06368369368207943</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05438155015627641</v>
+        <v>0.0543815501562765</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08906029851959911</v>
+        <v>0.08906029851959898</v>
       </c>
       <c r="J2" t="n">
         <v>0.3694541633057867</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2755936800224032</v>
+        <v>0.2755936800224033</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02801312790385069</v>
+        <v>0.0280131279038507</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02938604579229052</v>
+        <v>0.02938604579229082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2984983999705684</v>
+        <v>0.2984983999705683</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04925037032047398</v>
+        <v>0.04925037032047403</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3081214902438656</v>
+        <v>0.3081214902438657</v>
       </c>
       <c r="F3" t="n">
         <v>0.2785950731306989</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07911319568719928</v>
+        <v>0.07911319568719917</v>
       </c>
       <c r="H3" t="n">
         <v>0.06841613004813073</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1083259672318311</v>
+        <v>0.1083259672318312</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3976238490446665</v>
+        <v>0.3976238490446661</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2959887432644341</v>
+        <v>0.2959887432644338</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03808675392722098</v>
+        <v>0.03808675392722099</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03762050595615875</v>
+        <v>0.01045831254482059</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08323018335587246</v>
+        <v>0.05209750074859888</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04788691685056173</v>
+        <v>0.02072472343922376</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08371247480243157</v>
+        <v>0.05218238499887263</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0837124748024316</v>
+        <v>0.05218238499887268</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06391657392762538</v>
+        <v>0.03626347823342767</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05779365086549815</v>
+        <v>0.03063145745416019</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08237209728891834</v>
+        <v>0.05194933703032473</v>
       </c>
       <c r="J4" t="n">
-        <v>0.113741184297868</v>
+        <v>0.08657899088653009</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0829724515519389</v>
+        <v>0.05581025814060087</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04212629347142061</v>
+        <v>0.01496410006008264</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2007119889387655</v>
+        <v>0.03916241339422008</v>
       </c>
       <c r="C5" t="n">
-        <v>4.370453810029037</v>
+        <v>0.8066488549544567</v>
       </c>
       <c r="D5" t="n">
-        <v>1.274627127815292</v>
+        <v>0.2366309993991049</v>
       </c>
       <c r="E5" t="n">
-        <v>4.370453811189395</v>
+        <v>0.8066488561148208</v>
       </c>
       <c r="F5" t="n">
-        <v>4.370453811189395</v>
+        <v>0.8066488561148208</v>
       </c>
       <c r="G5" t="n">
-        <v>2.953463047753564</v>
+        <v>0.5448236548711061</v>
       </c>
       <c r="H5" t="n">
-        <v>2.599024467122383</v>
+        <v>0.4778880786918653</v>
       </c>
       <c r="I5" t="n">
-        <v>4.370457280209482</v>
+        <v>0.8066523251349041</v>
       </c>
       <c r="J5" t="n">
-        <v>8.606867206851748</v>
+        <v>1.581369162756336</v>
       </c>
       <c r="K5" t="n">
-        <v>4.936770348315345</v>
+        <v>0.910078683342016</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7797519151528157</v>
+        <v>0.1455880312207565</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.91701127240579</v>
+        <v>2.041816786034997</v>
       </c>
       <c r="C6" t="n">
-        <v>11.62516006849347</v>
+        <v>2.083477149525573</v>
       </c>
       <c r="D6" t="n">
-        <v>11.58418865121214</v>
+        <v>2.051113842043242</v>
       </c>
       <c r="E6" t="n">
-        <v>7.192973867997556</v>
+        <v>1.303412383421295</v>
       </c>
       <c r="F6" t="n">
-        <v>11.62339828124782</v>
+        <v>2.083167075928157</v>
       </c>
       <c r="G6" t="n">
-        <v>43.94330734037727</v>
+        <v>7.759036211281905</v>
       </c>
       <c r="H6" t="n">
-        <v>43.94054144552665</v>
+        <v>7.753995027464672</v>
       </c>
       <c r="I6" t="n">
-        <v>43.96176286373854</v>
+        <v>2.083307810520501</v>
       </c>
       <c r="J6" t="n">
-        <v>12.24294859253733</v>
+        <v>2.221319483169363</v>
       </c>
       <c r="K6" t="n">
-        <v>11.62654092883265</v>
+        <v>2.087478299133202</v>
       </c>
       <c r="L6" t="n">
-        <v>11.5816210817897</v>
+        <v>2.04591517179918</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0585635835721368</v>
+        <v>0.01414429418526006</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1033117047244496</v>
+        <v>0.05563184849031712</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06882910565074088</v>
+        <v>0.02441054864808326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.103386198484328</v>
+        <v>0.05564496034812405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.103386198484328</v>
+        <v>0.05564496034812405</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08485965154360353</v>
+        <v>0.03994945987386699</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07873672848147628</v>
+        <v>0.03431743909459951</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1033151749048965</v>
+        <v>0.05563531867076399</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1346842619138461</v>
+        <v>0.09026497252696944</v>
       </c>
       <c r="K7" t="n">
-        <v>0.103915529167917</v>
+        <v>0.05949623978104011</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06306937108739874</v>
+        <v>0.01865008170052192</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07551960087837735</v>
+        <v>0.01712855321498783</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1496813893783664</v>
+        <v>0.06379291294518488</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1212046371301377</v>
+        <v>0.0336286421385079</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1416499542643875</v>
+        <v>0.06237938132892344</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1212425876782244</v>
+        <v>0.05878768482922064</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1311513496852866</v>
+        <v>0.04809679870265599</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1250284266231676</v>
+        <v>0.04246477792338996</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1496068730465794</v>
+        <v>0.063782657499553</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1809817253083731</v>
+        <v>0.09841332604025339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1203266211458336</v>
+        <v>0.06238459195350262</v>
       </c>
       <c r="L8" t="n">
-        <v>0.140004640825875</v>
+        <v>0.03219068910112254</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1774342186620736</v>
+        <v>0.03506552584772512</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2631357631602321</v>
+        <v>0.08376088262259473</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2286540939305962</v>
+        <v>0.05253974643291686</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3103951788936905</v>
+        <v>0.09207854070275275</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2631357605575043</v>
+        <v>0.08376088312065404</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2446837099793858</v>
+        <v>0.06807849400614457</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2385607869172589</v>
+        <v>0.06244647322687707</v>
       </c>
       <c r="I9" t="n">
-        <v>0.263139233340679</v>
+        <v>0.08376435280304158</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2945083203496289</v>
+        <v>0.118394006659247</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2121719068174208</v>
+        <v>0.08344904789219816</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2228934295231812</v>
+        <v>0.04677911583279956</v>
       </c>
     </row>
   </sheetData>
@@ -911,34 +911,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01711413321033776</v>
+        <v>0.01711413321033775</v>
       </c>
       <c r="C2" t="n">
-        <v>0.223367665904061</v>
+        <v>0.2233676659040609</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0722477222465612</v>
+        <v>0.07224772224656122</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2328500307302169</v>
+        <v>0.2328500307302167</v>
       </c>
       <c r="F2" t="n">
         <v>0.2037343120374213</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06223669115787814</v>
+        <v>0.06223669115787813</v>
       </c>
       <c r="H2" t="n">
-        <v>0.106904471316777</v>
+        <v>0.1069044713167771</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03525257268746401</v>
+        <v>0.03525257268746397</v>
       </c>
       <c r="J2" t="n">
         <v>0.305559724367489</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2049961477651171</v>
+        <v>0.204996147765117</v>
       </c>
       <c r="L2" t="n">
         <v>0.05556651812838231</v>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02553542108023012</v>
+        <v>0.0255354210802301</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2345093111591191</v>
+        <v>0.234509311159119</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08895046936044917</v>
+        <v>0.08895046936044915</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2439956436476249</v>
+        <v>0.243995643647625</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2148799249548294</v>
+        <v>0.2148799249548293</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07743570982962113</v>
+        <v>0.07743570982962111</v>
       </c>
       <c r="H3" t="n">
-        <v>0.128813046960766</v>
+        <v>0.1288130469607661</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04638307401961906</v>
+        <v>0.04638307401961898</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3244867978351559</v>
+        <v>0.3244867978351554</v>
       </c>
       <c r="K3" t="n">
         <v>0.2152917444085534</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06976433264200327</v>
+        <v>0.06976433264200325</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02115234467892419</v>
+        <v>0.005866446728956277</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03310593341163164</v>
+        <v>0.01685443331979749</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05392692715261655</v>
+        <v>0.03864102920264863</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0335528230695683</v>
+        <v>0.0169330922028949</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03355282306956831</v>
+        <v>0.01693309220289492</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0484644762964121</v>
+        <v>0.03277590361771764</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07451893267228352</v>
+        <v>0.05923303472231566</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03520343428769304</v>
+        <v>0.01722058440244156</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0627298887300918</v>
+        <v>0.04744399078012391</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02857008177933019</v>
+        <v>0.01328418382936232</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04401400357679515</v>
+        <v>0.02872810562682727</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06424413607980982</v>
+        <v>0.01345060197441662</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9831722721718803</v>
+        <v>0.1840661080355475</v>
       </c>
       <c r="D5" t="n">
-        <v>2.804793978629631</v>
+        <v>0.5227936276391723</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9831722798220341</v>
+        <v>0.1840661156857015</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9831722798220346</v>
+        <v>0.1840661156857015</v>
       </c>
       <c r="G5" t="n">
-        <v>2.417749951922402</v>
+        <v>0.4497701450683661</v>
       </c>
       <c r="H5" t="n">
-        <v>5.209705964818637</v>
+        <v>0.9630259474827794</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9831686203884595</v>
+        <v>0.1840624562521266</v>
       </c>
       <c r="J5" t="n">
-        <v>4.036685994223867</v>
+        <v>0.7468602615571674</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6679654382241613</v>
+        <v>0.1258177659538777</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3365732899141295</v>
+        <v>0.4493366841190557</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.27001484353406</v>
+        <v>6.737666210050508</v>
       </c>
       <c r="C6" t="n">
-        <v>10.08660531139799</v>
+        <v>1.786270314257632</v>
       </c>
       <c r="D6" t="n">
-        <v>10.10965934125519</v>
+        <v>6.770618213909938</v>
       </c>
       <c r="E6" t="n">
-        <v>6.222773357332859</v>
+        <v>1.106235900330734</v>
       </c>
       <c r="F6" t="n">
-        <v>10.08862594428289</v>
+        <v>1.786625951947174</v>
       </c>
       <c r="G6" t="n">
-        <v>38.29732697515156</v>
+        <v>1.802240400004849</v>
       </c>
       <c r="H6" t="n">
-        <v>38.32753338917225</v>
+        <v>6.791763542585402</v>
       </c>
       <c r="I6" t="n">
-        <v>10.08897903641927</v>
+        <v>1.786685080789572</v>
       </c>
       <c r="J6" t="n">
-        <v>38.3142669509781</v>
+        <v>6.779714477256269</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07975499752992</v>
+        <v>1.78229271941591</v>
       </c>
       <c r="L6" t="n">
-        <v>10.09811115250879</v>
+        <v>1.798249194250525</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03581481826765769</v>
+        <v>0.008447042066590129</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04986955965984755</v>
+        <v>0.01980483152349646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06858906432383492</v>
+        <v>0.04122156533080017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04964349186611022</v>
+        <v>0.01976504989574101</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04964349186611024</v>
+        <v>0.01976504989574101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06312694988514564</v>
+        <v>0.03535649895535149</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08918140626101695</v>
+        <v>0.06181363005994953</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04986590787642655</v>
+        <v>0.01980117974007543</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07739236231882529</v>
+        <v>0.05002458611775772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0432325553680637</v>
+        <v>0.01586477916699617</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05867647716552863</v>
+        <v>0.03130870096446112</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04975872602424703</v>
+        <v>0.01090116981845191</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08543892950107591</v>
+        <v>0.02606504058163105</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1088984495639998</v>
+        <v>0.04831601709462713</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0794891958568251</v>
+        <v>0.02501789376964373</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06437101252157221</v>
+        <v>0.02235709351705704</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09890793786938618</v>
+        <v>0.04165395280645441</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1249623942453306</v>
+        <v>0.06811108391106523</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08564689586066711</v>
+        <v>0.02609863359117835</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1131776418865429</v>
+        <v>0.05632279528754851</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05677082815069643</v>
+        <v>0.01824751516382841</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1172681214080565</v>
+        <v>0.04162083029526861</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09640901364712963</v>
+        <v>0.01911162039559005</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1328697945709844</v>
+        <v>0.03441287278870132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1515896368402114</v>
+        <v>0.05582966601452691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.158725808714347</v>
+        <v>0.03896353755700166</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1328697309289481</v>
+        <v>0.0344128678914297</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1461271847962825</v>
+        <v>0.04996454022055637</v>
       </c>
       <c r="H9" t="n">
-        <v>0.172181641172154</v>
+        <v>0.07642167132515446</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1328661427875635</v>
+        <v>0.0344092210052803</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1603925972299622</v>
+        <v>0.06463262738296266</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1132506434788014</v>
+        <v>0.0281879626077115</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1416767120766655</v>
+        <v>0.04591674222966603</v>
       </c>
     </row>
   </sheetData>
@@ -1307,22 +1307,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.156600183197955</v>
+        <v>0.1566001831979551</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1715253167236705</v>
+        <v>0.1715253167236707</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1307801959985861</v>
+        <v>0.1307801959985866</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2320939308811286</v>
+        <v>0.2320939308811285</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2320939308811286</v>
+        <v>0.2320939308811285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1385670302167369</v>
+        <v>0.1385670302167366</v>
       </c>
       <c r="H2" t="n">
         <v>0.1473607138615694</v>
@@ -1331,10 +1331,10 @@
         <v>0.152740271942168</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1879748465577753</v>
+        <v>0.1879748465577754</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1821616226897018</v>
+        <v>0.1821616226897013</v>
       </c>
       <c r="L2" t="n">
         <v>0.1184182088510317</v>
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1762073619980794</v>
+        <v>0.1762073619980795</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1850011073997383</v>
+        <v>0.1850011073997386</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1465090281245717</v>
+        <v>0.1465090281245708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2511224077168732</v>
+        <v>0.2511224077168733</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2511224077168732</v>
+        <v>0.2511224077168733</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1554655005132934</v>
+        <v>0.1554655005132921</v>
       </c>
       <c r="H3" t="n">
         <v>0.1655817387868919</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1717846700361553</v>
+        <v>0.1717846700361552</v>
       </c>
       <c r="J3" t="n">
-        <v>0.209988659462238</v>
+        <v>0.2099886594622377</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2011943762385069</v>
+        <v>0.2011943762385074</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1322913738472778</v>
+        <v>0.1322913738472779</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05665590737079625</v>
+        <v>0.03705371910639654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03011555500302635</v>
+        <v>0.01239664516810084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04130701906643763</v>
+        <v>0.02170483080203831</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05789031623158419</v>
+        <v>0.03538379879164207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05789031623158418</v>
+        <v>0.03538379879164207</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04637629816427506</v>
+        <v>0.02641127294374252</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05116176940749213</v>
+        <v>0.03155958114309246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05729482617996694</v>
+        <v>0.03528059939226184</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06618036744633375</v>
+        <v>0.04657817918193401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05438257036343815</v>
+        <v>0.03478038209903817</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03396433812708483</v>
+        <v>0.01436214986268504</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.078982973625323</v>
+        <v>0.5689832798848778</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6489753451947505</v>
+        <v>0.1213159676516535</v>
       </c>
       <c r="D5" t="n">
-        <v>1.495652057492219</v>
+        <v>0.2776695561780035</v>
       </c>
       <c r="E5" t="n">
-        <v>2.792720657350958</v>
+        <v>0.5167139362205161</v>
       </c>
       <c r="F5" t="n">
-        <v>2.792720657350958</v>
+        <v>0.5167139362205161</v>
       </c>
       <c r="G5" t="n">
-        <v>2.002573657359743</v>
+        <v>0.370702006296569</v>
       </c>
       <c r="H5" t="n">
-        <v>2.773232189940059</v>
+        <v>0.510643972560855</v>
       </c>
       <c r="I5" t="n">
-        <v>2.792722607410588</v>
+        <v>0.5167158862801451</v>
       </c>
       <c r="J5" t="n">
-        <v>4.112632521406208</v>
+        <v>0.758753754419876</v>
       </c>
       <c r="K5" t="n">
-        <v>2.774978749860267</v>
+        <v>0.5136053070959261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9019588532086916</v>
+        <v>0.1671291836892642</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.43612456678164</v>
+        <v>1.905219390284192</v>
       </c>
       <c r="C6" t="n">
-        <v>10.64351314262725</v>
+        <v>1.88035461046824</v>
       </c>
       <c r="D6" t="n">
-        <v>10.65422353008177</v>
+        <v>1.88957813171646</v>
       </c>
       <c r="E6" t="n">
-        <v>6.593372493828073</v>
+        <v>1.185628655815902</v>
       </c>
       <c r="F6" t="n">
-        <v>10.67192012385338</v>
+        <v>1.903453034810751</v>
       </c>
       <c r="G6" t="n">
-        <v>40.42584495757508</v>
+        <v>7.133197718491179</v>
       </c>
       <c r="H6" t="n">
-        <v>40.4354504486673</v>
+        <v>7.139194350179357</v>
       </c>
       <c r="I6" t="n">
-        <v>40.43676348559079</v>
+        <v>7.142067044939697</v>
       </c>
       <c r="J6" t="n">
-        <v>40.44847440042537</v>
+        <v>7.153861890474687</v>
       </c>
       <c r="K6" t="n">
-        <v>10.66978839543294</v>
+        <v>1.903091797187614</v>
       </c>
       <c r="L6" t="n">
-        <v>10.64779542051406</v>
+        <v>1.882396410240654</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07283077903865529</v>
+        <v>0.03990049650451413</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04852511574521178</v>
+        <v>0.01563672784116875</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05748145864631354</v>
+        <v>0.02455153215267127</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07350924458406181</v>
+        <v>0.03813273016678276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.07350924458406181</v>
+        <v>0.03813273016678276</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06255116983213392</v>
+        <v>0.02925805034186011</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06733664107535124</v>
+        <v>0.03440635854121005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07346969784782581</v>
+        <v>0.03812737679037945</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08235523911419268</v>
+        <v>0.04942495658005164</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07055744203129684</v>
+        <v>0.03762715949715576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05013920979494376</v>
+        <v>0.01720892726080265</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08635156473702196</v>
+        <v>0.04228015477453225</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08539339744735219</v>
+        <v>0.02212554538568726</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09913744135257384</v>
+        <v>0.03188298506924674</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1039581531102783</v>
+        <v>0.04349173803835851</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08775220831497293</v>
+        <v>0.04063949176983994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09937473692714603</v>
+        <v>0.03573899811546449</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1041602081704768</v>
+        <v>0.04088730631483446</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1102932649428375</v>
+        <v>0.04460832456398388</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1191833858297262</v>
+        <v>0.05590671036686342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08364536660528472</v>
+        <v>0.03993063420969598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1113044805653062</v>
+        <v>0.02797401485805462</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1427950669638496</v>
+        <v>0.05221421111262518</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1442417278469413</v>
+        <v>0.03248285147979052</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1531985342412426</v>
+        <v>0.04139773736609559</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1989020205824024</v>
+        <v>0.06020185862290674</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1691843568823872</v>
+        <v>0.05497154984004508</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1582677819338636</v>
+        <v>0.04610417398048186</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1630532531770807</v>
+        <v>0.05125248217983183</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1691863099495553</v>
+        <v>0.0549735004290012</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1780718512159215</v>
+        <v>0.06627108021867342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1338472730816039</v>
+        <v>0.0518471898681243</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1458558218966724</v>
+        <v>0.03405505089942439</v>
       </c>
     </row>
   </sheetData>
@@ -1703,13 +1703,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1319203604330616</v>
+        <v>0.1319203604330617</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1669019833755744</v>
+        <v>0.1669019833755745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1300741534405138</v>
+        <v>0.1300741534405139</v>
       </c>
       <c r="E2" t="n">
         <v>0.2066471411232798</v>
@@ -1727,7 +1727,7 @@
         <v>0.1260923106839598</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1675901010912766</v>
+        <v>0.1675901010912765</v>
       </c>
       <c r="K2" t="n">
         <v>0.1573346206694217</v>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1480611763161608</v>
+        <v>0.1480611763161609</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1796543047533086</v>
+        <v>0.1796543047533085</v>
       </c>
       <c r="D3" t="n">
         <v>0.1459376558341046</v>
@@ -1764,16 +1764,16 @@
         <v>0.155357182848282</v>
       </c>
       <c r="I3" t="n">
-        <v>0.141365124766977</v>
+        <v>0.1413651247669768</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1865887115517578</v>
+        <v>0.1865887115517576</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1727443635445496</v>
+        <v>0.1727443635445497</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1257560077425999</v>
+        <v>0.1257560077425998</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03685816991444369</v>
+        <v>0.02229566482425931</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02165460494279904</v>
+        <v>0.008576949365356301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03576067808780008</v>
+        <v>0.02119817299761604</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03607423442239599</v>
+        <v>0.01930507073282422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.036074234422396</v>
+        <v>0.01930507073282422</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03339313734927222</v>
+        <v>0.0184886482394699</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04062566504687012</v>
+        <v>0.02606315995668542</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03616131396263352</v>
+        <v>0.01932049937010218</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04816813610635391</v>
+        <v>0.03360563101616954</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03396488602713777</v>
+        <v>0.01940238093695289</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02533372671321434</v>
+        <v>0.01077122162303006</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.683428162400327</v>
+        <v>0.3120919819314835</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4106473158572437</v>
+        <v>0.07703966611532602</v>
       </c>
       <c r="D5" t="n">
-        <v>1.530744856775921</v>
+        <v>0.2843153870209972</v>
       </c>
       <c r="E5" t="n">
-        <v>1.32943801323763</v>
+        <v>0.246937094570857</v>
       </c>
       <c r="F5" t="n">
-        <v>1.32943801323763</v>
+        <v>0.246937094570857</v>
       </c>
       <c r="G5" t="n">
-        <v>1.313178823943636</v>
+        <v>0.2437309278595788</v>
       </c>
       <c r="H5" t="n">
-        <v>2.237701194455476</v>
+        <v>0.4127484510373057</v>
       </c>
       <c r="I5" t="n">
-        <v>1.329438137798649</v>
+        <v>0.2469372191318753</v>
       </c>
       <c r="J5" t="n">
-        <v>2.811019810880855</v>
+        <v>0.5198675231416201</v>
       </c>
       <c r="K5" t="n">
-        <v>1.371355566370774</v>
+        <v>0.2547831394019975</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6589160130592761</v>
+        <v>0.1222817034157056</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.27722022332781</v>
+        <v>6.752599349756163</v>
       </c>
       <c r="C6" t="n">
-        <v>10.07201544105215</v>
+        <v>1.777440446935832</v>
       </c>
       <c r="D6" t="n">
-        <v>10.08672679452795</v>
+        <v>6.751584657428262</v>
       </c>
       <c r="E6" t="n">
-        <v>6.222896416867006</v>
+        <v>1.108185768942863</v>
       </c>
       <c r="F6" t="n">
-        <v>10.08674846437071</v>
+        <v>1.788223725618657</v>
       </c>
       <c r="G6" t="n">
-        <v>10.084087079975</v>
+        <v>1.787410772556509</v>
       </c>
       <c r="H6" t="n">
-        <v>38.28528822408642</v>
+        <v>6.757123733874687</v>
       </c>
       <c r="I6" t="n">
-        <v>10.08685525658836</v>
+        <v>1.78824262368714</v>
       </c>
       <c r="J6" t="n">
-        <v>10.61050363923523</v>
+        <v>1.892576669493823</v>
       </c>
       <c r="K6" t="n">
-        <v>10.08456925020145</v>
+        <v>1.788308739446629</v>
       </c>
       <c r="L6" t="n">
-        <v>10.07567799908454</v>
+        <v>1.779631803975628</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04849396294297344</v>
+        <v>0.02434356438618387</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03505032813709465</v>
+        <v>0.01093459663477718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04739608942019129</v>
+        <v>0.02324600538102055</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04778464690422799</v>
+        <v>0.02136610331845873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04778464690422799</v>
+        <v>0.02136610331845873</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04502893037780176</v>
+        <v>0.02053654780139446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05226145807539975</v>
+        <v>0.02811105951861005</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04779710699116362</v>
+        <v>0.02136839893202674</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05980392913488401</v>
+        <v>0.0356535305780941</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0456006790556678</v>
+        <v>0.02145028049887742</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03696951974174463</v>
+        <v>0.01281912118495464</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05876761591853365</v>
+        <v>0.02615172730008475</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06262698465290613</v>
+        <v>0.01578808815533924</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07857063306201076</v>
+        <v>0.02873272503225022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07064003636531888</v>
+        <v>0.02538865184181411</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05861223531607974</v>
+        <v>0.02327175886861865</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07261355051453007</v>
+        <v>0.02539144091915211</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07984607821225638</v>
+        <v>0.03296595263638971</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07538172712789311</v>
+        <v>0.02622329204978436</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08739195133711301</v>
+        <v>0.04050902245937647</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05555277193187198</v>
+        <v>0.02320184883559827</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08263689256511085</v>
+        <v>0.02085657875831528</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.09220203033841158</v>
+        <v>0.03203618420609763</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09553949635462049</v>
+        <v>0.02158069018337476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1078856555899872</v>
+        <v>0.0338921689692171</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1276511831490037</v>
+        <v>0.0354226136213726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1082861372670755</v>
+        <v>0.03201436556462117</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1055180985953272</v>
+        <v>0.03118264134999202</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1127506262929256</v>
+        <v>0.03875715306720762</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1082862752086895</v>
+        <v>0.03201449248062429</v>
       </c>
       <c r="J9" t="n">
-        <v>0.12029309735241</v>
+        <v>0.0462996241266916</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0963668183896729</v>
+        <v>0.03038512097324795</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0974586879592703</v>
+        <v>0.02346521473355219</v>
       </c>
     </row>
   </sheetData>
@@ -2105,28 +2105,28 @@
         <v>0.1636536742041841</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1320489369022644</v>
+        <v>0.1320489369022645</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1900506355109541</v>
+        <v>0.1900506355109539</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1900506355109541</v>
+        <v>0.1900506355109539</v>
       </c>
       <c r="G2" t="n">
         <v>0.1182121068987683</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1310733038932072</v>
+        <v>0.1310733038932073</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1100597985628032</v>
+        <v>0.110059798562803</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1564703881643145</v>
+        <v>0.1564703881643142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1409159180874043</v>
+        <v>0.1409159180874042</v>
       </c>
       <c r="L2" t="n">
         <v>0.1074276467874091</v>
@@ -2142,25 +2142,25 @@
         <v>0.1302427509679246</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1758767330683788</v>
+        <v>0.1758767330683789</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1481123266525435</v>
+        <v>0.1481123266525436</v>
       </c>
       <c r="E3" t="n">
         <v>0.2028114708714501</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2028114708714501</v>
+        <v>0.2028114708714502</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1321971058578228</v>
+        <v>0.1321971058578229</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1469909492927337</v>
+        <v>0.1469909492927336</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1228203378826263</v>
+        <v>0.1228203378826262</v>
       </c>
       <c r="J3" t="n">
         <v>0.1738255391067983</v>
@@ -2169,7 +2169,7 @@
         <v>0.1538640645666664</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1197932869903033</v>
+        <v>0.1197932869903032</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02326752534326363</v>
+        <v>0.01211863948833552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01600349661343448</v>
+        <v>0.005931852891996006</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03250299701644557</v>
+        <v>0.02135411116151729</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02144406535271982</v>
+        <v>0.008637942881690803</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02144406535271982</v>
+        <v>0.008637942881690803</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02467655541644249</v>
+        <v>0.0131989203239516</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03192029999783053</v>
+        <v>0.0207714141429022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02209368013711851</v>
+        <v>0.008751389548753791</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03761525229451498</v>
+        <v>0.02646636643958718</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02017415562468386</v>
+        <v>0.009025269769755677</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01786971002379854</v>
+        <v>0.006720824168870246</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8302543839757844</v>
+        <v>0.1541483258380569</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2641470180760661</v>
+        <v>0.04960511243277193</v>
       </c>
       <c r="D5" t="n">
-        <v>1.653496792755861</v>
+        <v>0.3066490176657636</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4595497698340302</v>
+        <v>0.08574454645259125</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4595497698340302</v>
+        <v>0.08574454645259125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9245522589337356</v>
+        <v>0.171577043284808</v>
       </c>
       <c r="H5" t="n">
-        <v>1.810286351969491</v>
+        <v>0.333763837593932</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4595486951563975</v>
+        <v>0.08574347177495738</v>
       </c>
       <c r="J5" t="n">
-        <v>2.234680729651144</v>
+        <v>0.4131498883590649</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5226510097884155</v>
+        <v>0.0974611956233734</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3547964657908249</v>
+        <v>0.06601993286254861</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.25899334306285</v>
+        <v>1.780637009698385</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06437898237002</v>
+        <v>1.774445928802274</v>
       </c>
       <c r="D6" t="n">
-        <v>10.08250992830465</v>
+        <v>1.790155321483815</v>
       </c>
       <c r="E6" t="n">
-        <v>6.20597574117628</v>
+        <v>1.097115511928609</v>
       </c>
       <c r="F6" t="n">
-        <v>10.070290329293</v>
+        <v>1.777234875751854</v>
       </c>
       <c r="G6" t="n">
-        <v>10.07307644060366</v>
+        <v>6.742686627778166</v>
       </c>
       <c r="H6" t="n">
-        <v>38.27165824969099</v>
+        <v>6.750965256820642</v>
       </c>
       <c r="I6" t="n">
-        <v>10.07049356532434</v>
+        <v>6.738239097002964</v>
       </c>
       <c r="J6" t="n">
-        <v>10.59758965152335</v>
+        <v>6.756396807921613</v>
       </c>
       <c r="K6" t="n">
-        <v>10.06787534009871</v>
+        <v>1.777420668654951</v>
       </c>
       <c r="L6" t="n">
-        <v>10.06612451082201</v>
+        <v>1.775213659526592</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03222696667798084</v>
+        <v>0.01369550115470133</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02623426869394551</v>
+        <v>0.00773246876840919</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0414620273145592</v>
+        <v>0.02293090048544168</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03096472743823312</v>
+        <v>0.01031357939966153</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03096472743823312</v>
+        <v>0.01031357939966153</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03363599675115957</v>
+        <v>0.01477578199031742</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04087974133254758</v>
+        <v>0.02234827580926802</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03105312147183566</v>
+        <v>0.01032825121511959</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04657469362923194</v>
+        <v>0.0280432281059531</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02913359695940109</v>
+        <v>0.01060213143612155</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02682915135851564</v>
+        <v>0.008297685835236088</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04058851364041349</v>
+        <v>0.01516713341211529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04818646615425135</v>
+        <v>0.01159605550042001</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06633217268424747</v>
+        <v>0.02730804604678853</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04927558279041523</v>
+        <v>0.01353628992418293</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03979602893606014</v>
+        <v>0.01186788845485683</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0556705451640663</v>
+        <v>0.01865386248997513</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06291428974561045</v>
+        <v>0.02622635630895332</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05308766988474254</v>
+        <v>0.01420633171477746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06861192915104707</v>
+        <v>0.03192178153677587</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0372411609026668</v>
+        <v>0.01202906268240429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06314629307877354</v>
+        <v>0.01468950274336678</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.06273058791048804</v>
+        <v>0.01906413846253194</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06881260635853</v>
+        <v>0.0152262561567699</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08404078514930614</v>
+        <v>0.03042476182375048</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08756648600300404</v>
+        <v>0.02027548885308155</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0736325155701599</v>
+        <v>0.01782311007018943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07621433441574402</v>
+        <v>0.02226956937867838</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08345807899713203</v>
+        <v>0.02984206319762909</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07363145913641997</v>
+        <v>0.01782203860348075</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08915303129381658</v>
+        <v>0.03553701549431366</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06443195796795782</v>
+        <v>0.0154199751185161</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06940748902310015</v>
+        <v>0.01579147322359723</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>0.1518247071237616</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1687342331557406</v>
+        <v>0.1687342331557411</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1288246460718285</v>
+        <v>0.1288246460718294</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2275366762364739</v>
+        <v>0.2275366762364747</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2275366762364739</v>
+        <v>0.2275366762364747</v>
       </c>
       <c r="G2" t="n">
-        <v>0.134645121839661</v>
+        <v>0.1346451218396618</v>
       </c>
       <c r="H2" t="n">
-        <v>0.181954042915109</v>
+        <v>0.1819540429151091</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1451154207802508</v>
+        <v>0.1451154207802513</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1870641291073297</v>
+        <v>0.1870641291073303</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1763581673636976</v>
+        <v>0.1763581673636977</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1087628737235981</v>
+        <v>0.1087628737235984</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.171215195425698</v>
+        <v>0.1712151954256983</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1818146756960959</v>
+        <v>0.1818146756960965</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1447603607676816</v>
+        <v>0.1447603607676824</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2459203516806747</v>
+        <v>0.2459203516806756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2459203516806747</v>
+        <v>0.2459203516806756</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1514551136086121</v>
+        <v>0.1514551136086125</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2058711328434673</v>
+        <v>0.2058711328434675</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1635119381056905</v>
+        <v>0.1635119381056908</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2089528965002591</v>
+        <v>0.2089528965002594</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1945868567136894</v>
+        <v>0.1945868567136895</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1216866423491493</v>
+        <v>0.1216866423491495</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05494871582864608</v>
+        <v>0.03601008743637744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02757128779792537</v>
+        <v>0.01062384245425457</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04127615412853131</v>
+        <v>0.02233752573626336</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05417307695070581</v>
+        <v>0.03259030752101775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05417307695070579</v>
+        <v>0.03259030752101775</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04516813798815837</v>
+        <v>0.02587357649177108</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07284875457052178</v>
+        <v>0.05391012617825327</v>
       </c>
       <c r="I4" t="n">
-        <v>0.053839195533297</v>
+        <v>0.03253273460038496</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06483586876843841</v>
+        <v>0.04589724037616997</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05035079721955957</v>
+        <v>0.03141216882729116</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02935757500768865</v>
+        <v>0.0104189466154203</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.995657959189582</v>
+        <v>0.5535749114634243</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4955827335564512</v>
+        <v>0.09299385646158403</v>
       </c>
       <c r="D5" t="n">
-        <v>1.57742659885689</v>
+        <v>0.2927000025434721</v>
       </c>
       <c r="E5" t="n">
-        <v>2.545123192562844</v>
+        <v>0.4709975254932022</v>
       </c>
       <c r="F5" t="n">
-        <v>2.545123192562844</v>
+        <v>0.4709975254932022</v>
       </c>
       <c r="G5" t="n">
-        <v>1.970076596788503</v>
+        <v>0.3646574634048997</v>
       </c>
       <c r="H5" t="n">
-        <v>5.250942972158465</v>
+        <v>0.9652547035355171</v>
       </c>
       <c r="I5" t="n">
-        <v>2.545124636990649</v>
+        <v>0.4709989699210069</v>
       </c>
       <c r="J5" t="n">
-        <v>4.064671198072515</v>
+        <v>0.7498682545191451</v>
       </c>
       <c r="K5" t="n">
-        <v>2.46752978578925</v>
+        <v>0.4568356685103547</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4840027411097525</v>
+        <v>0.09043649541580064</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.43372001790663</v>
+        <v>1.904098493198748</v>
       </c>
       <c r="C6" t="n">
-        <v>10.64048306038437</v>
+        <v>1.878496304308208</v>
       </c>
       <c r="D6" t="n">
-        <v>10.6540816364369</v>
+        <v>1.890191280501387</v>
       </c>
       <c r="E6" t="n">
-        <v>6.589126010930112</v>
+        <v>1.182742017669178</v>
       </c>
       <c r="F6" t="n">
-        <v>10.66793205582456</v>
+        <v>1.900611877680746</v>
       </c>
       <c r="G6" t="n">
-        <v>10.65930686460636</v>
+        <v>1.893961982254143</v>
       </c>
       <c r="H6" t="n">
-        <v>40.45711189484863</v>
+        <v>7.161540400353755</v>
       </c>
       <c r="I6" t="n">
-        <v>40.43261049761131</v>
+        <v>1.900621140362757</v>
       </c>
       <c r="J6" t="n">
-        <v>40.44652807820807</v>
+        <v>7.153075030726552</v>
       </c>
       <c r="K6" t="n">
-        <v>10.66488364390806</v>
+        <v>1.899569939721662</v>
       </c>
       <c r="L6" t="n">
-        <v>10.64265475035657</v>
+        <v>1.878359239355195</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07091781683847939</v>
+        <v>0.03882064919887877</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04590040832119388</v>
+        <v>0.01384976764887031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05724484543187573</v>
+        <v>0.02514801539042274</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06981481317852942</v>
+        <v>0.03534325308219777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06981481317852942</v>
+        <v>0.03534325308219777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06113723899799164</v>
+        <v>0.02868413825427217</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08881785558035493</v>
+        <v>0.05672068794075463</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06980829654313032</v>
+        <v>0.03534329636288652</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08080496977827159</v>
+        <v>0.04870780213867153</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06631989822939287</v>
+        <v>0.03422273058979249</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04532667601752195</v>
+        <v>0.01322950837792159</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08434610051027062</v>
+        <v>0.04118402711230806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08245452609008153</v>
+        <v>0.02028329234133392</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0985794530195554</v>
+        <v>0.03242290628643493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1000383298755353</v>
+        <v>0.04066259199204728</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08397278322708061</v>
+        <v>0.03783505579724084</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09767875714490505</v>
+        <v>0.03511544541328053</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1253593737273991</v>
+        <v>0.06315199509978577</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1063498146900436</v>
+        <v>0.04177460352189444</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1173510302938605</v>
+        <v>0.05513990875456192</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07931884170822452</v>
+        <v>0.03651054462967017</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1060119002301965</v>
+        <v>0.02391010778147848</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1390030276190012</v>
+        <v>0.05080364623132044</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1391613868867973</v>
+        <v>0.03026369978747645</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1505062341098781</v>
+        <v>0.04156201970881093</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1921200881807876</v>
+        <v>0.05686898136595673</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1630677946180814</v>
+        <v>0.05175577772662642</v>
       </c>
       <c r="G9" t="n">
-        <v>0.154398217563595</v>
+        <v>0.04509807039287851</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1820788341459582</v>
+        <v>0.07313462007936074</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1630692751087338</v>
+        <v>0.05175722850149287</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1740659483438752</v>
+        <v>0.06512173427727699</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1278800911897197</v>
+        <v>0.04505732449210189</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1385876545831254</v>
+        <v>0.02964344051652763</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1231021163761725</v>
+        <v>0.1231021163761727</v>
       </c>
       <c r="C2" t="n">
         <v>0.1629107837316668</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1270263742676084</v>
+        <v>0.1270263742676085</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1996617849833865</v>
+        <v>0.1996617849833867</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1996617849833865</v>
+        <v>0.1996617849833867</v>
       </c>
       <c r="G2" t="n">
         <v>0.1201299141470952</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2199854202349798</v>
+        <v>0.2199854202349797</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1146677759952287</v>
+        <v>0.1146677759952288</v>
       </c>
       <c r="J2" t="n">
         <v>0.1603920366016442</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1493674167087272</v>
+        <v>0.1493674167087273</v>
       </c>
       <c r="L2" t="n">
         <v>0.1001244285302181</v>
@@ -2931,28 +2931,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1386713185084596</v>
+        <v>0.1386713185084597</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1751144218665166</v>
+        <v>0.1751144218665164</v>
       </c>
       <c r="D3" t="n">
         <v>0.1431850279911842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2139645541880532</v>
+        <v>0.2139645541880534</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2139645541880532</v>
+        <v>0.2139645541880534</v>
       </c>
       <c r="G3" t="n">
         <v>0.1352526702551838</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2501066601869799</v>
+        <v>0.2501066601869796</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1289728861754243</v>
+        <v>0.1289728861754244</v>
       </c>
       <c r="J3" t="n">
         <v>0.1783353957131663</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03371850538284581</v>
+        <v>0.01976163016818124</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0181894530165933</v>
+        <v>0.0060628408239823</v>
       </c>
       <c r="D4" t="n">
-        <v>0.036051310414392</v>
+        <v>0.02209443519972748</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03099163057185214</v>
+        <v>0.01515179859742495</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03099163057185217</v>
+        <v>0.01515179859742495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03235116687667209</v>
+        <v>0.01806509560610292</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0912887417968468</v>
+        <v>0.07733186658218226</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03137124037451041</v>
+        <v>0.01521801860090017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04311443446114779</v>
+        <v>0.02915755924648326</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02884039547003723</v>
+        <v>0.01488352025537268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02006472605359801</v>
+        <v>0.006107850838933454</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.46123236005674</v>
+        <v>0.2710040672294025</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1982363262118528</v>
+        <v>0.03775109033464191</v>
       </c>
       <c r="D5" t="n">
-        <v>1.630739845537895</v>
+        <v>0.3027596158606508</v>
       </c>
       <c r="E5" t="n">
-        <v>0.968026827821914</v>
+        <v>0.1800699924198093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.968026827821914</v>
+        <v>0.1800699924198093</v>
       </c>
       <c r="G5" t="n">
-        <v>1.291526568728652</v>
+        <v>0.2396799651312075</v>
       </c>
       <c r="H5" t="n">
-        <v>7.593279308250505</v>
+        <v>1.397682199123571</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9680261101988191</v>
+        <v>0.1800692747967145</v>
       </c>
       <c r="J5" t="n">
-        <v>2.399319445085703</v>
+        <v>0.4438496388693531</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9720679669841557</v>
+        <v>0.1808915719423259</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1844526126949934</v>
+        <v>0.03504011873104652</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.08388728708473</v>
+        <v>1.788591326163125</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06807921381946</v>
+        <v>1.774843429140964</v>
       </c>
       <c r="D6" t="n">
-        <v>38.2769690988286</v>
+        <v>1.791035726358124</v>
       </c>
       <c r="E6" t="n">
-        <v>6.216980120780764</v>
+        <v>1.103885766974776</v>
       </c>
       <c r="F6" t="n">
-        <v>10.08133439728368</v>
+        <v>1.784012115953952</v>
       </c>
       <c r="G6" t="n">
-        <v>10.08251994857856</v>
+        <v>6.748320180484805</v>
       </c>
       <c r="H6" t="n">
-        <v>38.34054215042849</v>
+        <v>6.809200430024006</v>
       </c>
       <c r="I6" t="n">
-        <v>10.08154002207639</v>
+        <v>6.745473103479599</v>
       </c>
       <c r="J6" t="n">
-        <v>10.60486734071156</v>
+        <v>1.888026060674082</v>
       </c>
       <c r="K6" t="n">
-        <v>10.0783205298062</v>
+        <v>1.783592014314606</v>
       </c>
       <c r="L6" t="n">
-        <v>10.06980786002845</v>
+        <v>1.774862632834322</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04574482691240535</v>
+        <v>0.02187826274591451</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03238423343761566</v>
+        <v>0.008561122164545054</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04807736704045211</v>
+        <v>0.0242110211544451</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04337583227172215</v>
+        <v>0.01733141808479157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04337583227172215</v>
+        <v>0.01733141808479157</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04437748840623164</v>
+        <v>0.02018172818383619</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1033150633264064</v>
+        <v>0.07944849915991566</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04339756190407001</v>
+        <v>0.01733465117863347</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05514075599070735</v>
+        <v>0.03127419182421653</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04086671699959679</v>
+        <v>0.01700015283310596</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03209104758315759</v>
+        <v>0.008224483416666747</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05661983539259255</v>
+        <v>0.02379226422805625</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06143220627640075</v>
+        <v>0.0136735653564689</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08091515930281958</v>
+        <v>0.0299904725613052</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06747314944154081</v>
+        <v>0.02157254588369866</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05483666857385873</v>
+        <v>0.0193485252630377</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07344307988284242</v>
+        <v>0.02529727225600057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1323806548041788</v>
+        <v>0.08456404323228432</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07246315338068071</v>
+        <v>0.02245019525079783</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08420992239850594</v>
+        <v>0.03639036508426659</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05140382606502681</v>
+        <v>0.01885468401857266</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08015822403460493</v>
+        <v>0.01668430642628105</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08727943034029706</v>
+        <v>0.02918835290961296</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09031546980172826</v>
+        <v>0.01875701970938131</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1060088179589903</v>
+        <v>0.03440695646086008</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1202507319724613</v>
+        <v>0.03086140035880803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1013294317729208</v>
+        <v>0.02753125154173369</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1023087247703443</v>
+        <v>0.03037762572867247</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1612462996905191</v>
+        <v>0.08964439670475183</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1013287982681826</v>
+        <v>0.02753054872346974</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1130719923548199</v>
+        <v>0.04147008936905283</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08929765866929483</v>
+        <v>0.02356230606698796</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0900222839472702</v>
+        <v>0.01842038096150304</v>
       </c>
     </row>
   </sheetData>
@@ -3290,16 +3290,16 @@
         <v>0.104961615597386</v>
       </c>
       <c r="C2" t="n">
-        <v>0.160397725451475</v>
+        <v>0.1603977254514751</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1227852677045758</v>
+        <v>0.1227852677045759</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1864026694935283</v>
+        <v>0.1864026694935282</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1864026694935283</v>
+        <v>0.1864026694935282</v>
       </c>
       <c r="G2" t="n">
         <v>0.1076398314344801</v>
@@ -3308,16 +3308,16 @@
         <v>0.1818304338483859</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09867004028987827</v>
+        <v>0.09867004028987829</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1410052509592181</v>
+        <v>0.141005250959218</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1356465936661825</v>
+        <v>0.1356465936661824</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09472844419184154</v>
+        <v>0.09472844419184152</v>
       </c>
     </row>
     <row r="3">
@@ -3333,16 +3333,16 @@
         <v>0.1722056859901767</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1387100679875248</v>
+        <v>0.1387100679875249</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1987055141128834</v>
+        <v>0.1987055141128833</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1987055141128834</v>
+        <v>0.1987055141128833</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1212896789092431</v>
+        <v>0.1212896789092432</v>
       </c>
       <c r="H3" t="n">
         <v>0.2066239164318762</v>
@@ -3351,10 +3351,10 @@
         <v>0.1109690786510448</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1560873702287943</v>
+        <v>0.1560873702287945</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1479108259116997</v>
+        <v>0.1479108259116998</v>
       </c>
       <c r="L3" t="n">
         <v>0.1064392992593294</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02085917357670119</v>
+        <v>0.009880022434257516</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01271081475975702</v>
+        <v>0.003761230028049847</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0314545795022195</v>
+        <v>0.02047542835977582</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01863745268230136</v>
+        <v>0.006408234082052664</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01863745268230136</v>
+        <v>0.006408234082052663</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0228445484186226</v>
+        <v>0.01154132712958575</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06653744733979572</v>
+        <v>0.0555582961973521</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01974482441444604</v>
+        <v>0.006602150244301115</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02811959739845249</v>
+        <v>0.01714044625600884</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01696756875826725</v>
+        <v>0.005988417615823621</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0147794357420197</v>
+        <v>0.003800284599576052</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6268836058230906</v>
+        <v>0.1165403219316718</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08716543145038762</v>
+        <v>0.01686524249459577</v>
       </c>
       <c r="D5" t="n">
-        <v>1.581385138735705</v>
+        <v>0.2932632053067398</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2693346845629235</v>
+        <v>0.05053094665395864</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2693346845629235</v>
+        <v>0.05053094665395864</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7766760404776413</v>
+        <v>0.1442156690130629</v>
       </c>
       <c r="H5" t="n">
-        <v>5.440425846662396</v>
+        <v>1.001362649353191</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2693334937115259</v>
+        <v>0.05052975580256087</v>
       </c>
       <c r="J5" t="n">
-        <v>1.341600338620018</v>
+        <v>0.2483130554583723</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2510879053721297</v>
+        <v>0.04719359663658841</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05492640280175421</v>
+        <v>0.01086615076380219</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.25622008745717</v>
+        <v>6.739303506813136</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06151335110413</v>
+        <v>1.772350466841374</v>
       </c>
       <c r="D6" t="n">
-        <v>10.0811561115369</v>
+        <v>1.789222888413735</v>
       </c>
       <c r="E6" t="n">
-        <v>6.20296435767573</v>
+        <v>1.094849763463063</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06752619963456</v>
+        <v>1.77501264396228</v>
       </c>
       <c r="G6" t="n">
-        <v>38.25820546229905</v>
+        <v>6.740964811508457</v>
       </c>
       <c r="H6" t="n">
-        <v>38.31282307592803</v>
+        <v>6.786904530354391</v>
       </c>
       <c r="I6" t="n">
-        <v>10.06775526951278</v>
+        <v>1.775051978999078</v>
       </c>
       <c r="J6" t="n">
-        <v>38.26658626674273</v>
+        <v>6.747110543593557</v>
       </c>
       <c r="K6" t="n">
-        <v>10.06394052421102</v>
+        <v>1.774255648194005</v>
       </c>
       <c r="L6" t="n">
-        <v>10.0625754629463</v>
+        <v>1.772212375805203</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0300097530922822</v>
+        <v>0.0114905244202731</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02428468169452599</v>
+        <v>0.005798230597531482</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04060503773409134</v>
+        <v>0.02208590899985871</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02870466565956753</v>
+        <v>0.00818006355645067</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02870466565956753</v>
+        <v>0.00818006355645067</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03199512793420362</v>
+        <v>0.01315182911560124</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07568802685537677</v>
+        <v>0.05716879818336768</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02889540393002706</v>
+        <v>0.008212652230316721</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03727017691403353</v>
+        <v>0.0187509482420244</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02611814827384827</v>
+        <v>0.00759891960183918</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02393001525760073</v>
+        <v>0.005410786585591638</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0390880468313449</v>
+        <v>0.01308830410969039</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04794311447463048</v>
+        <v>0.009962114744267437</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06750485332494151</v>
+        <v>0.02682027651819466</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04853729794158092</v>
+        <v>0.01167060681917116</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03832835655527012</v>
+        <v>0.009873833144916465</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05583409953301689</v>
+        <v>0.01734748809425775</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09952699845581484</v>
+        <v>0.06136445716231014</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05273437552884037</v>
+        <v>0.01240831120897325</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06111204936805173</v>
+        <v>0.02294711777119414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03492225484718735</v>
+        <v>0.009148442350350592</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06318774911014144</v>
+        <v>0.01232014770619969</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05739822039714844</v>
+        <v>0.01631089463980988</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06316159747359122</v>
+        <v>0.01264056773757101</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07948203532001676</v>
+        <v>0.02892826053790558</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08103081916866395</v>
+        <v>0.01738946652414955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06777344524019964</v>
+        <v>0.01505616872538302</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07087204371326879</v>
+        <v>0.01999416625564079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1145649426344419</v>
+        <v>0.06401113532340716</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06777231970909227</v>
+        <v>0.01505498937035633</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0761470926930987</v>
+        <v>0.02559328538206398</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05833859528453696</v>
+        <v>0.0132221877301854</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06280693103666593</v>
+        <v>0.0122531237256312</v>
       </c>
     </row>
   </sheetData>
@@ -3683,28 +3683,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1486535319400622</v>
+        <v>0.1486535319400621</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667146915468443</v>
+        <v>0.1667146915468441</v>
       </c>
       <c r="D2" t="n">
         <v>0.1326677245298251</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2240556920799737</v>
+        <v>0.2240556920799734</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2240556920799737</v>
+        <v>0.2240556920799735</v>
       </c>
       <c r="G2" t="n">
         <v>0.1347744407432764</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1799197986366343</v>
+        <v>0.1799197986366342</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1396536178396501</v>
+        <v>0.13965361783965</v>
       </c>
       <c r="J2" t="n">
         <v>0.2006533077927776</v>
@@ -3723,16 +3723,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1678974723665098</v>
+        <v>0.1678974723665096</v>
       </c>
       <c r="C3" t="n">
         <v>0.1795961896018983</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1495104823947085</v>
+        <v>0.1495104823947081</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2419486061918192</v>
+        <v>0.2419486061918195</v>
       </c>
       <c r="F3" t="n">
         <v>0.2419486061918192</v>
@@ -3744,13 +3744,13 @@
         <v>0.2038612065586009</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1575558859314916</v>
+        <v>0.1575558859314914</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2245662107527834</v>
+        <v>0.2245662107527835</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1943129093027828</v>
+        <v>0.1943129093027827</v>
       </c>
       <c r="L3" t="n">
         <v>0.1179628080128916</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.05398037958773678</v>
+        <v>0.03535563174397702</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02625354088654066</v>
+        <v>0.009737675013893891</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04447749445847117</v>
+        <v>0.02585274661471119</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05152470547784389</v>
+        <v>0.03051766819780687</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05152470547784389</v>
+        <v>0.03051766819780687</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04615061623527931</v>
+        <v>0.02717915534730916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07255678384276665</v>
+        <v>0.0539320359990069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05143650498907665</v>
+        <v>0.03050270621133697</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07245819770096774</v>
+        <v>0.05383344985720792</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04995975354947615</v>
+        <v>0.0313350057057163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02818017401599993</v>
+        <v>0.009555426172240228</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.934965576103445</v>
+        <v>0.5424090235832199</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4146794961890938</v>
+        <v>0.07810064277671137</v>
       </c>
       <c r="D5" t="n">
-        <v>1.92305813670772</v>
+        <v>0.3564829378590224</v>
       </c>
       <c r="E5" t="n">
-        <v>2.352340323634007</v>
+        <v>0.4354612147990633</v>
       </c>
       <c r="F5" t="n">
-        <v>2.352340323634007</v>
+        <v>0.4354612147990633</v>
       </c>
       <c r="G5" t="n">
-        <v>2.105584238813203</v>
+        <v>0.3896394709569952</v>
       </c>
       <c r="H5" t="n">
-        <v>5.258812568410018</v>
+        <v>0.9667130491368433</v>
       </c>
       <c r="I5" t="n">
-        <v>2.352341004822682</v>
+        <v>0.4354618959877378</v>
       </c>
       <c r="J5" t="n">
-        <v>4.879880770861081</v>
+        <v>0.8999398181486733</v>
       </c>
       <c r="K5" t="n">
-        <v>2.464816106592431</v>
+        <v>0.45634972153829</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3928580860802039</v>
+        <v>0.07373873834775584</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>40.43332817911502</v>
+        <v>1.9035003859843</v>
       </c>
       <c r="C6" t="n">
-        <v>10.63932735087673</v>
+        <v>1.877638655450752</v>
       </c>
       <c r="D6" t="n">
-        <v>10.65819746599304</v>
+        <v>1.893867451482707</v>
       </c>
       <c r="E6" t="n">
-        <v>6.586497324606893</v>
+        <v>1.180672842932284</v>
       </c>
       <c r="F6" t="n">
-        <v>10.66575547594098</v>
+        <v>1.898622273676799</v>
       </c>
       <c r="G6" t="n">
-        <v>40.42549841576258</v>
+        <v>7.13394432955537</v>
       </c>
       <c r="H6" t="n">
-        <v>40.45747195997792</v>
+        <v>7.161677068484738</v>
       </c>
       <c r="I6" t="n">
-        <v>10.66589539341557</v>
+        <v>7.13726788041939</v>
       </c>
       <c r="J6" t="n">
-        <v>40.45480097153551</v>
+        <v>7.161125739540484</v>
       </c>
       <c r="K6" t="n">
-        <v>10.66471991475424</v>
+        <v>1.89953278395473</v>
       </c>
       <c r="L6" t="n">
-        <v>10.64179155420152</v>
+        <v>1.877551018962964</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07029725216339197</v>
+        <v>0.03822740130173136</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04506307460070701</v>
+        <v>0.01304815292964899</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06079395936883982</v>
+        <v>0.02872444442337561</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06774660004052706</v>
+        <v>0.0333727216253687</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06774660004052706</v>
+        <v>0.0333727216253687</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06246748881093448</v>
+        <v>0.03005092490506348</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08887365641842183</v>
+        <v>0.05680380555676112</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06775337756473176</v>
+        <v>0.03337447576909125</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08877507027662287</v>
+        <v>0.05670521941496223</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06627662612513127</v>
+        <v>0.03420677526347063</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04449704659165507</v>
+        <v>0.01242719572999458</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08402761696476356</v>
+        <v>0.04064394549367852</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08238143618584537</v>
+        <v>0.01961618453304381</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1030047504850877</v>
+        <v>0.0361535436195797</v>
       </c>
       <c r="E8" t="n">
-        <v>0.09861978014780542</v>
+        <v>0.03880640129480677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08222739426311818</v>
+        <v>0.03592134139473477</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09978659340282274</v>
+        <v>0.03661908727764564</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1261927610104523</v>
+        <v>0.06337196792936825</v>
       </c>
       <c r="I8" t="n">
-        <v>0.10507248215662</v>
+        <v>0.03994263814167335</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1260988106879444</v>
+        <v>0.06327419769176001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07956881797816015</v>
+        <v>0.03654620101692736</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1064565623126529</v>
+        <v>0.0233320704378009</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1399655710339356</v>
+        <v>0.0504890253565058</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1404683956501355</v>
+        <v>0.02983948934336253</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1561996939850448</v>
+        <v>0.04551585362484135</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1928579310945736</v>
+        <v>0.05539231577156518</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1631579802514246</v>
+        <v>0.05016512445149504</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1578728098603633</v>
+        <v>0.04684226131877701</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1842789774678501</v>
+        <v>0.07359514197047472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1631586986141599</v>
+        <v>0.05016581218280476</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1841803913260517</v>
+        <v>0.07349655582867573</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1461648258276398</v>
+        <v>0.04837357898371929</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1399023676410842</v>
+        <v>0.02921853214370802</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1063725113946573</v>
+        <v>0.1063725113946572</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1614870144628268</v>
+        <v>0.1614870144628266</v>
       </c>
       <c r="D2" t="n">
         <v>0.1175371984520745</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1968739974936435</v>
+        <v>0.1968739974936431</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1968739974936435</v>
+        <v>0.1968739974936431</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1063754419502965</v>
+        <v>0.1063754419502966</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1927521688452008</v>
+        <v>0.1927521688452006</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09795044591641065</v>
+        <v>0.09795044591641064</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1609169515822824</v>
+        <v>0.1609169515822823</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1472006182140518</v>
+        <v>0.147200618214052</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0837154958219315</v>
+        <v>0.08371549582193147</v>
       </c>
     </row>
     <row r="3">
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.121629155614593</v>
+        <v>0.1216291556145929</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1736179714847811</v>
+        <v>0.1736179714847812</v>
       </c>
       <c r="D3" t="n">
         <v>0.1344708584885793</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2108659589067685</v>
+        <v>0.2108659589067681</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2108659589067685</v>
+        <v>0.2108659589067682</v>
       </c>
       <c r="G3" t="n">
         <v>0.121632526360641</v>
@@ -4140,16 +4140,16 @@
         <v>0.2209833268089192</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1119426484502818</v>
+        <v>0.111942648450282</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1789108081471646</v>
+        <v>0.1789108081471645</v>
       </c>
       <c r="K3" t="n">
         <v>0.1613832654490067</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0955700155561951</v>
+        <v>0.09557001555619507</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03197089149036986</v>
+        <v>0.01857891309187835</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01745386159970171</v>
+        <v>0.005840233343893384</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03860782485808283</v>
+        <v>0.02521584645959135</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02904650694732977</v>
+        <v>0.01394002704063851</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02904650694732976</v>
+        <v>0.01394002704063851</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03236487440985471</v>
+        <v>0.01864968956844076</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08330026577098722</v>
+        <v>0.06990828737249578</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02958315710349781</v>
+        <v>0.01403355162477561</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04280364319563205</v>
+        <v>0.02941166479714061</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02772045666678769</v>
+        <v>0.01432847826829639</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01850838850136789</v>
+        <v>0.005116410102876407</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.362082020269571</v>
+        <v>0.252678470488525</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1892122050284767</v>
+        <v>0.03606970162355629</v>
       </c>
       <c r="D5" t="n">
-        <v>1.930251548022951</v>
+        <v>0.3581451399325969</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8716299706542142</v>
+        <v>0.1622347158494996</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8716299706542142</v>
+        <v>0.1622347158494996</v>
       </c>
       <c r="G5" t="n">
-        <v>1.36003180932292</v>
+        <v>0.2523190688469782</v>
       </c>
       <c r="H5" t="n">
-        <v>6.835121840157567</v>
+        <v>1.258228878025494</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8716288470585396</v>
+        <v>0.1622335922538254</v>
       </c>
       <c r="J5" t="n">
-        <v>2.437261066820629</v>
+        <v>0.4508361690716065</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9335706967361299</v>
+        <v>0.1737581196566144</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09391116857592667</v>
+        <v>0.01838729932408904</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.27167385237879</v>
+        <v>1.787369373155682</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06702625514478</v>
+        <v>1.774564965023806</v>
       </c>
       <c r="D6" t="n">
-        <v>10.08977010861487</v>
+        <v>1.794220395556617</v>
       </c>
       <c r="E6" t="n">
-        <v>6.214784561868781</v>
+        <v>1.102629918807633</v>
       </c>
       <c r="F6" t="n">
-        <v>10.07929633661077</v>
+        <v>1.782783987476737</v>
       </c>
       <c r="G6" t="n">
-        <v>10.0823107246836</v>
+        <v>1.787440149632245</v>
       </c>
       <c r="H6" t="n">
-        <v>38.33168412270966</v>
+        <v>6.801623809717209</v>
       </c>
       <c r="I6" t="n">
-        <v>10.07952900737724</v>
+        <v>6.744221236272899</v>
       </c>
       <c r="J6" t="n">
-        <v>10.60435269861521</v>
+        <v>6.760117266041101</v>
       </c>
       <c r="K6" t="n">
-        <v>10.0768607672082</v>
+        <v>1.782977163339979</v>
       </c>
       <c r="L6" t="n">
-        <v>10.06804175178107</v>
+        <v>1.773834272456122</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04372272500123053</v>
+        <v>0.02064723577858242</v>
       </c>
       <c r="C7" t="n">
-        <v>0.03130741290326452</v>
+        <v>0.008278458360108659</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0503593777715866</v>
+        <v>0.0272841197611609</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04129404609208474</v>
+        <v>0.01609559391843522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04129404609208474</v>
+        <v>0.01609559391843522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04411670792071514</v>
+        <v>0.0207180122551448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09505209928184792</v>
+        <v>0.07197661005919974</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04133499061435841</v>
+        <v>0.01610187431147968</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05455547670649279</v>
+        <v>0.03147998748384467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0394722901776486</v>
+        <v>0.01639680095500045</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03026022201222855</v>
+        <v>0.007184732789580464</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05438359565765635</v>
+        <v>0.02252354900394641</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05963605918338234</v>
+        <v>0.01326430007839308</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08239583517876867</v>
+        <v>0.03292253623427251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06482665611946886</v>
+        <v>0.02023733326081237</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05253325306124772</v>
+        <v>0.01807369433428936</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07248179924516517</v>
+        <v>0.0257102683011969</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1234171906073899</v>
+        <v>0.07696886610544409</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0697000819388084</v>
+        <v>0.0210941303575318</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08292404738175695</v>
+        <v>0.03647285589563673</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04980429584894192</v>
+        <v>0.01821523394329469</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0771188521940003</v>
+        <v>0.01543185165688444</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08606884172149068</v>
+        <v>0.02810015228096378</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09012210859063233</v>
+        <v>0.01862984474499532</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1091743157662585</v>
+        <v>0.03763554879213286</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1191550724429098</v>
+        <v>0.02979913448192635</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1001507348743119</v>
+        <v>0.02645437108797708</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1029314036080832</v>
+        <v>0.03106939864003148</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1538667949692158</v>
+        <v>0.08232799644408643</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1001496863017262</v>
+        <v>0.02645326069636634</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1133701723938608</v>
+        <v>0.04183137386873134</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07755011523843749</v>
+        <v>0.0250687996723765</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0890749176995965</v>
+        <v>0.01753611917446714</v>
       </c>
     </row>
   </sheetData>
@@ -4475,19 +4475,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1071680622243525</v>
+        <v>0.1071680622243524</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1586929412085923</v>
+        <v>0.1586929412085922</v>
       </c>
       <c r="D2" t="n">
         <v>0.1333558559837777</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1853341050975686</v>
+        <v>0.1853341050975687</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1853341050975686</v>
+        <v>0.1853341050975687</v>
       </c>
       <c r="G2" t="n">
         <v>0.1123078274700491</v>
@@ -4502,10 +4502,10 @@
         <v>0.1407480130455159</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1361316037465965</v>
+        <v>0.1361316037465966</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09680100327807996</v>
+        <v>0.09680100327807997</v>
       </c>
     </row>
     <row r="3">
@@ -4518,19 +4518,19 @@
         <v>0.120346031231597</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1704251412921878</v>
+        <v>0.1704251412921879</v>
       </c>
       <c r="D3" t="n">
         <v>0.1504674188400704</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1974739674303302</v>
+        <v>0.1974739674303301</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1974739674303302</v>
+        <v>0.1974739674303301</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1262578259633114</v>
+        <v>0.1262578259633113</v>
       </c>
       <c r="H3" t="n">
         <v>0.2040747007776192</v>
@@ -4539,10 +4539,10 @@
         <v>0.1123928565202019</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1557533436056449</v>
+        <v>0.1557533436056451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1485134132427802</v>
+        <v>0.14851341324278</v>
       </c>
       <c r="L3" t="n">
         <v>0.1084223918389513</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01982679826953202</v>
+        <v>0.009762135336627537</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01220565164256769</v>
+        <v>0.00371401977605562</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03539433198855796</v>
+        <v>0.02532966905565347</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01755928649178294</v>
+        <v>0.005977735078666532</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01755928649178295</v>
+        <v>0.005977735078666532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02326968499327028</v>
+        <v>0.01288571046178452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06308484452207286</v>
+        <v>0.05302018158916838</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01830485507384108</v>
+        <v>0.006107627989892733</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02705873773330369</v>
+        <v>0.0169940748003992</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01667592898566791</v>
+        <v>0.006611266052763416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01366814962996364</v>
+        <v>0.003603486697059144</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6334436127091445</v>
+        <v>0.1177586940928089</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09124755599407317</v>
+        <v>0.01762539486654031</v>
       </c>
       <c r="D5" t="n">
-        <v>2.044704311897939</v>
+        <v>0.3789682236034781</v>
       </c>
       <c r="E5" t="n">
-        <v>0.241455293900744</v>
+        <v>0.04538343216911972</v>
       </c>
       <c r="F5" t="n">
-        <v>0.241455293900744</v>
+        <v>0.04538343216911972</v>
       </c>
       <c r="G5" t="n">
-        <v>0.921770686980069</v>
+        <v>0.1710218859545838</v>
       </c>
       <c r="H5" t="n">
-        <v>5.195837815508314</v>
+        <v>0.9563846995877742</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2414536832714913</v>
+        <v>0.04538182153986801</v>
       </c>
       <c r="J5" t="n">
-        <v>1.345596476431633</v>
+        <v>0.2490567155538494</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3258717590802138</v>
+        <v>0.06102973185453145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05398164646026206</v>
+        <v>0.01069866210074572</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>38.2545635884354</v>
+        <v>1.778143357731391</v>
       </c>
       <c r="C6" t="n">
-        <v>10.06000473371692</v>
+        <v>1.772126648638815</v>
       </c>
       <c r="D6" t="n">
-        <v>10.08544363511021</v>
+        <v>1.794138336820591</v>
       </c>
       <c r="E6" t="n">
-        <v>6.201101859021238</v>
+        <v>1.094281221946766</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06568889420872</v>
+        <v>1.774448536454205</v>
       </c>
       <c r="G6" t="n">
-        <v>38.25800647515918</v>
+        <v>6.742199349067495</v>
       </c>
       <c r="H6" t="n">
-        <v>38.30671587973109</v>
+        <v>6.783899207313987</v>
       </c>
       <c r="I6" t="n">
-        <v>10.06592549130635</v>
+        <v>6.735421266595601</v>
       </c>
       <c r="J6" t="n">
-        <v>38.26464963508549</v>
+        <v>1.875366034578723</v>
       </c>
       <c r="K6" t="n">
-        <v>10.06328465308691</v>
+        <v>1.774814391913391</v>
       </c>
       <c r="L6" t="n">
-        <v>10.06109402857395</v>
+        <v>1.771950431809226</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02880735708260339</v>
+        <v>0.01134271367916355</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02305085512274562</v>
+        <v>0.005622775578224167</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04437467552053351</v>
+        <v>0.02691020950871685</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02722459318862362</v>
+        <v>0.007678829048092936</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02722459318862362</v>
+        <v>0.007678829048092936</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03225024380634166</v>
+        <v>0.01446628880432055</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07206540333514423</v>
+        <v>0.05460075993170439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02728541388691244</v>
+        <v>0.007688206332428769</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03603929654637508</v>
+        <v>0.01857465314293522</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02565648779873927</v>
+        <v>0.008191844395299448</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02264870844303501</v>
+        <v>0.005184065039595176</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.03734066945424709</v>
+        <v>0.01284457664843486</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04527982820608259</v>
+        <v>0.009535074819692289</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06951230143405099</v>
+        <v>0.03133443164552282</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04576084706688749</v>
+        <v>0.01094120971298984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03621915313062946</v>
+        <v>0.009261871589308074</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05453599637656514</v>
+        <v>0.01838858123542652</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0943511559066723</v>
+        <v>0.05852305236303994</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04957116645713593</v>
+        <v>0.01161049876353475</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0583277518391011</v>
+        <v>0.02249742125319908</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03393434153544114</v>
+        <v>0.009648746645064599</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05930003473663538</v>
+        <v>0.01163469843231542</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05834382299523763</v>
+        <v>0.01654113165161901</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06438168044845564</v>
+        <v>0.01289700079613294</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08570568396820735</v>
+        <v>0.03418446695609112</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08222818395487325</v>
+        <v>0.01735946097049735</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0686177878437116</v>
+        <v>0.01496403126791278</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07358106913205148</v>
+        <v>0.02174051402222934</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1133962286608541</v>
+        <v>0.06187498514961324</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06861623921262228</v>
+        <v>0.01496243155033754</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07737012187208482</v>
+        <v>0.02584887836084401</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0598763504236904</v>
+        <v>0.01421454018465623</v>
       </c>
       <c r="L9" t="n">
-        <v>0.06397953376874481</v>
+        <v>0.01245829025750395</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01917557815607407</v>
+        <v>0.01917557815607424</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2875686217410569</v>
+        <v>0.2875686217410571</v>
       </c>
       <c r="D2" t="n">
         <v>0.03344243910845224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2971231553451787</v>
+        <v>0.2971231553451789</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2677816983836304</v>
+        <v>0.2677816983836305</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05798147320727143</v>
+        <v>0.05798147320727141</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04182054072288301</v>
+        <v>0.04182054072288306</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09714754858004357</v>
+        <v>0.09714754858004362</v>
       </c>
       <c r="J2" t="n">
         <v>0.3587551911189472</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2728329462779769</v>
+        <v>0.2728329462779771</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02729525910397774</v>
+        <v>0.02729525910397776</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02789697102317069</v>
+        <v>0.02789697102317061</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3080041075996931</v>
+        <v>0.3080041075996937</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04430681648974833</v>
+        <v>0.04430681648974834</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3175582579272214</v>
+        <v>0.3175582579272216</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2882168009656732</v>
+        <v>0.2882168009656734</v>
       </c>
       <c r="G3" t="n">
         <v>0.07253178894899016</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0539455444408181</v>
+        <v>0.05394554444081821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1176145541370673</v>
+        <v>0.1176145541370675</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3853212899685958</v>
+        <v>0.385321289968596</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2927913807417986</v>
+        <v>0.2927913807417987</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03723806694789301</v>
+        <v>0.03723806694789304</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03682725962080841</v>
+        <v>0.009750342947967897</v>
       </c>
       <c r="C4" t="n">
-        <v>0.08886405458632386</v>
+        <v>0.057107816728839</v>
       </c>
       <c r="D4" t="n">
-        <v>0.045308303918817</v>
+        <v>0.0182313872459765</v>
       </c>
       <c r="E4" t="n">
-        <v>0.08923910151063197</v>
+        <v>0.05717382483524554</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08923910151063204</v>
+        <v>0.05717382483524554</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06051856558308433</v>
+        <v>0.03292842405318074</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05029285206212653</v>
+        <v>0.02321593538928598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08732003654065247</v>
+        <v>0.05684047822870567</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1074492080857471</v>
+        <v>0.08037229141290636</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08129881176171905</v>
+        <v>0.0542218950888785</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04166279250145506</v>
+        <v>0.01458587582861452</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1282205038591543</v>
+        <v>0.02583555384675896</v>
       </c>
       <c r="C5" t="n">
-        <v>4.385571808184259</v>
+        <v>0.8133283772644163</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9493009769920603</v>
+        <v>0.1773340968447528</v>
       </c>
       <c r="E5" t="n">
-        <v>4.385571807999893</v>
+        <v>0.8133283770800538</v>
       </c>
       <c r="F5" t="n">
-        <v>4.385571807999893</v>
+        <v>0.8133283770800538</v>
       </c>
       <c r="G5" t="n">
-        <v>2.417419985261418</v>
+        <v>0.4477430716688506</v>
       </c>
       <c r="H5" t="n">
-        <v>1.616471510598307</v>
+        <v>0.2988633777980302</v>
       </c>
       <c r="I5" t="n">
-        <v>4.385577158517299</v>
+        <v>0.8133337275974576</v>
       </c>
       <c r="J5" t="n">
-        <v>7.426598154055497</v>
+        <v>1.368542498923496</v>
       </c>
       <c r="K5" t="n">
-        <v>4.439051861016183</v>
+        <v>0.8211864276017872</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2536982994731245</v>
+        <v>0.05190412485341502</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41.09459552014134</v>
+        <v>7.235917517643838</v>
       </c>
       <c r="C6" t="n">
-        <v>10.88971420034979</v>
+        <v>1.958057432082716</v>
       </c>
       <c r="D6" t="n">
-        <v>10.83989083318614</v>
+        <v>1.91807790210251</v>
       </c>
       <c r="E6" t="n">
-        <v>6.742370062047859</v>
+        <v>1.228124867544879</v>
       </c>
       <c r="F6" t="n">
-        <v>10.88696097836952</v>
+        <v>1.9575728648649</v>
       </c>
       <c r="G6" t="n">
-        <v>10.8603809176089</v>
+        <v>7.259095598749044</v>
       </c>
       <c r="H6" t="n">
-        <v>10.84850141246851</v>
+        <v>7.249870914929832</v>
       </c>
       <c r="I6" t="n">
-        <v>41.14508829706115</v>
+        <v>7.283007652924571</v>
       </c>
       <c r="J6" t="n">
-        <v>41.16735746044611</v>
+        <v>7.306916104670552</v>
       </c>
       <c r="K6" t="n">
-        <v>10.88302134720279</v>
+        <v>1.955325051025181</v>
       </c>
       <c r="L6" t="n">
-        <v>10.8395774058587</v>
+        <v>1.915018837481797</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05545764052476491</v>
+        <v>0.01302928996929701</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1059450671115663</v>
+        <v>0.06011407491699201</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06393776338125159</v>
+        <v>0.0215101720935986</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1060576506585061</v>
+        <v>0.06013388946923204</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1060576506585061</v>
+        <v>0.06013388946923204</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07914894648704082</v>
+        <v>0.03620737107450977</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06892323296608301</v>
+        <v>0.02649488241061511</v>
       </c>
       <c r="I7" t="n">
-        <v>0.105950417444609</v>
+        <v>0.06011942525003464</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1260795889897036</v>
+        <v>0.0836512384342354</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09992919266567551</v>
+        <v>0.05750084211020755</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06029317340541156</v>
+        <v>0.01786482284994359</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06986070005529166</v>
+        <v>0.01556422843293391</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1459848068767454</v>
+        <v>0.06716106907747871</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1091570783555925</v>
+        <v>0.02946877148595807</v>
       </c>
       <c r="E8" t="n">
-        <v>0.138992311267863</v>
+        <v>0.06593038970506988</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1212248768267989</v>
+        <v>0.06280332126038693</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1190749842250694</v>
+        <v>0.04323435367832635</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1088492707041274</v>
+        <v>0.03352186501443445</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1458764551826376</v>
+        <v>0.06714640785385133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1660106426817878</v>
+        <v>0.0906791038459611</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1138581497760682</v>
+        <v>0.05995233854835287</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1268800960384645</v>
+        <v>0.02958412116985867</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1488087392788417</v>
+        <v>0.02945908326098782</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2322385798663117</v>
+        <v>0.0823417330413843</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1902322316742557</v>
+        <v>0.04373799839272354</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2702534691857186</v>
+        <v>0.08903235337343207</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2322385888149666</v>
+        <v>0.08234173446443351</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2054424592417863</v>
+        <v>0.05843502919890208</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1952167457208285</v>
+        <v>0.04872254053500737</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2322439301993546</v>
+        <v>0.08234708337442706</v>
       </c>
       <c r="J9" t="n">
-        <v>0.252373101744449</v>
+        <v>0.1058788965586278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2071357557145456</v>
+        <v>0.07636919710456855</v>
       </c>
       <c r="L9" t="n">
-        <v>0.186586686160157</v>
+        <v>0.04009248097433591</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02016037087287464</v>
+        <v>0.02016037087287471</v>
       </c>
       <c r="C2" t="n">
         <v>0.2659112557306498</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02917792238985985</v>
+        <v>0.02917792238985978</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2753887714786561</v>
+        <v>0.2753887714786564</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2462740711090482</v>
+        <v>0.2462740711090483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04720174606846492</v>
+        <v>0.04720174606846485</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03680477086509847</v>
+        <v>0.03680477086509844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07616457104240229</v>
+        <v>0.0761645710424023</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3345976610183303</v>
+        <v>0.3345976610183308</v>
       </c>
       <c r="K2" t="n">
         <v>0.2401081160795061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02415968105720265</v>
+        <v>0.02415968105720264</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02901081465244131</v>
+        <v>0.02901081465244134</v>
       </c>
       <c r="C3" t="n">
         <v>0.2831750516010259</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03938286687714351</v>
+        <v>0.03938286687714342</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2926528776437231</v>
+        <v>0.2926528776437233</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2635381772741149</v>
+        <v>0.2635381772741153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06011399773136636</v>
+        <v>0.06011399773136639</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04815692248799934</v>
+        <v>0.04815692248799933</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09345215742785774</v>
+        <v>0.09345215742785776</v>
       </c>
       <c r="J3" t="n">
         <v>0.3576533485362156</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2553427515599164</v>
+        <v>0.2553427515599167</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0336121558913155</v>
+        <v>0.03361215589131551</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03068191023774925</v>
+        <v>0.009184049809669192</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06875383578210224</v>
+        <v>0.04332208447653225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03604246250852634</v>
+        <v>0.01454460208044592</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06906966199229997</v>
+        <v>0.04337767117907371</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06906966199230001</v>
+        <v>0.04337767117907371</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0473594982980185</v>
+        <v>0.025365065519636</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04057902507637652</v>
+        <v>0.01908116464829603</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06798378219238843</v>
+        <v>0.04318982764268266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08690037593846217</v>
+        <v>0.06540251551038086</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05594789431886044</v>
+        <v>0.03445003389077971</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03306584296832647</v>
+        <v>0.01156798254024603</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2262761426738199</v>
+        <v>0.04360863453188466</v>
       </c>
       <c r="C5" t="n">
-        <v>3.029179758260039</v>
+        <v>0.5643570440093674</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7012467858191374</v>
+        <v>0.1316205623487242</v>
       </c>
       <c r="E5" t="n">
-        <v>3.029179759825387</v>
+        <v>0.5643570455747173</v>
       </c>
       <c r="F5" t="n">
-        <v>3.029179759825387</v>
+        <v>0.5643570455747173</v>
       </c>
       <c r="G5" t="n">
-        <v>1.696366285844095</v>
+        <v>0.3155902585551297</v>
       </c>
       <c r="H5" t="n">
-        <v>1.267683653153084</v>
+        <v>0.2350515780195383</v>
       </c>
       <c r="I5" t="n">
-        <v>3.029183729858586</v>
+        <v>0.5643610156079142</v>
       </c>
       <c r="J5" t="n">
-        <v>5.65620207372601</v>
+        <v>1.04559960900969</v>
       </c>
       <c r="K5" t="n">
-        <v>2.353356967796806</v>
+        <v>0.4387940286319179</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5182626558415748</v>
+        <v>0.0543440615428717</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.08933026000378</v>
+        <v>6.741164769501785</v>
       </c>
       <c r="C6" t="n">
-        <v>10.12876571349682</v>
+        <v>1.813884165360349</v>
       </c>
       <c r="D6" t="n">
-        <v>10.09146716942415</v>
+        <v>1.784299340907997</v>
       </c>
       <c r="E6" t="n">
-        <v>6.264523107839106</v>
+        <v>1.133777471739667</v>
       </c>
       <c r="F6" t="n">
-        <v>10.12684690136274</v>
+        <v>1.813546455716426</v>
       </c>
       <c r="G6" t="n">
-        <v>10.10600784806406</v>
+        <v>6.757345785211753</v>
       </c>
       <c r="H6" t="n">
-        <v>38.29300882422852</v>
+        <v>6.751508772818713</v>
       </c>
       <c r="I6" t="n">
-        <v>10.12663213195843</v>
+        <v>6.775170547334797</v>
       </c>
       <c r="J6" t="n">
-        <v>10.65794243671533</v>
+        <v>6.797728363548607</v>
       </c>
       <c r="K6" t="n">
-        <v>10.11513876361424</v>
+        <v>1.804867617293573</v>
       </c>
       <c r="L6" t="n">
-        <v>10.09076102470831</v>
+        <v>1.781722324934718</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04472257166200127</v>
+        <v>0.0116552062069473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08202047201809416</v>
+        <v>0.04565701244141476</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05008243951986478</v>
+        <v>0.01701563802105188</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08202969150071555</v>
+        <v>0.04565863636019524</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08202969150071555</v>
+        <v>0.04565863636019524</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06140015972227059</v>
+        <v>0.02783622191691415</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05461968650062871</v>
+        <v>0.02155232104557411</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0820244436166403</v>
+        <v>0.04566098403996079</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1009410373627131</v>
+        <v>0.06787367190765892</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06998855574311239</v>
+        <v>0.03692119028805783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0471065043925786</v>
+        <v>0.0140391389375241</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.05597534453348938</v>
+        <v>0.01363569422159773</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1127887502837678</v>
+        <v>0.05107222938689554</v>
       </c>
       <c r="D8" t="n">
-        <v>0.08488192634664342</v>
+        <v>0.02314034766937743</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1074536180345509</v>
+        <v>0.05013324740590406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09389734125618397</v>
+        <v>0.04774734270583979</v>
       </c>
       <c r="G8" t="n">
-        <v>0.09215506743479447</v>
+        <v>0.03324908564498816</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08537459421319096</v>
+        <v>0.02696518477365496</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1127793513291642</v>
+        <v>0.05107384776803481</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1316997777705159</v>
+        <v>0.07328721019009832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08087906645035832</v>
+        <v>0.03883792016214723</v>
       </c>
       <c r="L8" t="n">
-        <v>0.09823302265785025</v>
+        <v>0.02303740610345388</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1080649839348503</v>
+        <v>0.02280347070656067</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1682568924838128</v>
+        <v>0.06083462236113975</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1363195639874396</v>
+        <v>0.03219337184510296</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1946761128685693</v>
+        <v>0.06548440641350943</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1682568949197455</v>
+        <v>0.06083462407971176</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1476365801879888</v>
+        <v>0.04301383183663916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1408561069663466</v>
+        <v>0.03672993096529909</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1682608640823589</v>
+        <v>0.06083859395968575</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1871774578284314</v>
+        <v>0.08305128182738389</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1273973282509656</v>
+        <v>0.04702513419469077</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1333429248582965</v>
+        <v>0.02921674885724911</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02101132385403108</v>
+        <v>0.02101132385403102</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2216094395630533</v>
+        <v>0.2216094395630534</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02964365276045808</v>
+        <v>0.02964365276045813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2310634668760631</v>
+        <v>0.2310634668760634</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2020308111850351</v>
+        <v>0.2020308111850353</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04050861850940594</v>
+        <v>0.04050861850940596</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05983951462532766</v>
+        <v>0.05983951462532761</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03322233668560538</v>
+        <v>0.03322233668560545</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3078188004008954</v>
+        <v>0.3078188004008953</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2051758797840715</v>
+        <v>0.205175879784072</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0215280777281942</v>
+        <v>0.02152807772819424</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03000507813969936</v>
+        <v>0.0300050781396994</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2324348622463377</v>
+        <v>0.2324348622463379</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03993404456363631</v>
+        <v>0.03993404456363633</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2418917650104699</v>
+        <v>0.2418917650104701</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2128591093194421</v>
+        <v>0.2128591093194423</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05243100584580077</v>
+        <v>0.0524310058458009</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07466587904362462</v>
+        <v>0.07466587904362457</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04404689751251034</v>
+        <v>0.04404689751251043</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3270452475287978</v>
+        <v>0.3270452475287979</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2154399977128487</v>
+        <v>0.2154399977128488</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03060051405971224</v>
+        <v>0.03060051405971219</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02120908602065733</v>
+        <v>0.00789354213157027</v>
       </c>
       <c r="C4" t="n">
-        <v>0.03057149840332625</v>
+        <v>0.01552386078711994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02634063977272401</v>
+        <v>0.01302509588363691</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03096098226324221</v>
+        <v>0.01559241581478602</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03096098226324223</v>
+        <v>0.01559241581478602</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03332961125662325</v>
+        <v>0.01957717454637758</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04428660264770452</v>
+        <v>0.03097105875861739</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03200631924082942</v>
+        <v>0.01577560350322556</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06170584216045555</v>
+        <v>0.04839029827136846</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02623665867010636</v>
+        <v>0.01292111478101916</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02152157096503387</v>
+        <v>0.008206027075946693</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3221611643406298</v>
+        <v>0.06086110762887455</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9241071057316496</v>
+        <v>0.1727861268247629</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7590023542503778</v>
+        <v>0.141973556932983</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9241071128538492</v>
+        <v>0.1727861339469622</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9241071128538492</v>
+        <v>0.1727861339469622</v>
       </c>
       <c r="G5" t="n">
-        <v>1.360040110120865</v>
+        <v>0.2530782210812333</v>
       </c>
       <c r="H5" t="n">
-        <v>2.619197778475073</v>
+        <v>0.4841554232486078</v>
       </c>
       <c r="I5" t="n">
-        <v>0.924106152151643</v>
+        <v>0.1727851732447556</v>
       </c>
       <c r="J5" t="n">
-        <v>4.263531931083951</v>
+        <v>0.7879116859147303</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7020938589626877</v>
+        <v>0.1318719813879661</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4191718692313451</v>
+        <v>0.07819247919158877</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.0733514673149</v>
+        <v>1.777070591652888</v>
       </c>
       <c r="C6" t="n">
-        <v>10.08331648701936</v>
+        <v>1.784806969196498</v>
       </c>
       <c r="D6" t="n">
-        <v>38.26782676456909</v>
+        <v>6.743526617377875</v>
       </c>
       <c r="E6" t="n">
-        <v>6.219496169846266</v>
+        <v>1.104774602927552</v>
       </c>
       <c r="F6" t="n">
-        <v>10.08401305552484</v>
+        <v>1.78492957112149</v>
       </c>
       <c r="G6" t="n">
-        <v>10.08547199255087</v>
+        <v>1.788754224067694</v>
       </c>
       <c r="H6" t="n">
-        <v>38.28879392811344</v>
+        <v>6.762004311567773</v>
       </c>
       <c r="I6" t="n">
-        <v>38.27327821866548</v>
+        <v>6.746239421332242</v>
       </c>
       <c r="J6" t="n">
-        <v>38.30515538728719</v>
+        <v>1.907744905192969</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07745788408008</v>
+        <v>1.781936040867582</v>
       </c>
       <c r="L6" t="n">
-        <v>10.0734475915486</v>
+        <v>1.777344997112391</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0320726595633181</v>
+        <v>0.009805531064718228</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04287084636349704</v>
+        <v>0.01768854601638045</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03720390077941241</v>
+        <v>0.01493702981045405</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04263577215341911</v>
+        <v>0.01764717882432322</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04263577215341911</v>
+        <v>0.01764717882432322</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04419318479928388</v>
+        <v>0.02148916347952548</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05515017619036521</v>
+        <v>0.03288304769176532</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04286989278349014</v>
+        <v>0.01768759243637355</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07256941570311631</v>
+        <v>0.0503022872045164</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03710023221276697</v>
+        <v>0.01483310371416715</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03238514450769456</v>
+        <v>0.01011801600909469</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04208213664740165</v>
+        <v>0.01156719902197114</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06882498120093834</v>
+        <v>0.02225647372301827</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06673184707945386</v>
+        <v>0.02013394833110128</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0644272632654051</v>
+        <v>0.0214824812392508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05325271766318192</v>
+        <v>0.01951576122391641</v>
       </c>
       <c r="G8" t="n">
-        <v>0.07036868778333265</v>
+        <v>0.02609605197975516</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08132567917447732</v>
+        <v>0.03748993619200616</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06904539576753886</v>
+        <v>0.02229448093660321</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09874809574592516</v>
+        <v>0.05490973486708481</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04680941706854352</v>
+        <v>0.01654192023952444</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07544741329887218</v>
+        <v>0.01769697527527454</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07496905584643283</v>
+        <v>0.01735529676963724</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1018986051003679</v>
+        <v>0.02807743149777642</v>
       </c>
       <c r="D9" t="n">
-        <v>0.09623197433789531</v>
+        <v>0.02532597070045347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1205138214845032</v>
+        <v>0.03135371543232372</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1018985777939774</v>
+        <v>0.02807743256054408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1032209435361548</v>
+        <v>0.03187804896092156</v>
       </c>
       <c r="H9" t="n">
-        <v>0.114177934927236</v>
+        <v>0.04327193317316134</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1018976515203611</v>
+        <v>0.02807647791776953</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1315971744399871</v>
+        <v>0.06069117268591243</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08678141715251479</v>
+        <v>0.0235769922161831</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09141290324456536</v>
+        <v>0.02050690149049067</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02153969927100366</v>
+        <v>0.02153969927100367</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2946284485932787</v>
+        <v>0.2946284485932786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06656320192692143</v>
+        <v>0.06656320192692149</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3043122056166525</v>
+        <v>0.3043122056166526</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2746337942115224</v>
+        <v>0.2746337942115222</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08689377005147489</v>
+        <v>0.08689377005147483</v>
       </c>
       <c r="H2" t="n">
         <v>0.1176656052778973</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1043111902540193</v>
+        <v>0.1043111902540192</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4151465473296765</v>
+        <v>0.4151465473296762</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2905043276227927</v>
+        <v>0.2905043276227925</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08959568168652524</v>
+        <v>0.08959568168652532</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03064146129668846</v>
+        <v>0.03064146129668838</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3161624846079805</v>
+        <v>0.3161624846079804</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08242781594147175</v>
+        <v>0.08242781594147165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3258480402889512</v>
+        <v>0.325848040288951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2961696288838207</v>
+        <v>0.2961696288838209</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1058121807492074</v>
+        <v>0.1058121807492075</v>
       </c>
       <c r="H3" t="n">
-        <v>0.141207005836576</v>
+        <v>0.1412070058365759</v>
       </c>
       <c r="I3" t="n">
         <v>0.1258624874161324</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4501213953763139</v>
+        <v>0.4501213953763136</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3131186911213122</v>
+        <v>0.3131186911213119</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1089204027209542</v>
+        <v>0.1089204027209544</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04133901748419545</v>
+        <v>0.01157144526941791</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09448267446055252</v>
+        <v>0.06147286337472985</v>
       </c>
       <c r="D4" t="n">
-        <v>0.06810358200549625</v>
+        <v>0.03833600979071869</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09497663136047901</v>
+        <v>0.06155980285241797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09497663136047901</v>
+        <v>0.06155980285241796</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0807667399046095</v>
+        <v>0.05052331046754968</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09847517614895936</v>
+        <v>0.06870760393418181</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09439111214408427</v>
+        <v>0.06145870313612173</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1437339658451945</v>
+        <v>0.1139663936304168</v>
       </c>
       <c r="K4" t="n">
-        <v>0.09481629224427508</v>
+        <v>0.06504872002949751</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08179760853389584</v>
+        <v>0.05203003631911836</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.172543637536826</v>
+        <v>0.03466345827355426</v>
       </c>
       <c r="C5" t="n">
-        <v>4.666992502903827</v>
+        <v>0.8662345888200608</v>
       </c>
       <c r="D5" t="n">
-        <v>2.504348602040636</v>
+        <v>0.4671151309935183</v>
       </c>
       <c r="E5" t="n">
-        <v>4.666992506621996</v>
+        <v>0.8662345925382301</v>
       </c>
       <c r="F5" t="n">
-        <v>4.666992506621996</v>
+        <v>0.8662345925382301</v>
       </c>
       <c r="G5" t="n">
-        <v>3.782416204421163</v>
+        <v>0.7020136126922945</v>
       </c>
       <c r="H5" t="n">
-        <v>5.789936376499317</v>
+        <v>1.070404769768044</v>
       </c>
       <c r="I5" t="n">
-        <v>4.666994875147764</v>
+        <v>0.8662369610639935</v>
       </c>
       <c r="J5" t="n">
-        <v>10.74896952607322</v>
+        <v>1.980487842116605</v>
       </c>
       <c r="K5" t="n">
-        <v>5.004268546924763</v>
+        <v>0.9291123121712451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5816848462235515</v>
+        <v>0.8491200878543476</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.84602993057433</v>
+        <v>1.913197035669126</v>
       </c>
       <c r="C6" t="n">
-        <v>10.899523054808</v>
+        <v>1.963159960011391</v>
       </c>
       <c r="D6" t="n">
-        <v>10.86874069299405</v>
+        <v>7.266694175205055</v>
       </c>
       <c r="E6" t="n">
-        <v>6.751962991433484</v>
+        <v>1.23318939587667</v>
       </c>
       <c r="F6" t="n">
-        <v>10.89849002896279</v>
+        <v>1.962978150527392</v>
       </c>
       <c r="G6" t="n">
-        <v>41.15034155483523</v>
+        <v>1.952148900867257</v>
       </c>
       <c r="H6" t="n">
-        <v>41.17234933371684</v>
+        <v>7.297709416495026</v>
       </c>
       <c r="I6" t="n">
-        <v>41.16396592707471</v>
+        <v>1.963084293535828</v>
       </c>
       <c r="J6" t="n">
-        <v>41.21624802870001</v>
+        <v>7.34272882952305</v>
       </c>
       <c r="K6" t="n">
-        <v>10.90077639222288</v>
+        <v>1.966897687320364</v>
       </c>
       <c r="L6" t="n">
-        <v>10.88550967390751</v>
+        <v>1.953483349521652</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06534943306609149</v>
+        <v>0.01579727838893349</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1183991554820477</v>
+        <v>0.06568216401170451</v>
       </c>
       <c r="D7" t="n">
-        <v>0.09211318613666429</v>
+        <v>0.04256170009490693</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1183379863071066</v>
+        <v>0.06567140130074534</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1183379863071066</v>
+        <v>0.06567140130074534</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1047771554865057</v>
+        <v>0.05474914358706533</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1224855917308554</v>
+        <v>0.07293343705369752</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1184015277259806</v>
+        <v>0.0656845362556374</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1677443814270906</v>
+        <v>0.1181922267499325</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1188267078261711</v>
+        <v>0.0692745531490131</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1058080241157919</v>
+        <v>0.056255869438634</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.08481831771546117</v>
+        <v>0.01922380206865555</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1709538334358683</v>
+        <v>0.07493178728137119</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1515909651129608</v>
+        <v>0.05302978913801266</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1618965524815869</v>
+        <v>0.07333770890591321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1388824247148735</v>
+        <v>0.06928722244091964</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1573829656440641</v>
+        <v>0.06400776612462682</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1750914018884472</v>
+        <v>0.08219205959126473</v>
       </c>
       <c r="I8" t="n">
-        <v>0.171007337883539</v>
+        <v>0.07494315879319879</v>
       </c>
       <c r="J8" t="n">
-        <v>0.220356703899496</v>
+        <v>0.1274519954549008</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1376800570750646</v>
+        <v>0.07259274259883836</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1930281237938345</v>
+        <v>0.07160660689878987</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1913751563361498</v>
+        <v>0.03797780556427622</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2883166582830886</v>
+        <v>0.09558764434264162</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2620315202380658</v>
+        <v>0.07246732673470677</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3389667972311271</v>
+        <v>0.1045020718129649</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2883166094920706</v>
+        <v>0.09558763881919477</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2746946582875468</v>
+        <v>0.08465462391800251</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2924030945318967</v>
+        <v>0.1028389173846347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2883190305270213</v>
+        <v>0.09559001658657458</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3376618842281318</v>
+        <v>0.1480977070808697</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2334766203981699</v>
+        <v>0.09470416675273463</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2757255269168332</v>
+        <v>0.08616134976957118</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01903090546681276</v>
+        <v>0.01903090546681084</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2656513064958769</v>
+        <v>0.2656513064958708</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06436401562698729</v>
+        <v>0.0643640156269787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2751605614575817</v>
+        <v>0.2751605614575762</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2459732569667219</v>
+        <v>0.2459732569667199</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07089523203317036</v>
+        <v>0.07089523203316846</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1002102644872383</v>
+        <v>0.1002102644872389</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07631634593819091</v>
+        <v>0.07631634593819092</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3453423458913245</v>
+        <v>0.3453423458913241</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2266153057131151</v>
+        <v>0.2266153057131126</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09507852107987561</v>
+        <v>0.09507852107987208</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02768284762257137</v>
+        <v>0.0276828476225719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2829067546876946</v>
+        <v>0.2829067546876926</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0798253150322482</v>
+        <v>0.07982531503224374</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2924179509363102</v>
+        <v>0.2924179509363114</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2632306464454504</v>
+        <v>0.2632306464454551</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08733756683676547</v>
+        <v>0.08733756683676495</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1210566532229739</v>
+        <v>0.1210566532229699</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09358049617487263</v>
+        <v>0.09358049617486842</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3700206453589907</v>
+        <v>0.370020645358986</v>
       </c>
       <c r="K3" t="n">
-        <v>0.239943713904736</v>
+        <v>0.2399437139047318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1151525828371359</v>
+        <v>0.1151525828371354</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03114008626960412</v>
+        <v>0.008600482079852543</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06844031649084198</v>
+        <v>0.04322811635796091</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05808869933297636</v>
+        <v>0.03554909514324719</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06882593333903141</v>
+        <v>0.04329598857262817</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06882593333902658</v>
+        <v>0.04329598857262817</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06252567442520754</v>
+        <v>0.03952920863450045</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07939141045896586</v>
+        <v>0.05685180626922833</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06889039248332118</v>
+        <v>0.04330794899720073</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09456576452218532</v>
+        <v>0.07202616033246216</v>
       </c>
       <c r="K4" t="n">
-        <v>0.04964760013420809</v>
+        <v>0.02710799594448644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07634374162554391</v>
+        <v>0.05380413743579843</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.104622506304876</v>
+        <v>0.02153338793598689</v>
       </c>
       <c r="C5" t="n">
-        <v>2.927463851311776</v>
+        <v>0.5464162557598635</v>
       </c>
       <c r="D5" t="n">
-        <v>2.222823825981507</v>
+        <v>0.4165424753689305</v>
       </c>
       <c r="E5" t="n">
-        <v>2.927463855741016</v>
+        <v>0.5464162601891756</v>
       </c>
       <c r="F5" t="n">
-        <v>2.927463855741026</v>
+        <v>0.5464162601891756</v>
       </c>
       <c r="G5" t="n">
-        <v>2.69476124373857</v>
+        <v>0.5028026663233535</v>
       </c>
       <c r="H5" t="n">
-        <v>4.207478832553788</v>
+        <v>0.783395188621075</v>
       </c>
       <c r="I5" t="n">
-        <v>2.927464602846922</v>
+        <v>0.5464170072950472</v>
       </c>
       <c r="J5" t="n">
-        <v>5.820981470311469</v>
+        <v>1.079875319090255</v>
       </c>
       <c r="K5" t="n">
-        <v>1.643260623453737</v>
+        <v>0.3075838865289374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2631896333003094</v>
+        <v>0.08668901419236812</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.09088145683418</v>
+        <v>6.741864652492143</v>
       </c>
       <c r="C6" t="n">
-        <v>10.12935160236919</v>
+        <v>1.813948493077717</v>
       </c>
       <c r="D6" t="n">
-        <v>10.11726332842488</v>
+        <v>1.805963842316335</v>
       </c>
       <c r="E6" t="n">
-        <v>6.265127717059189</v>
+        <v>1.133845096598129</v>
       </c>
       <c r="F6" t="n">
-        <v>10.12897779597497</v>
+        <v>1.813882706802445</v>
       </c>
       <c r="G6" t="n">
-        <v>10.1222670449898</v>
+        <v>1.810043680260149</v>
       </c>
       <c r="H6" t="n">
-        <v>38.34034347199599</v>
+        <v>1.827505798751567</v>
       </c>
       <c r="I6" t="n">
-        <v>10.12863176304792</v>
+        <v>1.81382242062285</v>
       </c>
       <c r="J6" t="n">
-        <v>10.66738193118129</v>
+        <v>6.805786124430771</v>
       </c>
       <c r="K6" t="n">
-        <v>10.10731004633627</v>
+        <v>1.797256576884313</v>
       </c>
       <c r="L6" t="n">
-        <v>10.13680822637281</v>
+        <v>1.824445877156914</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04897935696914396</v>
+        <v>0.01174019370595974</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08672891164771326</v>
+        <v>0.04644690908812455</v>
       </c>
       <c r="D7" t="n">
-        <v>0.07592735357400046</v>
+        <v>0.03868869827266132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08662337114418692</v>
+        <v>0.04642833760936167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08662337114417711</v>
+        <v>0.04642833760936167</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08036494512479175</v>
+        <v>0.04266892026060754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09723068115846432</v>
+        <v>0.05999151789533541</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08672966318282953</v>
+        <v>0.0464476606233078</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1124050352216592</v>
+        <v>0.07516587195856921</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06748687083378911</v>
+        <v>0.03024770757059353</v>
       </c>
       <c r="L7" t="n">
-        <v>0.09418301232511818</v>
+        <v>0.05694384906190555</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.06374680842669653</v>
+        <v>0.01433926514840792</v>
       </c>
       <c r="C8" t="n">
-        <v>0.126180518003224</v>
+        <v>0.05339039176907204</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1206132321268543</v>
+        <v>0.04655341285533714</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1194136384357153</v>
+        <v>0.05219942462139778</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1022192476589818</v>
+        <v>0.04917321186109476</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1199119958823222</v>
+        <v>0.04962920115622137</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1367777319160523</v>
+        <v>0.06695179879095081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1262767139404771</v>
+        <v>0.05340794151892169</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1519569558518239</v>
+        <v>0.08212700995175465</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08179402851488599</v>
+        <v>0.03276576730882705</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1596144265613083</v>
+        <v>0.06845977790508624</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1328564665728597</v>
+        <v>0.02650256491622304</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2005040484905503</v>
+        <v>0.06647133306396304</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1897031151874335</v>
+        <v>0.05871323220810687</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2350056870246197</v>
+        <v>0.07254362506280715</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2005040025978476</v>
+        <v>0.06647132863659908</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1941400819676277</v>
+        <v>0.062693344236446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2110058180013596</v>
+        <v>0.08001594187117395</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2005048000257439</v>
+        <v>0.06647208459914626</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2261801720646424</v>
+        <v>0.09519029593440771</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1632361591883602</v>
+        <v>0.04709958222968654</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2079581491679639</v>
+        <v>0.07696827303774391</v>
       </c>
     </row>
   </sheetData>
@@ -6851,31 +6851,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0171654562491565</v>
+        <v>0.01716545624915651</v>
       </c>
       <c r="C2" t="n">
-        <v>0.232894986523114</v>
+        <v>0.2328949865231142</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03783095702799948</v>
+        <v>0.03783095702799952</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2422392691590552</v>
+        <v>0.2422392691590551</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2135013094081039</v>
+        <v>0.2135013094081041</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04879606439428329</v>
+        <v>0.04879606439428327</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08695911824166642</v>
+        <v>0.08695911824166645</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04450754432649595</v>
+        <v>0.04450754432649597</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2721844017136911</v>
+        <v>0.2721844017136908</v>
       </c>
       <c r="K2" t="n">
         <v>0.1989204749192157</v>
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02551597397807915</v>
+        <v>0.02551597397807916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2453505163704238</v>
+        <v>0.245350516370424</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04928558071933837</v>
+        <v>0.04928558071933842</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2546971673256193</v>
+        <v>0.2546971673256192</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2259592075746682</v>
+        <v>0.2259592075746683</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06189772560571274</v>
+        <v>0.06189772560571279</v>
       </c>
       <c r="H3" t="n">
         <v>0.1057931102627871</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05696494564424147</v>
+        <v>0.05696494564424148</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2860984864015232</v>
+        <v>0.2860984864015231</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2082284955472555</v>
+        <v>0.2082284955472556</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09260238440415768</v>
+        <v>0.09260238440415762</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0215054823621233</v>
+        <v>0.006058230163947435</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04035107264275063</v>
+        <v>0.02276942422745956</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03379024690359619</v>
+        <v>0.01834299470542046</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04069365078928489</v>
+        <v>0.02282972241259544</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04069365078928489</v>
+        <v>0.02282972241259544</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04084400469993633</v>
+        <v>0.02495552843641788</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06298634252446096</v>
+        <v>0.04753909032628494</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04133103633068372</v>
+        <v>0.02294144231920383</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04352377391803417</v>
+        <v>0.0280765217198582</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02529488188838046</v>
+        <v>0.009847629690204507</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05617319685221992</v>
+        <v>0.04072594465404398</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.09713683885767446</v>
+        <v>0.01936934883503676</v>
       </c>
       <c r="C5" t="n">
-        <v>1.484349930605574</v>
+        <v>0.2769132218518115</v>
       </c>
       <c r="D5" t="n">
-        <v>1.11976400066378</v>
+        <v>0.2094743743315473</v>
       </c>
       <c r="E5" t="n">
-        <v>1.484349935983818</v>
+        <v>0.2769132272300552</v>
       </c>
       <c r="F5" t="n">
-        <v>1.484349935983818</v>
+        <v>0.2769132272300552</v>
       </c>
       <c r="G5" t="n">
-        <v>1.729626528250451</v>
+        <v>0.3221812509707604</v>
       </c>
       <c r="H5" t="n">
-        <v>3.994805866872452</v>
+        <v>0.7395393228618564</v>
       </c>
       <c r="I5" t="n">
-        <v>1.484349377794414</v>
+        <v>0.2769126690406507</v>
       </c>
       <c r="J5" t="n">
-        <v>2.126554172890452</v>
+        <v>0.3946898699524706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.40356646065348</v>
+        <v>0.07642342719211424</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4582744092037633</v>
+        <v>0.6702522991913475</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.07363804942559</v>
+        <v>1.775233552380657</v>
       </c>
       <c r="C6" t="n">
-        <v>10.09351766837001</v>
+        <v>1.792126735488011</v>
       </c>
       <c r="D6" t="n">
-        <v>38.27896224172663</v>
+        <v>1.787421044941238</v>
       </c>
       <c r="E6" t="n">
-        <v>6.229776612334615</v>
+        <v>1.112108317742203</v>
       </c>
       <c r="F6" t="n">
-        <v>10.09385162690556</v>
+        <v>1.79218551662162</v>
       </c>
       <c r="G6" t="n">
-        <v>10.09297657176341</v>
+        <v>6.756026029195684</v>
       </c>
       <c r="H6" t="n">
-        <v>38.31113632404928</v>
+        <v>6.779213450598364</v>
       </c>
       <c r="I6" t="n">
-        <v>10.09346360339417</v>
+        <v>1.792116764535915</v>
       </c>
       <c r="J6" t="n">
-        <v>10.60769143380518</v>
+        <v>6.759571804174092</v>
       </c>
       <c r="K6" t="n">
-        <v>10.07532722247885</v>
+        <v>1.778653312049667</v>
       </c>
       <c r="L6" t="n">
-        <v>10.10938373610766</v>
+        <v>1.810090989975511</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03402053226823216</v>
+        <v>0.008260878935487289</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05384663904795368</v>
+        <v>0.02514464390190494</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04630487328357828</v>
+        <v>0.02054556893636246</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05369077461507444</v>
+        <v>0.0251172161935394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05369077461507444</v>
+        <v>0.0251172161935394</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05335905460604539</v>
+        <v>0.02715817720795773</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07550139243056966</v>
+        <v>0.04974173909782487</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05384608623679248</v>
+        <v>0.02514409109074371</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05603882382414298</v>
+        <v>0.03027917049139809</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03780993179448873</v>
+        <v>0.01205027846174437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0686882467583288</v>
+        <v>0.04292859342558386</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04481382690902732</v>
+        <v>0.01016049878197393</v>
       </c>
       <c r="C8" t="n">
-        <v>0.08227090297046527</v>
+        <v>0.0301473143251932</v>
       </c>
       <c r="D8" t="n">
-        <v>0.07856073255708133</v>
+        <v>0.02622260013773726</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07742472193599725</v>
+        <v>0.02929439089938735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06511068408628178</v>
+        <v>0.02712712024958102</v>
       </c>
       <c r="G8" t="n">
-        <v>0.08192849146534631</v>
+        <v>0.03218639806794887</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1040708292898794</v>
+        <v>0.05476995995781742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.08241552309609404</v>
+        <v>0.03017231195073487</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08461175418202596</v>
+        <v>0.03530800620713621</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04827302546916394</v>
+        <v>0.01389178293850879</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1158263505608234</v>
+        <v>0.05122489964986868</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.08560130342633598</v>
+        <v>0.0173390946101224</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1244445353817</v>
+        <v>0.03756987358931689</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1169031807983529</v>
+        <v>0.03297087099163497</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1463898202571371</v>
+        <v>0.04143224813813776</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1244444859058581</v>
+        <v>0.03756986931324137</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1239569509397912</v>
+        <v>0.03958340689536972</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1460992887643155</v>
+        <v>0.06216696878523673</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1244439825705387</v>
+        <v>0.03756932077815565</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1266367201578887</v>
+        <v>0.04270440017881002</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09738922592315639</v>
+        <v>0.02245755546478094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1392861430920745</v>
+        <v>0.05535382311299584</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01979780953691525</v>
+        <v>0.01979780953691412</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2902892411082121</v>
+        <v>0.2902892411082114</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03723350507847945</v>
+        <v>0.03723350507848224</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2999209842714098</v>
+        <v>0.2999209842714059</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2703831544718847</v>
+        <v>0.2703831544718832</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0640291248920655</v>
+        <v>0.06402912489206319</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05112020846397689</v>
+        <v>0.05112020846397512</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09977642088296755</v>
+        <v>0.09977642088296704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3980916122419031</v>
+        <v>0.3980916122419038</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2809170973757859</v>
+        <v>0.2809170973757862</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03389987926884144</v>
+        <v>0.03389987926884063</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02861498416513083</v>
+        <v>0.02861498416513087</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3111213514093112</v>
+        <v>0.3111213514093075</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04866964583138014</v>
+        <v>0.04866964583137794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3207532259940349</v>
+        <v>0.3207532259940344</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2912153961945102</v>
+        <v>0.2912153961945107</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07949015931292641</v>
+        <v>0.07949015931292773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06464420488770954</v>
+        <v>0.0646442048877085</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1206376489252582</v>
+        <v>0.1206376489252603</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4304871745553579</v>
+        <v>0.430487174555355</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3020645772868696</v>
+        <v>0.3020645772868688</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04483711331032617</v>
+        <v>0.0448371133103252</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.037879354707144</v>
+        <v>0.01021665349633829</v>
       </c>
       <c r="C4" t="n">
-        <v>0.09073919508489049</v>
+        <v>0.05870172398365237</v>
       </c>
       <c r="D4" t="n">
-        <v>0.04824413689351206</v>
+        <v>0.02058143568270302</v>
       </c>
       <c r="E4" t="n">
-        <v>0.09114184793027214</v>
+        <v>0.05877259162064785</v>
       </c>
       <c r="F4" t="n">
-        <v>0.09114184793027212</v>
+        <v>0.05877259162064814</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06478920982131579</v>
+        <v>0.03661874961262702</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0565025877415895</v>
+        <v>0.02883988653078432</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08952240485235932</v>
+        <v>0.05849159202270553</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1311928383600248</v>
+        <v>0.1035301371492208</v>
       </c>
       <c r="K4" t="n">
-        <v>0.08667759128751083</v>
+        <v>0.05901489007670448</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04627127783230382</v>
+        <v>0.01860857662149577</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1440040171969295</v>
+        <v>0.0288945939933327</v>
       </c>
       <c r="C5" t="n">
-        <v>4.490515401268781</v>
+        <v>0.8330623320760563</v>
       </c>
       <c r="D5" t="n">
-        <v>1.101147230691622</v>
+        <v>0.2058923791870102</v>
       </c>
       <c r="E5" t="n">
-        <v>4.490515402162712</v>
+        <v>0.8330623329699891</v>
       </c>
       <c r="F5" t="n">
-        <v>4.490515402162711</v>
+        <v>0.8330623329699891</v>
       </c>
       <c r="G5" t="n">
-        <v>2.671857954206036</v>
+        <v>0.4954628461380425</v>
       </c>
       <c r="H5" t="n">
-        <v>2.027778671522045</v>
+        <v>0.3757844753962024</v>
       </c>
       <c r="I5" t="n">
-        <v>4.490520283694525</v>
+        <v>0.8330672145018028</v>
       </c>
       <c r="J5" t="n">
-        <v>9.78305581856066</v>
+        <v>1.802258012459806</v>
       </c>
       <c r="K5" t="n">
-        <v>4.746697997053396</v>
+        <v>0.879178477047353</v>
       </c>
       <c r="L5" t="n">
-        <v>1.115913815719406</v>
+        <v>0.2068656622695433</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.8397143046792</v>
+        <v>1.911339594389983</v>
       </c>
       <c r="C6" t="n">
-        <v>10.89343485557895</v>
+        <v>1.959976149928346</v>
       </c>
       <c r="D6" t="n">
-        <v>10.84453300861987</v>
+        <v>1.920728266810403</v>
       </c>
       <c r="E6" t="n">
-        <v>6.745964900828096</v>
+        <v>1.230021442584137</v>
       </c>
       <c r="F6" t="n">
-        <v>10.89098752674338</v>
+        <v>1.959545420792224</v>
       </c>
       <c r="G6" t="n">
-        <v>41.12518369410985</v>
+        <v>7.263248139689163</v>
       </c>
       <c r="H6" t="n">
-        <v>41.11974809813611</v>
+        <v>7.255971057199251</v>
       </c>
       <c r="I6" t="n">
-        <v>10.89135735482441</v>
+        <v>7.285120982099244</v>
       </c>
       <c r="J6" t="n">
-        <v>41.19381727286034</v>
+        <v>7.330551998460899</v>
       </c>
       <c r="K6" t="n">
-        <v>10.89059262669691</v>
+        <v>1.960503926005337</v>
       </c>
       <c r="L6" t="n">
-        <v>10.8461341847273</v>
+        <v>1.919384437935466</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05749495565261895</v>
+        <v>0.01366899924403183</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1091331233720897</v>
+        <v>0.0619390553446496</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06785885268049274</v>
+        <v>0.02403362564250322</v>
       </c>
       <c r="E7" t="n">
-        <v>0.109191279856385</v>
+        <v>0.06194929162243225</v>
       </c>
       <c r="F7" t="n">
-        <v>0.109191279856385</v>
+        <v>0.06194929162243225</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08440481076679077</v>
+        <v>0.04007109536032279</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07611818868706442</v>
+        <v>0.03229223227847746</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1091380057978343</v>
+        <v>0.06194393777040136</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1508084393054997</v>
+        <v>0.1069824828969156</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1062931922329858</v>
+        <v>0.06246723582439561</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06588687877777873</v>
+        <v>0.02206092236919295</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07298162937072261</v>
+        <v>0.01639465380364402</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1516848916281778</v>
+        <v>0.06942816651724384</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1159489072806228</v>
+        <v>0.03249747520627434</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1442930866011891</v>
+        <v>0.06812720957603602</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1255109785907876</v>
+        <v>0.06482155858412254</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1268946897006671</v>
+        <v>0.04754931401217229</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1186080676209459</v>
+        <v>0.03977045093031818</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1516278847317106</v>
+        <v>0.06942215642223962</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1933036251010992</v>
+        <v>0.1144616355564134</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1212782675542548</v>
+        <v>0.06510460906665197</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1365838634920232</v>
+        <v>0.03450359161147552</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1580863190562921</v>
+        <v>0.03137307910714612</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2450138251809556</v>
+        <v>0.08585405873342655</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2037404763519325</v>
+        <v>0.04794879127908773</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2857370111002071</v>
+        <v>0.09302134015297769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2450138289395682</v>
+        <v>0.08585406013153291</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2202855125756565</v>
+        <v>0.06398609874910186</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2119988904959303</v>
+        <v>0.05620723566724937</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2450187076067</v>
+        <v>0.0858589411591734</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2866891411143657</v>
+        <v>0.1308974862856905</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2208975756087151</v>
+        <v>0.08278360844725265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2017675805866445</v>
+        <v>0.04597592575796301</v>
       </c>
     </row>
   </sheetData>
@@ -7643,22 +7643,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01805102996540171</v>
+        <v>0.01805102996540172</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2616236947793209</v>
+        <v>0.2616236947793208</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03517267742589585</v>
+        <v>0.0351726774258959</v>
       </c>
       <c r="E2" t="n">
         <v>0.2711579484458367</v>
       </c>
       <c r="F2" t="n">
-        <v>0.241897344675012</v>
+        <v>0.2418973446750119</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06092888369975986</v>
+        <v>0.06092888369975989</v>
       </c>
       <c r="H2" t="n">
         <v>0.1664322782000052</v>
@@ -7667,13 +7667,13 @@
         <v>0.07216705778848111</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3503291536759158</v>
+        <v>0.3503291536759161</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2362122262516457</v>
+        <v>0.2362122262516456</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05798179796886438</v>
+        <v>0.0579817979688644</v>
       </c>
     </row>
     <row r="3">
@@ -7689,31 +7689,31 @@
         <v>0.2782996423863848</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04629271403518358</v>
+        <v>0.0462927140351836</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2878357480733751</v>
+        <v>0.2878357480733749</v>
       </c>
       <c r="F3" t="n">
-        <v>0.25857514430255</v>
+        <v>0.2585751443025498</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07591768663218328</v>
+        <v>0.07591768663218332</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1972669718658003</v>
+        <v>0.1972669718658002</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08885635358578163</v>
+        <v>0.08885635358578164</v>
       </c>
       <c r="J3" t="n">
         <v>0.3757568609472631</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2509399052191099</v>
+        <v>0.25093990521911</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07252838202691754</v>
+        <v>0.07252838202691758</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0295074236801087</v>
+        <v>0.007866892241961252</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06536186008892959</v>
+        <v>0.04068816477993921</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03968551758962694</v>
+        <v>0.01804498615147921</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06573090770834265</v>
+        <v>0.04075312010758896</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06573090770834268</v>
+        <v>0.04075312010758896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05556220723836486</v>
+        <v>0.03345552548445853</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1176897584001715</v>
+        <v>0.09604922696202428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06544694259326249</v>
+        <v>0.04070441678960659</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0963093465917544</v>
+        <v>0.0746688151536065</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05396307043629087</v>
+        <v>0.03232253899814326</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05324700219323267</v>
+        <v>0.03160647075508453</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0810260643948322</v>
+        <v>0.01693417295862067</v>
       </c>
       <c r="C5" t="n">
-        <v>2.77996815083794</v>
+        <v>0.5184588693629141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.921711442624069</v>
+        <v>0.1732815481163757</v>
       </c>
       <c r="E5" t="n">
-        <v>2.779968154414373</v>
+        <v>0.5184588729393528</v>
       </c>
       <c r="F5" t="n">
-        <v>2.779968154414373</v>
+        <v>0.5184588729393528</v>
       </c>
       <c r="G5" t="n">
-        <v>2.292881252505222</v>
+        <v>0.4272236753177521</v>
       </c>
       <c r="H5" t="n">
-        <v>8.143510215278251</v>
+        <v>1.508593619718544</v>
       </c>
       <c r="I5" t="n">
-        <v>2.779969701188648</v>
+        <v>0.5184604197136238</v>
       </c>
       <c r="J5" t="n">
-        <v>6.517378975908291</v>
+        <v>1.204777063789708</v>
       </c>
       <c r="K5" t="n">
-        <v>2.121663760063472</v>
+        <v>0.3962378584006137</v>
       </c>
       <c r="L5" t="n">
-        <v>2.540658736486067</v>
+        <v>0.0537993778017588</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10.08920613993305</v>
+        <v>6.740625487866248</v>
       </c>
       <c r="C6" t="n">
-        <v>10.12556655634856</v>
+        <v>1.811284181727477</v>
       </c>
       <c r="D6" t="n">
-        <v>10.09572917618887</v>
+        <v>1.787908660474754</v>
       </c>
       <c r="E6" t="n">
-        <v>6.261318678766679</v>
+        <v>1.131176561905283</v>
       </c>
       <c r="F6" t="n">
-        <v>10.12490290685652</v>
+        <v>1.811167382364495</v>
       </c>
       <c r="G6" t="n">
-        <v>38.30987261693402</v>
+        <v>1.803962489951301</v>
       </c>
       <c r="H6" t="n">
-        <v>38.37670571986784</v>
+        <v>6.829635999693698</v>
       </c>
       <c r="I6" t="n">
-        <v>38.31975735228894</v>
+        <v>6.773463012413888</v>
       </c>
       <c r="J6" t="n">
-        <v>38.35305351397606</v>
+        <v>1.935382348682194</v>
       </c>
       <c r="K6" t="n">
-        <v>10.11270265990492</v>
+        <v>1.802660697151861</v>
       </c>
       <c r="L6" t="n">
-        <v>10.11239919243518</v>
+        <v>1.802017246644512</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04581665681596014</v>
+        <v>0.01073731725831749</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08175462537840505</v>
+        <v>0.04357329145525349</v>
       </c>
       <c r="D7" t="n">
-        <v>0.05599412392165876</v>
+        <v>0.02091530085036369</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08170178024686273</v>
+        <v>0.0435639936591375</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08170178024686274</v>
+        <v>0.0435639936591375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07187144037421718</v>
+        <v>0.03632595050081477</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1339989915360238</v>
+        <v>0.09891965197838051</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08175617572911437</v>
+        <v>0.04357484180596282</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1126185797276059</v>
+        <v>0.07753924016996271</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07027230357214302</v>
+        <v>0.03519296401449948</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06955623532908355</v>
+        <v>0.03447689577144075</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0594328330429972</v>
+        <v>0.01313376426129065</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1182123881584652</v>
+        <v>0.04998985766983517</v>
       </c>
       <c r="D8" t="n">
-        <v>0.09724367704039026</v>
+        <v>0.02817522215992186</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1119577938707192</v>
+        <v>0.04888905202808184</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09606513437557679</v>
+        <v>0.04609194397209316</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1083746013161086</v>
+        <v>0.04275050679177562</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1705021524779949</v>
+        <v>0.1053442082693554</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1182593366710063</v>
+        <v>0.04999939809692369</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1491262385860745</v>
+        <v>0.08396458809423692</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08346334231062717</v>
+        <v>0.03751458681989295</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1299667655547415</v>
+        <v>0.04510914903354468</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.119786578652694</v>
+        <v>0.02375602343103947</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1823773828401358</v>
+        <v>0.06128289667255674</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1566174488190456</v>
+        <v>0.03862500593634212</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2131340097452245</v>
+        <v>0.06669606592550562</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1823772822696625</v>
+        <v>0.0612828819191386</v>
       </c>
       <c r="G9" t="n">
-        <v>0.172494197835948</v>
+        <v>0.05403555571811808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2346217489977537</v>
+        <v>0.1166292571956838</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1823789331908451</v>
+        <v>0.06128444702326609</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2132413371893362</v>
+        <v>0.09524884538726605</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1554522784289741</v>
+        <v>0.04699589272026025</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1701789927908145</v>
+        <v>0.05218650098874406</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Ammonia/ammonia ionising radiation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0204504813673337</v>
+        <v>0.05281605903878067</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2792562633614045</v>
+        <v>0.2146983751643948</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03772069616208687</v>
+        <v>0.05372495614201913</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2888788523773536</v>
+        <v>0.222742896669805</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2593524352641873</v>
+        <v>0.1981659996308526</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06368369368207943</v>
+        <v>0.05509133713482981</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0543815501562765</v>
+        <v>0.05458120103296979</v>
       </c>
       <c r="I2" t="n">
-        <v>0.08906029851959898</v>
+        <v>0.05642734389430149</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3694541633057867</v>
+        <v>0.2434696783317295</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2755936800224033</v>
+        <v>0.2057019784851689</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0280131279038507</v>
+        <v>0.05317903924610821</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02938604579229082</v>
+        <v>0.02460740457325459</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2984983999705683</v>
+        <v>0.3115606567199884</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04925037032047403</v>
+        <v>0.0310786434762853</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3081214902438657</v>
+        <v>0.324823384662034</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2785950731306989</v>
+        <v>0.2842547225391923</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07911319568719917</v>
+        <v>0.04082600003730675</v>
       </c>
       <c r="H3" t="n">
-        <v>0.06841613004813073</v>
+        <v>0.03738767176358291</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1083259672318312</v>
+        <v>0.05028936616175839</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3976238490446661</v>
+        <v>0.3763046577404752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2959887432644338</v>
+        <v>0.2989303979150117</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03808675392722099</v>
+        <v>0.02744351687733085</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01045831254482059</v>
+        <v>0.01045831254482078</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05209750074859888</v>
+        <v>0.05209750074859884</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02072472343922376</v>
+        <v>0.02072472343922379</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05218238499887263</v>
+        <v>0.05218238499887266</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05218238499887268</v>
+        <v>0.05218238499887269</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03626347823342767</v>
+        <v>0.03626347823342776</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03063145745416019</v>
+        <v>0.03063145745416017</v>
       </c>
       <c r="I4" t="n">
         <v>0.05194933703032473</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08657899088653009</v>
+        <v>0.08657899088653012</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05581025814060087</v>
+        <v>0.05581025814060086</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01496410006008264</v>
+        <v>0.01496410006008265</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03916241339422008</v>
+        <v>0.03916241339422161</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8066488549544567</v>
+        <v>0.8066488549544586</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2366309993991049</v>
+        <v>0.2366309993991056</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8066488561148208</v>
+        <v>0.8066488561148217</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8066488561148208</v>
+        <v>0.8066488561148217</v>
       </c>
       <c r="G5" t="n">
         <v>0.5448236548711061</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4778880786918653</v>
+        <v>0.4778880786918643</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8066523251349041</v>
+        <v>0.8066523251349048</v>
       </c>
       <c r="J5" t="n">
-        <v>1.581369162756336</v>
+        <v>1.581369162756337</v>
       </c>
       <c r="K5" t="n">
-        <v>0.910078683342016</v>
+        <v>0.9100786833420168</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1455880312207565</v>
+        <v>0.1447862087725537</v>
       </c>
     </row>
     <row r="6">
@@ -675,13 +675,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.041816786034997</v>
+        <v>2.041816786034998</v>
       </c>
       <c r="C6" t="n">
-        <v>2.083477149525573</v>
+        <v>2.083477149525574</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051113842043242</v>
+        <v>2.051113817684984</v>
       </c>
       <c r="E6" t="n">
         <v>1.303412383421295</v>
@@ -690,22 +690,22 @@
         <v>2.083167075928157</v>
       </c>
       <c r="G6" t="n">
-        <v>7.759036211281905</v>
+        <v>7.759036211281911</v>
       </c>
       <c r="H6" t="n">
-        <v>7.753995027464672</v>
+        <v>7.753995027464667</v>
       </c>
       <c r="I6" t="n">
-        <v>2.083307810520501</v>
+        <v>7.774722070078809</v>
       </c>
       <c r="J6" t="n">
-        <v>2.221319483169363</v>
+        <v>7.809793347752276</v>
       </c>
       <c r="K6" t="n">
-        <v>2.087478299133202</v>
+        <v>2.087478299133199</v>
       </c>
       <c r="L6" t="n">
-        <v>2.04591517179918</v>
+        <v>2.045915171799181</v>
       </c>
     </row>
     <row r="7">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01414429418526006</v>
+        <v>0.01414429418526</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05563184849031712</v>
+        <v>0.05563184849031714</v>
       </c>
       <c r="D7" t="n">
         <v>0.02441054864808326</v>
@@ -727,25 +727,25 @@
         <v>0.05564496034812405</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05564496034812405</v>
+        <v>0.05564496034812408</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03994945987386699</v>
+        <v>0.03994945987386697</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03431743909459951</v>
+        <v>0.03431743909459944</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05563531867076399</v>
+        <v>0.05563531867076401</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09026497252696944</v>
+        <v>0.09026497252696941</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05949623978104011</v>
+        <v>0.05949623978104013</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01865008170052192</v>
+        <v>0.01865008170052193</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01712855321498783</v>
+        <v>0.0171285532149878</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06379291294518488</v>
+        <v>0.06379291294530057</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0336286421385079</v>
+        <v>0.03362864213850787</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06237938132892344</v>
+        <v>0.06237938132892341</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05878768482922064</v>
+        <v>0.05878768482922069</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04809679870265599</v>
+        <v>0.04809679870265597</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04246477792338996</v>
+        <v>0.04246477792338988</v>
       </c>
       <c r="I8" t="n">
-        <v>0.063782657499553</v>
+        <v>0.06378265749955306</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09841332604025339</v>
+        <v>0.09841332604025342</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06238459195350262</v>
+        <v>0.06238459195350263</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03219068910112254</v>
+        <v>0.03219068910112251</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03506552584772512</v>
+        <v>0.03506552584772501</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08376088262259473</v>
+        <v>0.08376088262259475</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05253974643291686</v>
+        <v>0.05253974643291679</v>
       </c>
       <c r="E9" t="n">
         <v>0.09207854070275275</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08376088312065404</v>
+        <v>0.08376088312065399</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06807849400614457</v>
+        <v>0.0680784940061446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06244647322687707</v>
+        <v>0.06244647322687701</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08376435280304158</v>
+        <v>0.08376435280304162</v>
       </c>
       <c r="J9" t="n">
         <v>0.118394006659247</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08344904789219816</v>
+        <v>0.07854936214411144</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04677911583279956</v>
+        <v>0.04677911583279949</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01711413321033775</v>
+        <v>0.05074594911150737</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2233676659040609</v>
+        <v>0.2082535752130411</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07224772224656122</v>
+        <v>0.05364752039835595</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2328500307302167</v>
+        <v>0.2161759362550037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2037343120374213</v>
+        <v>0.191940894352004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06223669115787813</v>
+        <v>0.05312065971566791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1069044713167771</v>
+        <v>0.05548306134496601</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03525257268746397</v>
+        <v>0.05170046969791797</v>
       </c>
       <c r="J2" t="n">
-        <v>0.305559724367489</v>
+        <v>0.2363025912653332</v>
       </c>
       <c r="K2" t="n">
-        <v>0.204996147765117</v>
+        <v>0.1974034640884806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05556651812838231</v>
+        <v>0.05275639618337474</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0255354210802301</v>
+        <v>0.02240669646625519</v>
       </c>
       <c r="C3" t="n">
-        <v>0.234509311159119</v>
+        <v>0.2876263071507316</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08895046936044915</v>
+        <v>0.04297964292592538</v>
       </c>
       <c r="E3" t="n">
-        <v>0.243995643647625</v>
+        <v>0.3006759914179798</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2148799249548293</v>
+        <v>0.2606716222783153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07743570982962111</v>
+        <v>0.03928144322956396</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1288130469607661</v>
+        <v>0.05614994320747617</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04638307401961898</v>
+        <v>0.02917930302739458</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3244867978351554</v>
+        <v>0.3488929351660976</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2152917444085534</v>
+        <v>0.2680583434616159</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06976433264200325</v>
+        <v>0.03689920256557198</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005866446728956277</v>
+        <v>0.005866446728956331</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01685443331979749</v>
+        <v>0.0168544333197975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03864102920264863</v>
+        <v>0.03864102920264861</v>
       </c>
       <c r="E4" t="n">
+        <v>0.01693309220289491</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.0169330922028949</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.01693309220289492</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.03277590361771764</v>
+        <v>0.03277590361771768</v>
       </c>
       <c r="H4" t="n">
         <v>0.05923303472231566</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01722058440244156</v>
+        <v>0.01722058440244157</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04744399078012391</v>
+        <v>0.04744399078012384</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01328418382936232</v>
+        <v>0.01328418382936233</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02872810562682727</v>
+        <v>0.02872810562682728</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01345060197441662</v>
+        <v>0.01345060197441657</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1840661080355475</v>
+        <v>0.1840661080355476</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5227936276391723</v>
+        <v>0.522793627639172</v>
       </c>
       <c r="E5" t="n">
         <v>0.1840661156857015</v>
@@ -1046,22 +1046,22 @@
         <v>0.1840661156857015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4497701450683661</v>
+        <v>0.4497701450683654</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9630259474827794</v>
+        <v>0.9630259474827799</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1840624562521266</v>
+        <v>0.1840624562521264</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7468602615571674</v>
+        <v>0.7468602615571688</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1258177659538777</v>
+        <v>0.1258177659538775</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4493366841190557</v>
+        <v>0.4493366841190563</v>
       </c>
     </row>
     <row r="6">
@@ -1071,31 +1071,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.737666210050508</v>
+        <v>1.775330943116088</v>
       </c>
       <c r="C6" t="n">
         <v>1.786270314257632</v>
       </c>
       <c r="D6" t="n">
-        <v>6.770618213909938</v>
+        <v>6.770618213909937</v>
       </c>
       <c r="E6" t="n">
-        <v>1.106235900330734</v>
+        <v>1.106235900330732</v>
       </c>
       <c r="F6" t="n">
-        <v>1.786625951947174</v>
+        <v>1.786625951947176</v>
       </c>
       <c r="G6" t="n">
-        <v>1.802240400004849</v>
+        <v>6.76457566693927</v>
       </c>
       <c r="H6" t="n">
-        <v>6.791763542585402</v>
+        <v>6.791763542585405</v>
       </c>
       <c r="I6" t="n">
         <v>1.786685080789572</v>
       </c>
       <c r="J6" t="n">
-        <v>6.779714477256269</v>
+        <v>1.907086706600375</v>
       </c>
       <c r="K6" t="n">
         <v>1.78229271941591</v>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008447042066590129</v>
+        <v>0.008447042066590141</v>
       </c>
       <c r="C7" t="n">
         <v>0.01980483152349646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04122156533080017</v>
+        <v>0.04122156533080015</v>
       </c>
       <c r="E7" t="n">
         <v>0.01976504989574101</v>
@@ -1126,19 +1126,19 @@
         <v>0.01976504989574101</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03535649895535149</v>
+        <v>0.03535649895535155</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06181363005994953</v>
+        <v>0.06181363005994951</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01980117974007543</v>
+        <v>0.01980117974007545</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05002458611775772</v>
+        <v>0.05002458611775773</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01586477916699617</v>
+        <v>0.01586477916699613</v>
       </c>
       <c r="L7" t="n">
         <v>0.03130870096446112</v>
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01090116981845191</v>
+        <v>0.01090116981845189</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02606504058163105</v>
+        <v>0.02606504058166822</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04831601709462713</v>
+        <v>0.04831601709462712</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02501789376964373</v>
+        <v>0.02501789376964374</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02235709351705704</v>
+        <v>0.02235709351705705</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04165395280645441</v>
+        <v>0.04165395280645438</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06811108391106523</v>
+        <v>0.06811108391106531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02609863359117835</v>
+        <v>0.02609863359117834</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05632279528754851</v>
+        <v>0.05632279528754842</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01824751516382841</v>
+        <v>0.01824751516382844</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04162083029526861</v>
+        <v>0.04162083029526854</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01911162039559005</v>
+        <v>0.01911162039559009</v>
       </c>
       <c r="C9" t="n">
         <v>0.03441287278870132</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05582966601452691</v>
+        <v>0.05582966601452688</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03896353755700166</v>
+        <v>0.03896353755700165</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0344128678914297</v>
+        <v>0.03441286789142971</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04996454022055637</v>
+        <v>0.04996454022055635</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07642167132515446</v>
+        <v>0.07642167132515439</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0344092210052803</v>
+        <v>0.03440922100528029</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06463262738296266</v>
+        <v>0.06463262738296253</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0281879626077115</v>
+        <v>0.02818796260771145</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04591674222966603</v>
+        <v>0.04591674222966597</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1566001831979551</v>
+        <v>0.1436808362891242</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1715253167236707</v>
+        <v>0.1878938257795089</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1307801959985866</v>
+        <v>0.1423219816454466</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2320939308811285</v>
+        <v>0.2095239861144814</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2320939308811285</v>
+        <v>0.2095239769010055</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1385670302167366</v>
+        <v>0.1427317872644495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1473607138615694</v>
+        <v>0.143188325558563</v>
       </c>
       <c r="I2" t="n">
-        <v>0.152740271942168</v>
+        <v>0.1434780767326242</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1879748465577754</v>
+        <v>0.1573030519428574</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1821616226897013</v>
+        <v>0.1679393014130293</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1184182088510317</v>
+        <v>0.1416503180812263</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1762073619980795</v>
+        <v>0.163422769839544</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1850011073997386</v>
+        <v>0.2246525011221368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1465090281245708</v>
+        <v>0.1537143950153086</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2511224077168733</v>
+        <v>0.2709777539186409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2511224077168733</v>
+        <v>0.2709777447051649</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1554655005132921</v>
+        <v>0.1566515842529247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1655817387868919</v>
+        <v>0.1600255062110063</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1717846700361552</v>
+        <v>0.1619571203267502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2099886594622377</v>
+        <v>0.1905576548180482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2011943762385074</v>
+        <v>0.2023377546754492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1322913738472779</v>
+        <v>0.1491011195235413</v>
       </c>
     </row>
     <row r="4">
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03705371910639654</v>
+        <v>0.03705371910639652</v>
       </c>
       <c r="C4" t="n">
         <v>0.01239664516810084</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02170483080203831</v>
+        <v>0.02170483080203833</v>
       </c>
       <c r="E4" t="n">
         <v>0.03538379879164207</v>
@@ -1408,16 +1408,16 @@
         <v>0.03155958114309246</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03528059939226184</v>
+        <v>0.03528059939226183</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04657817918193401</v>
+        <v>0.046578179181934</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03478038209903817</v>
+        <v>0.03478038209903814</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01436214986268504</v>
+        <v>0.01436214986268506</v>
       </c>
     </row>
     <row r="5">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5689832798848778</v>
+        <v>0.5689832798848787</v>
       </c>
       <c r="C5" t="n">
         <v>0.1213159676516535</v>
@@ -1436,28 +1436,28 @@
         <v>0.2776695561780035</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5167139362205161</v>
+        <v>0.5167139362205154</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5167139362205161</v>
+        <v>0.5167139362205154</v>
       </c>
       <c r="G5" t="n">
-        <v>0.370702006296569</v>
+        <v>0.3707020062965682</v>
       </c>
       <c r="H5" t="n">
-        <v>0.510643972560855</v>
+        <v>0.5106439725608547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5167158862801451</v>
+        <v>0.5167158862801439</v>
       </c>
       <c r="J5" t="n">
-        <v>0.758753754419876</v>
+        <v>0.7587537544198752</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5136053070959261</v>
+        <v>0.5136053070959252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1671291836892642</v>
+        <v>0.1671291836892641</v>
       </c>
     </row>
     <row r="6">
@@ -1467,34 +1467,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.905219390284192</v>
+        <v>7.143840164653845</v>
       </c>
       <c r="C6" t="n">
-        <v>1.88035461046824</v>
+        <v>1.880354610468241</v>
       </c>
       <c r="D6" t="n">
-        <v>1.88957813171646</v>
+        <v>1.889578126619456</v>
       </c>
       <c r="E6" t="n">
         <v>1.185628655815902</v>
       </c>
       <c r="F6" t="n">
-        <v>1.903453034810751</v>
+        <v>1.903453034810752</v>
       </c>
       <c r="G6" t="n">
-        <v>7.133197718491179</v>
+        <v>1.894576944121538</v>
       </c>
       <c r="H6" t="n">
-        <v>7.139194350179357</v>
+        <v>7.139194350179353</v>
       </c>
       <c r="I6" t="n">
-        <v>7.142067044939697</v>
+        <v>1.903446270570057</v>
       </c>
       <c r="J6" t="n">
-        <v>7.153861890474687</v>
+        <v>7.15386189047469</v>
       </c>
       <c r="K6" t="n">
-        <v>1.903091797187614</v>
+        <v>1.903091797187616</v>
       </c>
       <c r="L6" t="n">
         <v>1.882396410240654</v>
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03990049650451413</v>
+        <v>0.03990049650451415</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01563672784116875</v>
+        <v>0.01563672784116874</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02455153215267127</v>
+        <v>0.02455153215267129</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03813273016678276</v>
+        <v>0.03813273016678274</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03813273016678276</v>
+        <v>0.03813273016678274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02925805034186011</v>
+        <v>0.02925805034186013</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03440635854121005</v>
+        <v>0.03440635854121003</v>
       </c>
       <c r="I7" t="n">
         <v>0.03812737679037945</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04942495658005164</v>
+        <v>0.0494249565800516</v>
       </c>
       <c r="K7" t="n">
         <v>0.03762715949715576</v>
@@ -1547,22 +1547,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04228015477453225</v>
+        <v>0.04228015477453224</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02212554538568726</v>
+        <v>0.02212554538568727</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03188298506924674</v>
+        <v>0.03188298506924678</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04349173803835851</v>
+        <v>0.04349173803835849</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04063949176983994</v>
+        <v>0.04063949176983993</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03573899811546449</v>
+        <v>0.03573899811546456</v>
       </c>
       <c r="H8" t="n">
         <v>0.04088730631483446</v>
@@ -1571,13 +1571,13 @@
         <v>0.04460832456398388</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05590671036686342</v>
+        <v>0.05590671036686339</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03993063420969598</v>
+        <v>0.039930634209696</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02797401485805462</v>
+        <v>0.02797401485805466</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05221421111262518</v>
+        <v>0.0522142111126252</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03248285147979052</v>
+        <v>0.03248285147979051</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04139773736609559</v>
+        <v>0.0413977373660956</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06020185862290674</v>
+        <v>0.06020185862290678</v>
       </c>
       <c r="F9" t="n">
         <v>0.05497154984004508</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04610417398048186</v>
+        <v>0.04610417398048185</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05125248217983183</v>
+        <v>0.05125248217983186</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0549735004290012</v>
+        <v>0.05497350042900118</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06627108021867342</v>
+        <v>0.06627108021867344</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0518471898681243</v>
+        <v>0.05184718986812424</v>
       </c>
       <c r="L9" t="n">
         <v>0.03405505089942439</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1319203604330617</v>
+        <v>0.1395165209271445</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1669019833755745</v>
+        <v>0.1861955145728773</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1300741534405139</v>
+        <v>0.1394193587199891</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2066471411232798</v>
+        <v>0.2062580748412107</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2066471411232798</v>
+        <v>0.2062580601548897</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1253932985494856</v>
+        <v>0.1391730146240009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.138262564178701</v>
+        <v>0.1398496625201453</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1260923106839598</v>
+        <v>0.1392100332569564</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1675901010912765</v>
+        <v>0.1543718052934508</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1573346206694217</v>
+        <v>0.1644656538749742</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1125274242891995</v>
+        <v>0.1384823690891003</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1480611763161609</v>
+        <v>0.1516402928266306</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1796543047533085</v>
+        <v>0.2222027687531175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1459376558341046</v>
+        <v>0.1509306984262632</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2219132016071393</v>
+        <v>0.2601192248849177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2219132016071393</v>
+        <v>0.2601192101985964</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1405537030732525</v>
+        <v>0.1491890401585999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.155357182848282</v>
+        <v>0.1540860413015714</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1413651247669768</v>
+        <v>0.1494443618220662</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1865887115517576</v>
+        <v>0.18167000771668</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1727443635445497</v>
+        <v>0.1914062536685993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1257560077425998</v>
+        <v>0.1443717310253963</v>
       </c>
     </row>
     <row r="4">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02229566482425931</v>
+        <v>0.02229566482425933</v>
       </c>
       <c r="C4" t="n">
         <v>0.008576949365356301</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02119817299761604</v>
+        <v>0.02119817299761605</v>
       </c>
       <c r="E4" t="n">
         <v>0.01930507073282422</v>
@@ -1798,22 +1798,22 @@
         <v>0.01930507073282422</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0184886482394699</v>
+        <v>0.01848864823946991</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02606315995668542</v>
+        <v>0.02606315995668545</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01932049937010218</v>
+        <v>0.0193204993701022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03360563101616954</v>
+        <v>0.03360563101616958</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01940238093695289</v>
+        <v>0.01940238093695291</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01077122162303006</v>
+        <v>0.01077122162303009</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3120919819314835</v>
+        <v>0.3120919819314838</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07703966611532602</v>
+        <v>0.0770396661153262</v>
       </c>
       <c r="D5" t="n">
         <v>0.2843153870209972</v>
       </c>
       <c r="E5" t="n">
-        <v>0.246937094570857</v>
+        <v>0.2469370945708571</v>
       </c>
       <c r="F5" t="n">
-        <v>0.246937094570857</v>
+        <v>0.2469370945708571</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2437309278595788</v>
+        <v>0.2437309278595795</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4127484510373057</v>
+        <v>0.4127484510373059</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2469372191318753</v>
+        <v>0.2469372191318755</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5198675231416201</v>
+        <v>0.5198675231416202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2547831394019975</v>
+        <v>0.2547831394019977</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1222817034157056</v>
+        <v>0.1222817034157058</v>
       </c>
     </row>
     <row r="6">
@@ -1863,34 +1863,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.752599349756163</v>
+        <v>6.752599349756164</v>
       </c>
       <c r="C6" t="n">
-        <v>1.777440446935832</v>
+        <v>1.777440446935831</v>
       </c>
       <c r="D6" t="n">
-        <v>6.751584657428262</v>
+        <v>6.751584657428268</v>
       </c>
       <c r="E6" t="n">
-        <v>1.108185768942863</v>
+        <v>1.108185768942862</v>
       </c>
       <c r="F6" t="n">
         <v>1.788223725618657</v>
       </c>
       <c r="G6" t="n">
-        <v>1.787410772556509</v>
+        <v>6.748792333171367</v>
       </c>
       <c r="H6" t="n">
-        <v>6.757123733874687</v>
+        <v>6.757123733874685</v>
       </c>
       <c r="I6" t="n">
-        <v>1.78824262368714</v>
+        <v>1.788242623687138</v>
       </c>
       <c r="J6" t="n">
-        <v>1.892576669493823</v>
+        <v>1.89257666949382</v>
       </c>
       <c r="K6" t="n">
-        <v>1.788308739446629</v>
+        <v>1.788308739446628</v>
       </c>
       <c r="L6" t="n">
         <v>1.779631803975628</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02434356438618387</v>
+        <v>0.02434356438618391</v>
       </c>
       <c r="C7" t="n">
         <v>0.01093459663477718</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02324600538102055</v>
+        <v>0.02324600538102059</v>
       </c>
       <c r="E7" t="n">
         <v>0.02136610331845873</v>
@@ -1918,19 +1918,19 @@
         <v>0.02136610331845873</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02053654780139446</v>
+        <v>0.02053654780139448</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02811105951861005</v>
+        <v>0.02811105951861002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02136839893202674</v>
+        <v>0.02136839893202675</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0356535305780941</v>
+        <v>0.03565353057809417</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02145028049887742</v>
+        <v>0.02145028049887746</v>
       </c>
       <c r="L7" t="n">
         <v>0.01281912118495464</v>
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02615172730008475</v>
+        <v>0.02615172730008471</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01578808815533924</v>
+        <v>0.01578808815526087</v>
       </c>
       <c r="D8" t="n">
         <v>0.02873272503225022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02538865184181411</v>
+        <v>0.02538865184181406</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02327175886861865</v>
+        <v>0.02327175886861864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02539144091915211</v>
+        <v>0.02539144091915212</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03296595263638971</v>
+        <v>0.03296595263638979</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02622329204978436</v>
+        <v>0.02622329204978438</v>
       </c>
       <c r="J8" t="n">
-        <v>0.04050902245937647</v>
+        <v>0.04050902245937642</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02320184883559827</v>
+        <v>0.02320184883559838</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02085657875831528</v>
+        <v>0.0208565787583153</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03203618420609763</v>
+        <v>0.03203618420609768</v>
       </c>
       <c r="C9" t="n">
         <v>0.02158069018337476</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0338921689692171</v>
+        <v>0.03389216896921713</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0354226136213726</v>
+        <v>0.03542261362137261</v>
       </c>
       <c r="F9" t="n">
         <v>0.03201436556462117</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03118264134999202</v>
+        <v>0.03118264134999206</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03875715306720762</v>
+        <v>0.03875715306720761</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03201449248062429</v>
+        <v>0.03201449248062432</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0462996241266916</v>
+        <v>0.04629962412669173</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03038512097324795</v>
+        <v>0.03038512097324798</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02346521473355219</v>
+        <v>0.02346521473355225</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1165129739287129</v>
+        <v>0.1380095999779861</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1636536742041841</v>
+        <v>0.1850493322574388</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1320489369022645</v>
+        <v>0.1388272268523764</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1900506355109539</v>
+        <v>0.2042502645692883</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1900506355109539</v>
+        <v>0.204250244626598</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1182121068987683</v>
+        <v>0.1380990219714503</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1310733038932073</v>
+        <v>0.1387774724885093</v>
       </c>
       <c r="I2" t="n">
-        <v>0.110059798562803</v>
+        <v>0.1376701123018704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1564703881643142</v>
+        <v>0.1524492261481283</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1409159180874042</v>
+        <v>0.1623793939828282</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1074276467874091</v>
+        <v>0.1375209283536089</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1302427509679246</v>
+        <v>0.1457466200268941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1758767330683789</v>
+        <v>0.2205142216242967</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1481123266525436</v>
+        <v>0.1515611387645114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2028114708714501</v>
+        <v>0.253224201963405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2028114708714502</v>
+        <v>0.2532241820207146</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1321971058578229</v>
+        <v>0.1463838526027302</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1469909492927336</v>
+        <v>0.1512670029944093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1228203378826262</v>
+        <v>0.1433216537646501</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1738255391067983</v>
+        <v>0.1765608712802064</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1538640645666664</v>
+        <v>0.1844671198162784</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1197932869903032</v>
+        <v>0.142339372573392</v>
       </c>
     </row>
     <row r="4">
@@ -2182,34 +2182,34 @@
         <v>0.01211863948833552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005931852891996006</v>
+        <v>0.00593185289199596</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02135411116151729</v>
+        <v>0.02135411116151738</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008637942881690803</v>
+        <v>0.008637942881690753</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008637942881690803</v>
+        <v>0.008637942881690758</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0131989203239516</v>
+        <v>0.01319892032395166</v>
       </c>
       <c r="H4" t="n">
         <v>0.0207714141429022</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008751389548753791</v>
+        <v>0.008751389548753772</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02646636643958718</v>
+        <v>0.02646636643958675</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009025269769755677</v>
+        <v>0.009025269769755807</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006720824168870246</v>
+        <v>0.006720824168870257</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1541483258380569</v>
+        <v>0.1541483258380568</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04960511243277193</v>
+        <v>0.04960511243277117</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3066490176657636</v>
+        <v>0.3066490176657545</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08574454645259125</v>
+        <v>0.08574454645259103</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08574454645259125</v>
+        <v>0.08574454645259103</v>
       </c>
       <c r="G5" t="n">
-        <v>0.171577043284808</v>
+        <v>0.1715770432848085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.333763837593932</v>
+        <v>0.3337638375939319</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08574347177495738</v>
+        <v>0.08574347177495699</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4131498883590649</v>
+        <v>0.4131498883590679</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0974611956233734</v>
+        <v>0.09746119562337477</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06601993286254861</v>
+        <v>0.06601993286254852</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.780637009698385</v>
+        <v>1.780637009698386</v>
       </c>
       <c r="C6" t="n">
-        <v>1.774445928802274</v>
+        <v>1.774445928802275</v>
       </c>
       <c r="D6" t="n">
-        <v>1.790155321483815</v>
+        <v>1.790155316074383</v>
       </c>
       <c r="E6" t="n">
-        <v>1.097115511928609</v>
+        <v>1.097115511928608</v>
       </c>
       <c r="F6" t="n">
         <v>1.777234875751854</v>
       </c>
       <c r="G6" t="n">
-        <v>6.742686627778166</v>
+        <v>6.742686627778162</v>
       </c>
       <c r="H6" t="n">
-        <v>6.750965256820642</v>
+        <v>6.750965256820641</v>
       </c>
       <c r="I6" t="n">
-        <v>6.738239097002964</v>
+        <v>6.738239097002976</v>
       </c>
       <c r="J6" t="n">
-        <v>6.756396807921613</v>
+        <v>6.756396807921612</v>
       </c>
       <c r="K6" t="n">
-        <v>1.777420668654951</v>
+        <v>1.777420668654959</v>
       </c>
       <c r="L6" t="n">
-        <v>1.775213659526592</v>
+        <v>1.775213659526593</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01369550115470133</v>
+        <v>0.01369550115470132</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00773246876840919</v>
+        <v>0.007732468768409089</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02293090048544168</v>
+        <v>0.02293090048544136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01031357939966153</v>
+        <v>0.01031357939966148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01031357939966153</v>
+        <v>0.01031357939966148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01477578199031742</v>
+        <v>0.01477578199031748</v>
       </c>
       <c r="H7" t="n">
         <v>0.02234827580926802</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01032825121511959</v>
+        <v>0.0103282512151196</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0280432281059531</v>
+        <v>0.02804322810595258</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01060213143612155</v>
+        <v>0.01060213143612163</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008297685835236088</v>
+        <v>0.00829768583523607</v>
       </c>
     </row>
     <row r="8">
@@ -2339,22 +2339,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01516713341211529</v>
+        <v>0.01516713341211528</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01159605550042001</v>
+        <v>0.01159605550048766</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02730804604678853</v>
+        <v>0.02730804604678851</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01353628992418293</v>
+        <v>0.01353628992418294</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01186788845485683</v>
+        <v>0.01186788845485686</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01865386248997513</v>
+        <v>0.0186538624899753</v>
       </c>
       <c r="H8" t="n">
         <v>0.02622635630895332</v>
@@ -2363,13 +2363,13 @@
         <v>0.01420633171477746</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03192178153677587</v>
+        <v>0.03192178153677568</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01202906268240429</v>
+        <v>0.0120290626824044</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01468950274336678</v>
+        <v>0.01468950274336676</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01906413846253194</v>
+        <v>0.01906413846253212</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0152262561567699</v>
+        <v>0.01522625615677012</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03042476182375048</v>
+        <v>0.03042476182375058</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02027548885308155</v>
+        <v>0.0202754888530816</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01782311007018943</v>
+        <v>0.01782311007018946</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02226956937867838</v>
+        <v>0.02226956937867854</v>
       </c>
       <c r="H9" t="n">
         <v>0.02984206319762909</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01782203860348075</v>
+        <v>0.01782203860348065</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03553701549431366</v>
+        <v>0.03553701549431362</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0154199751185161</v>
+        <v>0.0168146429399645</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01579147322359723</v>
+        <v>0.01579147322359712</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1518247071237616</v>
+        <v>0.1407358286884038</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1687342331557411</v>
+        <v>0.1875273748556359</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1288246460718294</v>
+        <v>0.1395253811570412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2275366762364747</v>
+        <v>0.2089829807603862</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2275366762364747</v>
+        <v>0.2089829722593713</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1346451218396618</v>
+        <v>0.1398317012363062</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1819540429151091</v>
+        <v>0.142337823218478</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1451154207802513</v>
+        <v>0.1403830721037047</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1870641291073303</v>
+        <v>0.1570992124612353</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1763581673636977</v>
+        <v>0.1671877552825347</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1087628737235984</v>
+        <v>0.1384443692684749</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1712151954256983</v>
+        <v>0.1582844195574591</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1818146756960965</v>
+        <v>0.2234282716156251</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1447603607676824</v>
+        <v>0.1496338267412929</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2459203516806756</v>
+        <v>0.2689869904345643</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2459203516806756</v>
+        <v>0.2689869819335493</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1514551136086125</v>
+        <v>0.1518336929225964</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2058711328434675</v>
+        <v>0.1697552135995485</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1635119381056908</v>
+        <v>0.1557505080944301</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2089528965002594</v>
+        <v>0.1901198500428224</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1945868567136895</v>
+        <v>0.1996945335436249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1216866423491495</v>
+        <v>0.1421130860690435</v>
       </c>
     </row>
     <row r="4">
@@ -2578,34 +2578,34 @@
         <v>0.03601008743637744</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01062384245425457</v>
+        <v>0.01062384245425472</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02233752573626336</v>
+        <v>0.02233752573626261</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03259030752101775</v>
+        <v>0.03259030752101746</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03259030752101775</v>
+        <v>0.03259030752101746</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02587357649177108</v>
+        <v>0.02587357649177036</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05391012617825327</v>
+        <v>0.05391012617825294</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03253273460038496</v>
+        <v>0.03253273460038468</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04589724037616997</v>
+        <v>0.04589724037616965</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03141216882729116</v>
+        <v>0.03141216882729088</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0104189466154203</v>
+        <v>0.01041894661541993</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5535749114634243</v>
+        <v>0.5535749114634223</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09299385646158403</v>
+        <v>0.09299385646142469</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2927000025434721</v>
+        <v>0.292700002543467</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4709975254932022</v>
+        <v>0.4709975254931988</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4709975254932022</v>
+        <v>0.4709975254931988</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3646574634048997</v>
+        <v>0.3646574634048955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9652547035355171</v>
+        <v>0.9652547035355169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4709989699210069</v>
+        <v>0.4709989699210033</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7498682545191451</v>
+        <v>0.7498682545191453</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4568356685103547</v>
+        <v>0.4568356685103546</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09043649541580064</v>
+        <v>0.09043649541579976</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.904098493198748</v>
+        <v>1.904098493198749</v>
       </c>
       <c r="C6" t="n">
         <v>1.878496304308208</v>
       </c>
       <c r="D6" t="n">
-        <v>1.890191280501387</v>
+        <v>1.890191284604096</v>
       </c>
       <c r="E6" t="n">
-        <v>1.182742017669178</v>
+        <v>1.182742017669176</v>
       </c>
       <c r="F6" t="n">
-        <v>1.900611877680746</v>
+        <v>1.900611877680745</v>
       </c>
       <c r="G6" t="n">
-        <v>1.893961982254143</v>
+        <v>1.893961982254141</v>
       </c>
       <c r="H6" t="n">
-        <v>7.161540400353755</v>
+        <v>7.161540400353768</v>
       </c>
       <c r="I6" t="n">
-        <v>1.900621140362757</v>
+        <v>7.139196445257922</v>
       </c>
       <c r="J6" t="n">
-        <v>7.153075030726552</v>
+        <v>2.009082858826294</v>
       </c>
       <c r="K6" t="n">
-        <v>1.899569939721662</v>
+        <v>1.899569939721661</v>
       </c>
       <c r="L6" t="n">
-        <v>1.878359239355195</v>
+        <v>1.878359239355194</v>
       </c>
     </row>
     <row r="7">
@@ -2698,34 +2698,34 @@
         <v>0.03882064919887877</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01384976764887031</v>
+        <v>0.01384976764886997</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02514801539042274</v>
+        <v>0.02514801539042229</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03534325308219777</v>
+        <v>0.0353432530821973</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03534325308219777</v>
+        <v>0.0353432530821973</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02868413825427217</v>
+        <v>0.0286841382542717</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05672068794075463</v>
+        <v>0.05672068794075435</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03534329636288652</v>
+        <v>0.03534329636288602</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04870780213867153</v>
+        <v>0.04870780213867099</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03422273058979249</v>
+        <v>0.03422273058979221</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01322950837792159</v>
+        <v>0.01322950837792127</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04118402711230806</v>
+        <v>0.04118402711230784</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02028329234133392</v>
+        <v>0.02028329234143524</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03242290628643493</v>
+        <v>0.03242290628643418</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04066259199204728</v>
+        <v>0.04066259199204697</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03783505579724084</v>
+        <v>0.0378350557972402</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03511544541328053</v>
+        <v>0.03511544541327974</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06315199509978577</v>
+        <v>0.0631519950997854</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04177460352189444</v>
+        <v>0.04177460352189409</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05513990875456192</v>
+        <v>0.05513990875456161</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03651054462967017</v>
+        <v>0.03651054462966985</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02391010778147848</v>
+        <v>0.02391010778147807</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05080364623132044</v>
+        <v>0.05080364623131949</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03026369978747645</v>
+        <v>0.03026369978747556</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04156201970881093</v>
+        <v>0.04156201970880971</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05686898136595673</v>
+        <v>0.05686898136595534</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05175577772662642</v>
+        <v>0.05175577772662546</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04509807039287851</v>
+        <v>0.04509807039287729</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07313462007936074</v>
+        <v>0.07313462007935992</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05175722850149287</v>
+        <v>0.05175722850149164</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06512173427727699</v>
+        <v>0.06512173427727661</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04505732449210189</v>
+        <v>0.04806936155630868</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02964344051652763</v>
+        <v>0.02964344051652689</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1231021163761727</v>
+        <v>0.1351864179340257</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1629107837316668</v>
+        <v>0.1857609533439978</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1270263742676085</v>
+        <v>0.135392943832648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1996617849833867</v>
+        <v>0.2054868522324847</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1996617849833867</v>
+        <v>0.2054868402916271</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1201299141470952</v>
+        <v>0.1350299968339786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2199854202349797</v>
+        <v>0.1403355328460227</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1146677759952288</v>
+        <v>0.134742698377938</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1603920366016442</v>
+        <v>0.1539009050704105</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1493674167087273</v>
+        <v>0.1634473982267688</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1001244285302181</v>
+        <v>0.1339583721132143</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1386713185084597</v>
+        <v>0.1434794166621348</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1751144218665164</v>
+        <v>0.2205188548552463</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1431850279911842</v>
+        <v>0.1449350628420477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2139645541880534</v>
+        <v>0.2570832200100877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2139645541880534</v>
+        <v>0.2570832080692297</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1352526702551838</v>
+        <v>0.1423627520800683</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2501066601869796</v>
+        <v>0.1801168739572833</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1289728861754244</v>
+        <v>0.1403072471829507</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1783353957131663</v>
+        <v>0.1789476986025908</v>
       </c>
       <c r="K3" t="n">
-        <v>0.163704021340708</v>
+        <v>0.1877525700877754</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1122431713012426</v>
+        <v>0.1348436615274745</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01976163016818124</v>
+        <v>0.01976163016818128</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0060628408239823</v>
+        <v>0.006062840823982305</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02209443519972748</v>
+        <v>0.02209443519972746</v>
       </c>
       <c r="E4" t="n">
         <v>0.01515179859742495</v>
@@ -2986,22 +2986,22 @@
         <v>0.01515179859742495</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01806509560610292</v>
+        <v>0.01806509560610291</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07733186658218226</v>
+        <v>0.07733186658218236</v>
       </c>
       <c r="I4" t="n">
         <v>0.01521801860090017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02915755924648326</v>
+        <v>0.0291575592464833</v>
       </c>
       <c r="K4" t="n">
         <v>0.01488352025537268</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006107850838933454</v>
+        <v>0.006107850838933462</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2710040672294025</v>
+        <v>0.271004067229403</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03775109033464191</v>
+        <v>0.03775109033464192</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3027596158606508</v>
+        <v>0.302759615860651</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1800699924198093</v>
+        <v>0.1800699924198091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1800699924198093</v>
+        <v>0.1800699924198091</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2396799651312075</v>
+        <v>0.2396799651312062</v>
       </c>
       <c r="H5" t="n">
-        <v>1.397682199123571</v>
+        <v>1.39768219912357</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1800692747967145</v>
+        <v>0.1800692747967146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4438496388693531</v>
+        <v>0.443849638869353</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1808915719423259</v>
+        <v>0.1808915719423253</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03504011873104652</v>
+        <v>0.03504011873104655</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.788591326163125</v>
+        <v>1.788591326163127</v>
       </c>
       <c r="C6" t="n">
         <v>1.774843429140964</v>
       </c>
       <c r="D6" t="n">
-        <v>1.791035726358124</v>
+        <v>6.752495929491246</v>
       </c>
       <c r="E6" t="n">
         <v>1.103885766974776</v>
       </c>
       <c r="F6" t="n">
-        <v>1.784012115953952</v>
+        <v>1.784012115953953</v>
       </c>
       <c r="G6" t="n">
-        <v>6.748320180484805</v>
+        <v>1.786894791601048</v>
       </c>
       <c r="H6" t="n">
-        <v>6.809200430024006</v>
+        <v>6.809200430024012</v>
       </c>
       <c r="I6" t="n">
-        <v>6.745473103479599</v>
+        <v>6.745473103479606</v>
       </c>
       <c r="J6" t="n">
-        <v>1.888026060674082</v>
+        <v>6.759931983494837</v>
       </c>
       <c r="K6" t="n">
-        <v>1.783592014314606</v>
+        <v>1.783592014314607</v>
       </c>
       <c r="L6" t="n">
-        <v>1.774862632834322</v>
+        <v>1.774862632834323</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02187826274591451</v>
+        <v>0.02187826274591453</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008561122164545054</v>
+        <v>0.00856112216454505</v>
       </c>
       <c r="D7" t="n">
         <v>0.0242110211544451</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01733141808479157</v>
+        <v>0.01733141808479156</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01733141808479157</v>
+        <v>0.01733141808479156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02018172818383619</v>
+        <v>0.02018172818383621</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07944849915991566</v>
+        <v>0.07944849915991552</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01733465117863347</v>
+        <v>0.01733465117863346</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03127419182421653</v>
+        <v>0.03127419182421656</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01700015283310596</v>
+        <v>0.01700015283310597</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008224483416666747</v>
+        <v>0.008224483416666754</v>
       </c>
     </row>
     <row r="8">
@@ -3131,16 +3131,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02379226422805625</v>
+        <v>0.02379226422805628</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0136735653564689</v>
+        <v>0.01367356535639065</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0299904725613052</v>
+        <v>0.02999047256130519</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02157254588369866</v>
+        <v>0.02157254588369865</v>
       </c>
       <c r="F8" t="n">
         <v>0.0193485252630377</v>
@@ -3149,16 +3149,16 @@
         <v>0.02529727225600057</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08456404323228432</v>
+        <v>0.08456404323228442</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02245019525079783</v>
+        <v>0.02245019525079786</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03639036508426659</v>
+        <v>0.03639036508426661</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01885468401857266</v>
+        <v>0.01885468401857267</v>
       </c>
       <c r="L8" t="n">
         <v>0.01668430642628105</v>
@@ -3171,34 +3171,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02918835290961296</v>
+        <v>0.02918835290961298</v>
       </c>
       <c r="C9" t="n">
         <v>0.01875701970938131</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03440695646086008</v>
+        <v>0.03440695646086009</v>
       </c>
       <c r="E9" t="n">
         <v>0.03086140035880803</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02753125154173369</v>
+        <v>0.0275312515417337</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03037762572867247</v>
+        <v>0.03037762572867249</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08964439670475183</v>
+        <v>0.08964439670475186</v>
       </c>
       <c r="I9" t="n">
         <v>0.02753054872346974</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04147008936905283</v>
+        <v>0.04147008936905284</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02356230606698796</v>
+        <v>0.0255239985207855</v>
       </c>
       <c r="L9" t="n">
         <v>0.01842038096150304</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.104961615597386</v>
+        <v>0.1311442780659153</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1603977254514751</v>
+        <v>0.1847344005448989</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1227852677045759</v>
+        <v>0.1320823014756923</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1864026694935282</v>
+        <v>0.2038377042649967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1864026694935282</v>
+        <v>0.2038376899974067</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1076398314344801</v>
+        <v>0.1312852272460565</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1818304338483859</v>
+        <v>0.1352282249018053</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09867004028987829</v>
+        <v>0.1308132784392819</v>
       </c>
       <c r="J2" t="n">
-        <v>0.141005250959218</v>
+        <v>0.1516225070422605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1356465936661824</v>
+        <v>0.1617900787396571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09472844419184152</v>
+        <v>0.1305939707188783</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1182091759058458</v>
+        <v>0.1335000650997541</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1722056859901767</v>
+        <v>0.2192117274100929</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1387100679875249</v>
+        <v>0.1401741870103721</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1987055141128833</v>
+        <v>0.251677054219188</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1987055141128833</v>
+        <v>0.2516770399515981</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1212896789092432</v>
+        <v>0.1345049602140584</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2066239164318762</v>
+        <v>0.1625503764288466</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1109690786510448</v>
+        <v>0.1311370389874921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1560873702287945</v>
+        <v>0.1708361068355516</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1479108259116998</v>
+        <v>0.1821953630544569</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1064392992593294</v>
+        <v>0.1296500958225889</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009880022434257516</v>
+        <v>0.0098800224342578</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003761230028049847</v>
+        <v>0.003761230028049852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02047542835977582</v>
+        <v>0.02047542835977605</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006408234082052664</v>
+        <v>0.006408234082052671</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006408234082052663</v>
+        <v>0.006408234082052672</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01154132712958575</v>
+        <v>0.01154132712958626</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0555582961973521</v>
+        <v>0.0555582961973519</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006602150244301115</v>
+        <v>0.006602150244301039</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01714044625600884</v>
+        <v>0.01714044625600903</v>
       </c>
       <c r="K4" t="n">
-        <v>0.005988417615823621</v>
+        <v>0.00598841761582361</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003800284599576052</v>
+        <v>0.003800284599575912</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1165403219316718</v>
+        <v>0.116540321931672</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01686524249459577</v>
+        <v>0.01686524249459576</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2932632053067398</v>
+        <v>0.2932632053067399</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05053094665395864</v>
+        <v>0.05053094665395885</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05053094665395864</v>
+        <v>0.05053094665395885</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1442156690130629</v>
+        <v>0.1442156690130631</v>
       </c>
       <c r="H5" t="n">
-        <v>1.001362649353191</v>
+        <v>1.001362649353192</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05052975580256087</v>
+        <v>0.05052975580256103</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2483130554583723</v>
+        <v>0.2483130554583715</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04719359663658841</v>
+        <v>0.04719359663658881</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01086615076380219</v>
+        <v>0.01086615076380221</v>
       </c>
     </row>
     <row r="6">
@@ -3447,7 +3447,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739303506813136</v>
+        <v>6.739303506813126</v>
       </c>
       <c r="C6" t="n">
         <v>1.772350466841374</v>
@@ -3456,25 +3456,25 @@
         <v>1.789222888413735</v>
       </c>
       <c r="E6" t="n">
-        <v>1.094849763463063</v>
+        <v>1.094849763463062</v>
       </c>
       <c r="F6" t="n">
         <v>1.77501264396228</v>
       </c>
       <c r="G6" t="n">
-        <v>6.740964811508457</v>
+        <v>6.740964811508469</v>
       </c>
       <c r="H6" t="n">
-        <v>6.786904530354391</v>
+        <v>1.824298175278179</v>
       </c>
       <c r="I6" t="n">
-        <v>1.775051978999078</v>
+        <v>6.736025634623179</v>
       </c>
       <c r="J6" t="n">
-        <v>6.747110543593557</v>
+        <v>1.875601525052564</v>
       </c>
       <c r="K6" t="n">
-        <v>1.774255648194005</v>
+        <v>1.774255648193969</v>
       </c>
       <c r="L6" t="n">
         <v>1.772212375805203</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0114905244202731</v>
+        <v>0.01149052442027313</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005798230597531482</v>
+        <v>0.00579823059753149</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02208590899985871</v>
+        <v>0.02208590899985858</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00818006355645067</v>
+        <v>0.008180063556450672</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00818006355645067</v>
+        <v>0.008180063556450673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01315182911560124</v>
+        <v>0.01315182911560125</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05716879818336768</v>
+        <v>0.0571687981833675</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008212652230316721</v>
+        <v>0.008212652230316728</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0187509482420244</v>
+        <v>0.01875094824202446</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00759891960183918</v>
+        <v>0.007598919601838948</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005410786585591638</v>
+        <v>0.005410786585591436</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01308830410969039</v>
+        <v>0.01308830410969025</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009962114744267437</v>
+        <v>0.009962114744319375</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02682027651819466</v>
+        <v>0.02682027651819461</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01167060681917116</v>
+        <v>0.01167060681917115</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009873833144916465</v>
+        <v>0.009873833144916458</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01734748809425775</v>
+        <v>0.01734748809425768</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06136445716231014</v>
+        <v>0.06136445716231013</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01240831120897325</v>
+        <v>0.01240831120897324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02294711777119414</v>
+        <v>0.02294711777119401</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009148442350350592</v>
+        <v>0.009148442350350436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01232014770619969</v>
+        <v>0.0123201477061995</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01631089463980988</v>
+        <v>0.01631089463980989</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01264056773757101</v>
+        <v>0.01264056773757105</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02892826053790558</v>
+        <v>0.02892826053790524</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01738946652414955</v>
+        <v>0.01738946652414954</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01505616872538302</v>
+        <v>0.01505616872538303</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01999416625564079</v>
+        <v>0.01999416625564071</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06401113532340716</v>
+        <v>0.06401113532340724</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01505498937035633</v>
+        <v>0.0150549893703563</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02559328538206398</v>
+        <v>0.02559328538206392</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0132221877301854</v>
+        <v>0.01326971824499258</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0122531237256312</v>
+        <v>0.01225312372563114</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1486535319400621</v>
+        <v>0.1389093270834231</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1667146915468441</v>
+        <v>0.1869293637966171</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1326677245298251</v>
+        <v>0.1380680257897933</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2240556920799734</v>
+        <v>0.2086854499063055</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2240556920799735</v>
+        <v>0.2086854433419983</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1347744407432764</v>
+        <v>0.1381788980798321</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1799197986366342</v>
+        <v>0.1405692565580535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.13965361783965</v>
+        <v>0.1384359685789946</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2006533077927776</v>
+        <v>0.1579552666804541</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1760848979334919</v>
+        <v>0.1670161556565128</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1052384314991169</v>
+        <v>0.13659613867882</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1678974723665096</v>
+        <v>0.1549378604162769</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1795961896018983</v>
+        <v>0.2220112541957051</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1495104823947081</v>
+        <v>0.1489169860319089</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2419486061918195</v>
+        <v>0.267504447105756</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2419486061918192</v>
+        <v>0.267504440541449</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1519336424451261</v>
+        <v>0.1497261387466142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2038612065586009</v>
+        <v>0.1668341311364151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1575558859314914</v>
+        <v>0.1515450412814565</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2245662107527835</v>
+        <v>0.1953763308679589</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1943129093027827</v>
+        <v>0.1993599686906884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1179628080128916</v>
+        <v>0.1386282120148054</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03535563174397702</v>
+        <v>0.03535563174397727</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009737675013893891</v>
+        <v>0.009737675013889623</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02585274661471119</v>
+        <v>0.02585274661471082</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03051766819780687</v>
+        <v>0.03051766819780702</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03051766819780687</v>
+        <v>0.03051766819780704</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02717915534730916</v>
+        <v>0.027179155347309</v>
       </c>
       <c r="H4" t="n">
         <v>0.0539320359990069</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03050270621133697</v>
+        <v>0.03050270621133673</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05383344985720792</v>
+        <v>0.05383344985720769</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0313350057057163</v>
+        <v>0.03133500570571633</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009555426172240228</v>
+        <v>0.009555426172240505</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5424090235832199</v>
+        <v>0.5424090235832203</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07810064277671137</v>
+        <v>0.07810064277688929</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3564829378590224</v>
+        <v>0.3564829378590215</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4354612147990633</v>
+        <v>0.4354612147990624</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4354612147990633</v>
+        <v>0.4354612147990624</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3896394709569952</v>
+        <v>0.3896394709569964</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9667130491368433</v>
+        <v>0.9667130491368444</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4354618959877378</v>
+        <v>0.4354618959877379</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8999398181486733</v>
+        <v>0.8999398181486725</v>
       </c>
       <c r="K5" t="n">
-        <v>0.45634972153829</v>
+        <v>0.4563497215382932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07373873834775584</v>
+        <v>0.07373873834775604</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.9035003859843</v>
+        <v>1.903500385984301</v>
       </c>
       <c r="C6" t="n">
-        <v>1.877638655450752</v>
+        <v>1.877638655450762</v>
       </c>
       <c r="D6" t="n">
-        <v>1.893867451482707</v>
+        <v>1.893867451482709</v>
       </c>
       <c r="E6" t="n">
-        <v>1.180672842932284</v>
+        <v>1.180672842932283</v>
       </c>
       <c r="F6" t="n">
         <v>1.898622273676799</v>
       </c>
       <c r="G6" t="n">
-        <v>7.13394432955537</v>
+        <v>1.895323909587635</v>
       </c>
       <c r="H6" t="n">
         <v>7.161677068484738</v>
       </c>
       <c r="I6" t="n">
-        <v>7.13726788041939</v>
+        <v>1.898647460451663</v>
       </c>
       <c r="J6" t="n">
-        <v>7.161125739540484</v>
+        <v>2.017129188393661</v>
       </c>
       <c r="K6" t="n">
-        <v>1.89953278395473</v>
+        <v>1.899532783954711</v>
       </c>
       <c r="L6" t="n">
-        <v>1.877551018962964</v>
+        <v>1.877551018962962</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03822740130173136</v>
+        <v>0.03822740130173174</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01304815292964899</v>
+        <v>0.013048152929652</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02872444442337561</v>
+        <v>0.02872444442337524</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0333727216253687</v>
+        <v>0.0333727216253688</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0333727216253687</v>
+        <v>0.03337272162536881</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03005092490506348</v>
+        <v>0.03005092490506319</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05680380555676112</v>
+        <v>0.05680380555676132</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03337447576909125</v>
+        <v>0.03337447576909115</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05670521941496223</v>
+        <v>0.05670521941496202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03420677526347063</v>
+        <v>0.03420677526347048</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01242719572999458</v>
+        <v>0.01242719572999472</v>
       </c>
     </row>
     <row r="8">
@@ -3923,10 +3923,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04064394549367852</v>
+        <v>0.04064394549367862</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01961618453304381</v>
+        <v>0.01961618453294159</v>
       </c>
       <c r="D8" t="n">
         <v>0.0361535436195797</v>
@@ -3935,25 +3935,25 @@
         <v>0.03880640129480677</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03592134139473477</v>
+        <v>0.03592134139473486</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03661908727764564</v>
+        <v>0.03661908727764565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06337196792936825</v>
+        <v>0.06337196792936824</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03994263814167335</v>
+        <v>0.03994263814167359</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06327419769176001</v>
+        <v>0.06327419769176046</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03654620101692736</v>
+        <v>0.03654620101692677</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0233320704378009</v>
+        <v>0.02333207043780073</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0504890253565058</v>
+        <v>0.05048902535650612</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02983948934336253</v>
+        <v>0.02983948934336739</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04551585362484135</v>
+        <v>0.04551585362484115</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05539231577156518</v>
+        <v>0.05539231577156552</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05016512445149504</v>
+        <v>0.05016512445149549</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04684226131877701</v>
+        <v>0.0468422613187772</v>
       </c>
       <c r="H9" t="n">
         <v>0.07359514197047472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05016581218280476</v>
+        <v>0.05016581218280441</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07349655582867573</v>
+        <v>0.07349655582867533</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04837357898371929</v>
+        <v>0.04837357898371902</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02921853214370802</v>
+        <v>0.02921853214370881</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1063725113946572</v>
+        <v>0.1224904751126655</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1614870144628266</v>
+        <v>0.1845599617795874</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1175371984520745</v>
+        <v>0.1230780504176428</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1968739974936431</v>
+        <v>0.204386554093022</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1968739974936431</v>
+        <v>0.2043865418445479</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1063754419502966</v>
+        <v>0.1224906293419883</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1927521688452006</v>
+        <v>0.1270786953932721</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09795044591641064</v>
+        <v>0.1220473687456476</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1609169515822823</v>
+        <v>0.1536824384944548</v>
       </c>
       <c r="K2" t="n">
-        <v>0.147200618214052</v>
+        <v>0.162049778631497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08371549582193147</v>
+        <v>0.1212771473715471</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1216291556145929</v>
+        <v>0.1222466948919728</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1736179714847812</v>
+        <v>0.218721972623887</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1344708584885793</v>
+        <v>0.1264172505220725</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2108659589067681</v>
+        <v>0.2549953313037225</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2108659589067682</v>
+        <v>0.2549953190552484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.121632526360641</v>
+        <v>0.122246909439984</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2209833268089192</v>
+        <v>0.1549117324452637</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111942648450282</v>
+        <v>0.1190796274978545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1789108081471645</v>
+        <v>0.1790090271258112</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1613832654490067</v>
+        <v>0.1854748449428884</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09557001555619507</v>
+        <v>0.1137262818773561</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01857891309187835</v>
+        <v>0.01857891309187837</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005840233343893384</v>
+        <v>0.005840233343893382</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02521584645959135</v>
+        <v>0.02521584645959139</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01394002704063851</v>
+        <v>0.01394002704063855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01394002704063851</v>
+        <v>0.01394002704063855</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01864968956844076</v>
+        <v>0.01864968956844072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06990828737249578</v>
+        <v>0.06990828737249584</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01403355162477561</v>
+        <v>0.01403355162477565</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02941166479714061</v>
+        <v>0.02941166479714069</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01432847826829639</v>
+        <v>0.01432847826829636</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005116410102876407</v>
+        <v>0.005116410102876399</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.252678470488525</v>
+        <v>0.2526784704885252</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03606970162355629</v>
+        <v>0.03606970162355627</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3581451399325969</v>
+        <v>0.3581451399325977</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1622347158494996</v>
+        <v>0.1622347158495003</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1622347158494996</v>
+        <v>0.1622347158495003</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2523190688469782</v>
+        <v>0.252319068846978</v>
       </c>
       <c r="H5" t="n">
         <v>1.258228878025494</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1622335922538254</v>
+        <v>0.1622335922538263</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4508361690716065</v>
+        <v>0.450836169071609</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1737581196566144</v>
+        <v>0.1737581196566145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01838729932408904</v>
+        <v>0.01838729932408905</v>
       </c>
     </row>
     <row r="6">
@@ -4239,31 +4239,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.787369373155682</v>
+        <v>6.748766597740022</v>
       </c>
       <c r="C6" t="n">
-        <v>1.774564965023806</v>
+        <v>1.774564965023808</v>
       </c>
       <c r="D6" t="n">
-        <v>1.794220395556617</v>
+        <v>1.794220398815249</v>
       </c>
       <c r="E6" t="n">
-        <v>1.102629918807633</v>
+        <v>1.102629918807634</v>
       </c>
       <c r="F6" t="n">
-        <v>1.782783987476737</v>
+        <v>1.782783987476738</v>
       </c>
       <c r="G6" t="n">
         <v>1.787440149632245</v>
       </c>
       <c r="H6" t="n">
-        <v>6.801623809717209</v>
+        <v>6.80162380971721</v>
       </c>
       <c r="I6" t="n">
-        <v>6.744221236272899</v>
+        <v>6.744221236272914</v>
       </c>
       <c r="J6" t="n">
-        <v>6.760117266041101</v>
+        <v>1.888244288478707</v>
       </c>
       <c r="K6" t="n">
         <v>1.782977163339979</v>
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02064723577858242</v>
+        <v>0.02064723577858243</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008278458360108659</v>
+        <v>0.008278458360108668</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0272841197611609</v>
+        <v>0.02728411976116094</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01609559391843522</v>
+        <v>0.01609559391843524</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01609559391843522</v>
+        <v>0.01609559391843523</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0207180122551448</v>
+        <v>0.02071801225514478</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07197661005919974</v>
+        <v>0.07197661005919984</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01610187431147968</v>
+        <v>0.01610187431147971</v>
       </c>
       <c r="J7" t="n">
         <v>0.03147998748384467</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01639680095500045</v>
+        <v>0.01639680095500043</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007184732789580464</v>
+        <v>0.007184732789580452</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02252354900394641</v>
+        <v>0.0225235490039464</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01326430007839308</v>
+        <v>0.01326430007839307</v>
       </c>
       <c r="D8" t="n">
         <v>0.03292253623427251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02023733326081237</v>
+        <v>0.02023733326081246</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01807369433428936</v>
+        <v>0.01807369433428941</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0257102683011969</v>
+        <v>0.02571026830119688</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07696886610544409</v>
+        <v>0.07696886610544412</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0210941303575318</v>
+        <v>0.02109413035753184</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03647285589563673</v>
+        <v>0.03647285589563671</v>
       </c>
       <c r="K8" t="n">
         <v>0.01821523394329469</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01543185165688444</v>
+        <v>0.01543185165688441</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02810015228096378</v>
+        <v>0.02810015228096385</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01862984474499532</v>
+        <v>0.01862984474499537</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03763554879213286</v>
+        <v>0.03763554879213298</v>
       </c>
       <c r="E9" t="n">
         <v>0.02979913448192635</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02645437108797708</v>
+        <v>0.02645437108797711</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03106939864003148</v>
+        <v>0.03106939864003144</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08232799644408643</v>
+        <v>0.08232799644408653</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02645326069636634</v>
+        <v>0.02645326069636636</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04183137386873134</v>
+        <v>0.04183137386873152</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0250687996723765</v>
+        <v>0.02309849812938545</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01753611917446714</v>
+        <v>0.01753611917446713</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1071680622243524</v>
+        <v>0.1328066845206161</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1586929412085922</v>
+        <v>0.1831754591314401</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1333558559837777</v>
+        <v>0.1341848960930268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1853341050975687</v>
+        <v>0.2032588950251423</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1853341050975687</v>
+        <v>0.2032588751940088</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1123078274700491</v>
+        <v>0.1330771801571011</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1799629047795087</v>
+        <v>0.1366716444679718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1002554133716546</v>
+        <v>0.1324429635349033</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1407480130455159</v>
+        <v>0.1512715802159503</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1361316037465966</v>
+        <v>0.1610480018928633</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09680100327807997</v>
+        <v>0.1322470524881405</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.120346031231597</v>
+        <v>0.1363941626983889</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1704251412921879</v>
+        <v>0.216776586126822</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1504674188400704</v>
+        <v>0.1462032651046812</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1974739674303301</v>
+        <v>0.2506924360985603</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1974739674303301</v>
+        <v>0.2506924162674266</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1262578259633113</v>
+        <v>0.1383230742905133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2040747007776192</v>
+        <v>0.1639039862870334</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1123928565202019</v>
+        <v>0.1337979456350989</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1557533436056451</v>
+        <v>0.1703930501283391</v>
       </c>
       <c r="K3" t="n">
-        <v>0.14851341324278</v>
+        <v>0.1814792739013788</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1084223918389513</v>
+        <v>0.132492013837867</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009762135336627537</v>
+        <v>0.009762135336627533</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00371401977605562</v>
+        <v>0.003714019776055621</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02532966905565347</v>
+        <v>0.02532966905565345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005977735078666532</v>
+        <v>0.005977735078666526</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005977735078666532</v>
+        <v>0.005977735078666526</v>
       </c>
       <c r="G4" t="n">
         <v>0.01288571046178452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05302018158916838</v>
+        <v>0.05302018158916837</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006107627989892733</v>
+        <v>0.006107627989892729</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0169940748003992</v>
+        <v>0.01699407480039921</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006611266052763416</v>
+        <v>0.006611266052763433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003603486697059144</v>
+        <v>0.003603486697059156</v>
       </c>
     </row>
     <row r="5">
@@ -4595,34 +4595,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1177586940928089</v>
+        <v>0.1177586940928086</v>
       </c>
       <c r="C5" t="n">
         <v>0.01762539486654031</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3789682236034781</v>
+        <v>0.3789682236034766</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04538343216911972</v>
+        <v>0.04538343216911966</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04538343216911972</v>
+        <v>0.04538343216911966</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1710218859545838</v>
+        <v>0.1710218859545834</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9563846995877742</v>
+        <v>0.9563846995877717</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04538182153986801</v>
+        <v>0.04538182153986797</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2490567155538494</v>
+        <v>0.2490567155538493</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06102973185453145</v>
+        <v>0.06102973185453141</v>
       </c>
       <c r="L5" t="n">
         <v>0.01069866210074572</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.778143357731391</v>
+        <v>6.739075773942343</v>
       </c>
       <c r="C6" t="n">
         <v>1.772126648638815</v>
       </c>
       <c r="D6" t="n">
-        <v>1.794138336820591</v>
+        <v>1.794138329575179</v>
       </c>
       <c r="E6" t="n">
-        <v>1.094281221946766</v>
+        <v>1.094281221946765</v>
       </c>
       <c r="F6" t="n">
         <v>1.774448536454205</v>
       </c>
       <c r="G6" t="n">
-        <v>6.742199349067495</v>
+        <v>1.781266932856549</v>
       </c>
       <c r="H6" t="n">
-        <v>6.783899207313987</v>
+        <v>6.783899207313984</v>
       </c>
       <c r="I6" t="n">
-        <v>6.735421266595601</v>
+        <v>1.774488850384655</v>
       </c>
       <c r="J6" t="n">
-        <v>1.875366034578723</v>
+        <v>6.746810036268188</v>
       </c>
       <c r="K6" t="n">
-        <v>1.774814391913391</v>
+        <v>1.77481439191339</v>
       </c>
       <c r="L6" t="n">
-        <v>1.771950431809226</v>
+        <v>1.771950431809225</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01134271367916355</v>
+        <v>0.01134271367916358</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005622775578224167</v>
+        <v>0.005622775578224166</v>
       </c>
       <c r="D7" t="n">
         <v>0.02691020950871685</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007678829048092936</v>
+        <v>0.007678829048092932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007678829048092936</v>
+        <v>0.007678829048092932</v>
       </c>
       <c r="G7" t="n">
         <v>0.01446628880432055</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05460075993170439</v>
+        <v>0.05460075993170442</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007688206332428769</v>
+        <v>0.007688206332428765</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01857465314293522</v>
+        <v>0.01857465314293523</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008191844395299448</v>
+        <v>0.008191844395299472</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005184065039595176</v>
+        <v>0.005184065039595188</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01284457664843486</v>
+        <v>0.01284457664843487</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009535074819692289</v>
+        <v>0.009535074819648687</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03133443164552282</v>
+        <v>0.0313344316455228</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01094120971298984</v>
+        <v>0.01094120971298983</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009261871589308074</v>
+        <v>0.009261871589308076</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01838858123542652</v>
+        <v>0.01838858123542653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05852305236303994</v>
+        <v>0.05852305236303999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01161049876353475</v>
+        <v>0.01161049876353474</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02249742125319908</v>
+        <v>0.0224974212531991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009648746645064599</v>
+        <v>0.009648746645064619</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01163469843231542</v>
+        <v>0.01163469843231543</v>
       </c>
     </row>
     <row r="9">
@@ -4758,34 +4758,34 @@
         <v>0.01654113165161901</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01289700079613294</v>
+        <v>0.01289700079613295</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03418446695609112</v>
+        <v>0.03418446695609108</v>
       </c>
       <c r="E9" t="n">
         <v>0.01735946097049735</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01496403126791278</v>
+        <v>0.01496403126791276</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02174051402222934</v>
+        <v>0.02174051402222933</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06187498514961324</v>
+        <v>0.06187498514961322</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01496243155033754</v>
+        <v>0.01496243155033753</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02584887836084401</v>
+        <v>0.02584887836084399</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01421454018465623</v>
+        <v>0.01421454018465625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01245829025750395</v>
+        <v>0.01245829025750394</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01917557815607424</v>
+        <v>0.05245785222007529</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2875686217410571</v>
+        <v>0.2150212026685658</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03344243910845224</v>
+        <v>0.05320868877573073</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2971231553451789</v>
+        <v>0.2230061924127099</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2677816983836305</v>
+        <v>0.1985832438525178</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05798147320727141</v>
+        <v>0.05450012940190422</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04182054072288306</v>
+        <v>0.05362671707244108</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09714754858004362</v>
+        <v>0.05656197961718942</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3587551911189472</v>
+        <v>0.2424797685289345</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2728329462779771</v>
+        <v>0.2052618110328198</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02729525910397776</v>
+        <v>0.05285492320166672</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02789697102317061</v>
+        <v>0.02395418449712587</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3080041075996937</v>
+        <v>0.3146602777847723</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04430681648974834</v>
+        <v>0.0292970111177111</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3175582579272216</v>
+        <v>0.3278305310776138</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2882168009656734</v>
+        <v>0.2875159934651594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07253178894899016</v>
+        <v>0.03850416529891205</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05394554444081821</v>
+        <v>0.03247229910750011</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1176145541370675</v>
+        <v>0.05308413958727998</v>
       </c>
       <c r="J3" t="n">
-        <v>0.385321289968596</v>
+        <v>0.3719355316848285</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2927913807417987</v>
+        <v>0.2977037269509709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03723806694789304</v>
+        <v>0.02700097227765878</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009750342947967897</v>
+        <v>0.009750342947968072</v>
       </c>
       <c r="C4" t="n">
-        <v>0.057107816728839</v>
+        <v>0.05710781672883896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0182313872459765</v>
+        <v>0.01823138724597666</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05717382483524554</v>
+        <v>0.05717382483524548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05717382483524554</v>
+        <v>0.05717382483524548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03292842405318074</v>
+        <v>0.03292842405318082</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02321593538928598</v>
+        <v>0.02321593538928612</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05684047822870567</v>
+        <v>0.05684047822870563</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08037229141290636</v>
+        <v>0.08037229141290653</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0542218950888785</v>
+        <v>0.0542218950888786</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01458587582861452</v>
+        <v>0.01458587582861467</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02583555384675896</v>
+        <v>0.02583555384675987</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8133283772644163</v>
+        <v>0.8133283772644144</v>
       </c>
       <c r="D5" t="n">
         <v>0.1773340968447528</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8133283770800538</v>
+        <v>0.8133283770800517</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8133283770800538</v>
+        <v>0.8133283770800517</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4477430716688506</v>
+        <v>0.4477430716688514</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2988633777980302</v>
+        <v>0.2988633777980306</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8133337275974576</v>
+        <v>0.8133337275974568</v>
       </c>
       <c r="J5" t="n">
         <v>1.368542498923496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8211864276017872</v>
+        <v>0.8211864276017888</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05190412485341502</v>
+        <v>0.0519041248534149</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.235917517643838</v>
+        <v>1.910526106604959</v>
       </c>
       <c r="C6" t="n">
         <v>1.958057432082716</v>
       </c>
       <c r="D6" t="n">
-        <v>1.91807790210251</v>
+        <v>1.91807787943616</v>
       </c>
       <c r="E6" t="n">
-        <v>1.228124867544879</v>
+        <v>1.228124867544877</v>
       </c>
       <c r="F6" t="n">
-        <v>1.9575728648649</v>
+        <v>1.957572864864899</v>
       </c>
       <c r="G6" t="n">
-        <v>7.259095598749044</v>
+        <v>1.933704187710171</v>
       </c>
       <c r="H6" t="n">
-        <v>7.249870914929832</v>
+        <v>7.249870914929827</v>
       </c>
       <c r="I6" t="n">
-        <v>7.283007652924571</v>
+        <v>7.283007652924576</v>
       </c>
       <c r="J6" t="n">
-        <v>7.306916104670552</v>
+        <v>2.077885219275891</v>
       </c>
       <c r="K6" t="n">
-        <v>1.955325051025181</v>
+        <v>1.955325051025179</v>
       </c>
       <c r="L6" t="n">
         <v>1.915018837481797</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01302928996929701</v>
+        <v>0.01302928996929699</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06011407491699201</v>
+        <v>0.06011407491699193</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0215101720935986</v>
+        <v>0.02151017209359871</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06013388946923204</v>
+        <v>0.06013388946923191</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06013388946923204</v>
+        <v>0.06013388946923191</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03620737107450977</v>
+        <v>0.03620737107450985</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02649488241061511</v>
+        <v>0.02649488241061505</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06011942525003464</v>
+        <v>0.06011942525003463</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0836512384342354</v>
+        <v>0.08365123843423551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05750084211020755</v>
+        <v>0.0575008421102076</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01786482284994359</v>
+        <v>0.01786482284994357</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01556422843293391</v>
+        <v>0.01556422843293401</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06716106907747871</v>
+        <v>0.06716106907758392</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02946877148595807</v>
+        <v>0.02946877148595814</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06593038970506988</v>
+        <v>0.0659303897050698</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06280332126038693</v>
+        <v>0.06280332126038686</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04323435367832635</v>
+        <v>0.04323435367832647</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03352186501443445</v>
+        <v>0.03352186501443462</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06714640785385133</v>
+        <v>0.06714640785385124</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0906791038459611</v>
+        <v>0.09067910384596121</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05995233854835287</v>
+        <v>0.05995233854835307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02958412116985867</v>
+        <v>0.02958412116985864</v>
       </c>
     </row>
     <row r="9">
@@ -5151,34 +5151,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02945908326098782</v>
+        <v>0.02945908326098809</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0823417330413843</v>
+        <v>0.08234173304138423</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04373799839272354</v>
+        <v>0.04373799839272356</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08903235337343207</v>
+        <v>0.08903235337343202</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08234173446443351</v>
+        <v>0.08234173446443345</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05843502919890208</v>
+        <v>0.05843502919890216</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04872254053500737</v>
+        <v>0.04872254053500738</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08234708337442706</v>
+        <v>0.08234708337442696</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1058788965586278</v>
+        <v>0.105878896558628</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07636919710456855</v>
+        <v>0.07636919710456863</v>
       </c>
       <c r="L9" t="n">
         <v>0.04009248097433591</v>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02016037087287471</v>
+        <v>0.05095363763171468</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2659112557306498</v>
+        <v>0.2118087618371562</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02917792238985978</v>
+        <v>0.05142821345775372</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2753887714786564</v>
+        <v>0.2197220759585748</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2462740711090483</v>
+        <v>0.1954878672265158</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04720174606846485</v>
+        <v>0.0523767714997615</v>
       </c>
       <c r="H2" t="n">
-        <v>0.03680477086509844</v>
+        <v>0.05181315256764357</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0761645710424023</v>
+        <v>0.0539015288759668</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3345976610183308</v>
+        <v>0.2389406916872009</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2401081160795061</v>
+        <v>0.2008904008586716</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02415968105720264</v>
+        <v>0.05114153362447888</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02901081465244134</v>
+        <v>0.02350642298044697</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2831750516010259</v>
+        <v>0.3050757245751854</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03938286687714342</v>
+        <v>0.02688037589767226</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2926528776437233</v>
+        <v>0.3181297024125346</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2635381772741153</v>
+        <v>0.2781267179765323</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06011399773136639</v>
+        <v>0.03363940208996532</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04815692248799933</v>
+        <v>0.02977487784858236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09345215742785776</v>
+        <v>0.04441275070203542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3576533485362156</v>
+        <v>0.3611343943025654</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2553427515599167</v>
+        <v>0.2831768149368157</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03361215589131551</v>
+        <v>0.02501115075408503</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009184049809669192</v>
+        <v>0.009184049809669189</v>
       </c>
       <c r="C4" t="n">
         <v>0.04332208447653225</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01454460208044592</v>
+        <v>0.01454460208044596</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04337767117907371</v>
+        <v>0.04337767117907376</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04337767117907371</v>
+        <v>0.04337767117907374</v>
       </c>
       <c r="G4" t="n">
-        <v>0.025365065519636</v>
+        <v>0.02536506551963609</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01908116464829603</v>
+        <v>0.01908116464829602</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04318982764268266</v>
+        <v>0.04318982764268269</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06540251551038086</v>
+        <v>0.06540251551038084</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03445003389077971</v>
+        <v>0.03445003389077973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01156798254024603</v>
+        <v>0.01156798254024599</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04360863453188466</v>
+        <v>0.0436086345318849</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5643570440093674</v>
+        <v>0.5643570440093661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1316205623487242</v>
+        <v>0.1316205623487251</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5643570455747173</v>
+        <v>0.5643570455747163</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5643570455747173</v>
+        <v>0.5643570455747164</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3155902585551297</v>
+        <v>0.3155902585551306</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2350515780195383</v>
+        <v>0.2350515780195381</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5643610156079142</v>
+        <v>0.5643610156079132</v>
       </c>
       <c r="J5" t="n">
         <v>1.04559960900969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4387940286319179</v>
+        <v>0.4387940286319189</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0543440615428717</v>
+        <v>0.0543440615428719</v>
       </c>
     </row>
     <row r="6">
@@ -5427,7 +5427,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741164769501785</v>
+        <v>1.779506149775817</v>
       </c>
       <c r="C6" t="n">
         <v>1.813884165360349</v>
@@ -5436,25 +5436,25 @@
         <v>1.784299340907997</v>
       </c>
       <c r="E6" t="n">
-        <v>1.133777471739667</v>
+        <v>1.133777471739666</v>
       </c>
       <c r="F6" t="n">
         <v>1.813546455716426</v>
       </c>
       <c r="G6" t="n">
-        <v>6.757345785211753</v>
+        <v>1.795687165485784</v>
       </c>
       <c r="H6" t="n">
-        <v>6.751508772818713</v>
+        <v>6.751508772818712</v>
       </c>
       <c r="I6" t="n">
-        <v>6.775170547334797</v>
+        <v>6.775170547334802</v>
       </c>
       <c r="J6" t="n">
-        <v>6.797728363548607</v>
+        <v>1.925905908125776</v>
       </c>
       <c r="K6" t="n">
-        <v>1.804867617293573</v>
+        <v>1.804867617293574</v>
       </c>
       <c r="L6" t="n">
         <v>1.781722324934718</v>
@@ -5467,13 +5467,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0116552062069473</v>
+        <v>0.01165520620694733</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04565701244141476</v>
+        <v>0.04565701244141478</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01701563802105188</v>
+        <v>0.01701563802105195</v>
       </c>
       <c r="E7" t="n">
         <v>0.04565863636019524</v>
@@ -5482,22 +5482,22 @@
         <v>0.04565863636019524</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02783622191691415</v>
+        <v>0.02783622191691417</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02155232104557411</v>
+        <v>0.02155232104557415</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04566098403996079</v>
+        <v>0.04566098403996078</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06787367190765892</v>
+        <v>0.06787367190765897</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03692119028805783</v>
+        <v>0.0369211902880579</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0140391389375241</v>
+        <v>0.01403913893752414</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01363569422159773</v>
+        <v>0.01363569422159774</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05107222938689554</v>
+        <v>0.05107222938689557</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02314034766937743</v>
+        <v>0.02314034766937753</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05013324740590406</v>
+        <v>0.05013324740590409</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04774734270583979</v>
+        <v>0.0477473427058398</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03324908564498816</v>
+        <v>0.03324908564498822</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02696518477365496</v>
+        <v>0.02696518477365504</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05107384776803481</v>
+        <v>0.0510738477680348</v>
       </c>
       <c r="J8" t="n">
         <v>0.07328721019009832</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03883792016214723</v>
+        <v>0.03883792016214727</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02303740610345388</v>
+        <v>0.02303740610345394</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02280347070656067</v>
+        <v>0.02280347070656075</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06083462236113975</v>
+        <v>0.06083462236113979</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03219337184510296</v>
+        <v>0.03219337184510293</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06548440641350943</v>
+        <v>0.0654844064135095</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06083462407971176</v>
+        <v>0.06083462407971182</v>
       </c>
       <c r="G9" t="n">
         <v>0.04301383183663916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03672993096529909</v>
+        <v>0.03672993096529911</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06083859395968575</v>
+        <v>0.06083859395968578</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08305128182738389</v>
+        <v>0.08305128182738392</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04702513419469077</v>
+        <v>0.04976418309697956</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02921674885724911</v>
+        <v>0.0292167488572491</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02101132385403102</v>
+        <v>0.04925165517045921</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2216094395630534</v>
+        <v>0.2066824304178564</v>
       </c>
       <c r="D2" t="n">
-        <v>0.02964365276045813</v>
+        <v>0.04970595749561792</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2310634668760634</v>
+        <v>0.2145695910278213</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2020308111850353</v>
+        <v>0.1904036762771004</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04050861850940596</v>
+        <v>0.05027775906342487</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05983951462532761</v>
+        <v>0.05129785723810271</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03322233668560545</v>
+        <v>0.04989442350380863</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3078188004008953</v>
+        <v>0.2348624345797985</v>
       </c>
       <c r="K2" t="n">
-        <v>0.205175879784072</v>
+        <v>0.1959500151649253</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02152807772819424</v>
+        <v>0.04926051440018524</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0300050781396994</v>
+        <v>0.02291930786600753</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2324348622463379</v>
+        <v>0.2862953689732991</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03993404456363633</v>
+        <v>0.0261430696760726</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2418917650104701</v>
+        <v>0.2993001052957645</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2128591093194423</v>
+        <v>0.2594098509547549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0524310058458009</v>
+        <v>0.03021782760224097</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07466587904362457</v>
+        <v>0.0375331838265929</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04404689751251043</v>
+        <v>0.02747376257743452</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3270452475287979</v>
+        <v>0.3489945714903734</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2154399977128488</v>
+        <v>0.2674792107955621</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03060051405971219</v>
+        <v>0.02312072527501691</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00789354213157027</v>
+        <v>0.007893542131570879</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01552386078711994</v>
+        <v>0.01552386078712798</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01302509588363691</v>
+        <v>0.01302509588363754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01559241581478602</v>
+        <v>0.01559241581479711</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01559241581478602</v>
+        <v>0.01559241581479427</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01957717454637758</v>
+        <v>0.01957717454637822</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03097105875861739</v>
+        <v>0.03097105875861795</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01577560350322556</v>
+        <v>0.01577560350324201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04839029827136846</v>
+        <v>0.04839029827137005</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01292111478101916</v>
+        <v>0.01292111478101993</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008206027075946693</v>
+        <v>0.008206027075947782</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06086110762887455</v>
+        <v>0.0608611076288763</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1727861268247629</v>
+        <v>0.1727861268249403</v>
       </c>
       <c r="D5" t="n">
-        <v>0.141973556932983</v>
+        <v>0.1419735569329843</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1727861339469622</v>
+        <v>0.172786133947038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1727861339469622</v>
+        <v>0.172786133947038</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2530782210812333</v>
+        <v>0.253078221081235</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4841554232486078</v>
+        <v>0.4841554232486085</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1727851732447556</v>
+        <v>0.1727851732448446</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7879116859147303</v>
+        <v>0.7879116859147319</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1318719813879661</v>
+        <v>0.1318719813879677</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07819247919158877</v>
+        <v>0.1710715880843186</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.777070591652888</v>
+        <v>1.777070591652889</v>
       </c>
       <c r="C6" t="n">
-        <v>1.784806969196498</v>
+        <v>1.784806969196503</v>
       </c>
       <c r="D6" t="n">
-        <v>6.743526617377875</v>
+        <v>1.782015716615159</v>
       </c>
       <c r="E6" t="n">
-        <v>1.104774602927552</v>
+        <v>1.104774602927551</v>
       </c>
       <c r="F6" t="n">
-        <v>1.78492957112149</v>
+        <v>1.784929571121496</v>
       </c>
       <c r="G6" t="n">
-        <v>1.788754224067694</v>
+        <v>6.750040992375405</v>
       </c>
       <c r="H6" t="n">
         <v>6.762004311567773</v>
       </c>
       <c r="I6" t="n">
-        <v>6.746239421332242</v>
+        <v>1.784952653024555</v>
       </c>
       <c r="J6" t="n">
-        <v>1.907744905192969</v>
+        <v>6.779237381741876</v>
       </c>
       <c r="K6" t="n">
         <v>1.781936040867582</v>
       </c>
       <c r="L6" t="n">
-        <v>1.777344997112391</v>
+        <v>1.777344997112392</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009805531064718228</v>
+        <v>0.009805531064718912</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01768854601638045</v>
+        <v>0.01768854601637871</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01493702981045405</v>
+        <v>0.01493702981045563</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01764717882432322</v>
+        <v>0.01764717882432424</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01764717882432322</v>
+        <v>0.0176471788243243</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02148916347952548</v>
+        <v>0.02148916347952653</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03288304769176532</v>
+        <v>0.03288304769176693</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01768759243637355</v>
+        <v>0.01768759243638042</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0503022872045164</v>
+        <v>0.05030228720451699</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01483310371416715</v>
+        <v>0.01483310371416871</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01011801600909469</v>
+        <v>0.01011801600909564</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01156719902197114</v>
+        <v>0.01156719902197271</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02225647372301827</v>
+        <v>0.02225647372302763</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02013394833110128</v>
+        <v>0.02013394833110178</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0214824812392508</v>
+        <v>0.02148248123925994</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01951576122391641</v>
+        <v>0.01951576122393065</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02609605197975516</v>
+        <v>0.02609605197975589</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03748993619200616</v>
+        <v>0.03748993619200752</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02229448093660321</v>
+        <v>0.02229448093662324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05490973486708481</v>
+        <v>0.05490973486708666</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01654192023952444</v>
+        <v>0.01654192023952565</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01769697527527454</v>
+        <v>0.01769697527527493</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01735529676963724</v>
+        <v>0.01735529676964027</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02807743149777642</v>
+        <v>0.02807743149779404</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02532597070045347</v>
+        <v>0.02532597070045614</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03135371543232372</v>
+        <v>0.03135371543232818</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02807743256054408</v>
+        <v>0.02807743256055288</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03187804896092156</v>
+        <v>0.03187804896092251</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04327193317316134</v>
+        <v>0.04327193317316292</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02807647791776953</v>
+        <v>0.02807647791777497</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06069117268591243</v>
+        <v>0.06069117268591451</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0235769922161831</v>
+        <v>0.02357699221618521</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02050690149049067</v>
+        <v>0.02050690149049148</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.02153969927100367</v>
+        <v>0.05496248088187215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2946284485932786</v>
+        <v>0.2176794863021475</v>
       </c>
       <c r="D2" t="n">
-        <v>0.06656320192692149</v>
+        <v>0.05733197840277411</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3043122056166526</v>
+        <v>0.2257874529718037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2746337942115222</v>
+        <v>0.2010840475831433</v>
       </c>
       <c r="G2" t="n">
-        <v>0.08689377005147483</v>
+        <v>0.05840193582340864</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1176656052778973</v>
+        <v>0.06001816807398092</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1043111902540192</v>
+        <v>0.05931900152721158</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4151465473296762</v>
+        <v>0.2482788345921639</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2905043276227925</v>
+        <v>0.2086950598934083</v>
       </c>
       <c r="L2" t="n">
-        <v>0.08959568168652532</v>
+        <v>0.05853336227537067</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03064146129668838</v>
+        <v>0.02614614288524719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3161624846079804</v>
+        <v>0.3184893199773836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08242781594147165</v>
+        <v>0.0429250086901914</v>
       </c>
       <c r="E3" t="n">
-        <v>0.325848040288951</v>
+        <v>0.3318462729316656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2961696288838209</v>
+        <v>0.2910687810246579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1058121807492075</v>
+        <v>0.05057264417174227</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1412070058365759</v>
+        <v>0.062164885799307</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1258624874161324</v>
+        <v>0.0570598643288264</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4501213953763136</v>
+        <v>0.395002400743425</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3131186911213119</v>
+        <v>0.3056747625091604</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1089204027209544</v>
+        <v>0.05178793728312132</v>
       </c>
     </row>
     <row r="4">
@@ -6139,34 +6139,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01157144526941791</v>
+        <v>0.01157144526941795</v>
       </c>
       <c r="C4" t="n">
-        <v>0.06147286337472985</v>
+        <v>0.06147286337472986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03833600979071869</v>
+        <v>0.0383360097907187</v>
       </c>
       <c r="E4" t="n">
-        <v>0.06155980285241797</v>
+        <v>0.06155980285241801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06155980285241796</v>
+        <v>0.061559802852418</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05052331046754968</v>
+        <v>0.05052331046754972</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06870760393418181</v>
+        <v>0.06870760393418189</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06145870313612173</v>
+        <v>0.06145870313612174</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1139663936304168</v>
+        <v>0.1139663936304169</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06504872002949751</v>
+        <v>0.06504872002949753</v>
       </c>
       <c r="L4" t="n">
         <v>0.05203003631911836</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03466345827355426</v>
+        <v>0.0346634582735553</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8662345888200608</v>
+        <v>0.86623458882006</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4671151309935183</v>
+        <v>0.4671151309935195</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8662345925382301</v>
+        <v>0.8662345925382305</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8662345925382301</v>
+        <v>0.866234592538231</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7020136126922945</v>
+        <v>0.7020136126922946</v>
       </c>
       <c r="H5" t="n">
         <v>1.070404769768044</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8662369610639935</v>
+        <v>0.8662369610639927</v>
       </c>
       <c r="J5" t="n">
-        <v>1.980487842116605</v>
+        <v>1.980487842116606</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9291123121712451</v>
+        <v>0.9291123121712459</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8491200878543476</v>
+        <v>0.8491200878543473</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.913197035669126</v>
+        <v>7.239816573530209</v>
       </c>
       <c r="C6" t="n">
-        <v>1.963159960011391</v>
+        <v>1.963159960011389</v>
       </c>
       <c r="D6" t="n">
-        <v>7.266694175205055</v>
+        <v>7.266694175205051</v>
       </c>
       <c r="E6" t="n">
         <v>1.23318939587667</v>
@@ -6234,16 +6234,16 @@
         <v>1.962978150527392</v>
       </c>
       <c r="G6" t="n">
-        <v>1.952148900867257</v>
+        <v>7.278768438728334</v>
       </c>
       <c r="H6" t="n">
-        <v>7.297709416495026</v>
+        <v>1.970259849288449</v>
       </c>
       <c r="I6" t="n">
-        <v>1.963084293535828</v>
+        <v>7.28970383139691</v>
       </c>
       <c r="J6" t="n">
-        <v>7.34272882952305</v>
+        <v>7.342728829523048</v>
       </c>
       <c r="K6" t="n">
         <v>1.966897687320364</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01579727838893349</v>
+        <v>0.01579727838893353</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06568216401170451</v>
+        <v>0.06568216401170444</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04256170009490693</v>
+        <v>0.04256170009490695</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06567140130074534</v>
+        <v>0.06567140130074531</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06567140130074534</v>
+        <v>0.06567140130074532</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05474914358706533</v>
+        <v>0.05474914358706532</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07293343705369752</v>
+        <v>0.07293343705369747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0656845362556374</v>
+        <v>0.06568453625563737</v>
       </c>
       <c r="J7" t="n">
         <v>0.1181922267499325</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0692745531490131</v>
+        <v>0.06927455314901308</v>
       </c>
       <c r="L7" t="n">
-        <v>0.056255869438634</v>
+        <v>0.05625586943863401</v>
       </c>
     </row>
     <row r="8">
@@ -6299,34 +6299,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01922380206865555</v>
+        <v>0.0192238020686556</v>
       </c>
       <c r="C8" t="n">
-        <v>0.07493178728137119</v>
+        <v>0.0749317872813712</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05302978913801266</v>
+        <v>0.05302978913801275</v>
       </c>
       <c r="E8" t="n">
         <v>0.07333770890591321</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06928722244091964</v>
+        <v>0.0692872224409196</v>
       </c>
       <c r="G8" t="n">
         <v>0.06400776612462682</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08219205959126473</v>
+        <v>0.08219205959126477</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07494315879319879</v>
+        <v>0.07494315879319881</v>
       </c>
       <c r="J8" t="n">
         <v>0.1274519954549008</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07259274259883836</v>
+        <v>0.07259274259883841</v>
       </c>
       <c r="L8" t="n">
         <v>0.07160660689878987</v>
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03797780556427622</v>
+        <v>0.03797780556427624</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09558764434264162</v>
+        <v>0.09558764434264169</v>
       </c>
       <c r="D9" t="n">
-        <v>0.07246732673470677</v>
+        <v>0.07246732673470685</v>
       </c>
       <c r="E9" t="n">
         <v>0.1045020718129649</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09558763881919477</v>
+        <v>0.09558763881919473</v>
       </c>
       <c r="G9" t="n">
-        <v>0.08465462391800251</v>
+        <v>0.08465462391800252</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1028389173846347</v>
+        <v>0.1028389173846348</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09559001658657458</v>
+        <v>0.09559001658657465</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1480977070808697</v>
+        <v>0.1480977070808698</v>
       </c>
       <c r="K9" t="n">
         <v>0.09470416675273463</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08616134976957118</v>
+        <v>0.08616134976957122</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01903090546681084</v>
+        <v>0.05247150091951334</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2656513064958708</v>
+        <v>0.2130426218748179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0643640156269787</v>
+        <v>0.05485729246843399</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2751605614575762</v>
+        <v>0.2209945340792428</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2459732569667199</v>
+        <v>0.1966999022173798</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07089523203316846</v>
+        <v>0.05520101741585116</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1002102644872389</v>
+        <v>0.0567442488475727</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07631634593819092</v>
+        <v>0.05548658776920515</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3453423458913241</v>
+        <v>0.2408886388614142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2266153057131126</v>
+        <v>0.2009823807196588</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09507852107987208</v>
+        <v>0.05648184944259298</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0276828476225719</v>
+        <v>0.02403852699993365</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2829067546876926</v>
+        <v>0.3055044943039322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07982531503224374</v>
+        <v>0.04090853787341652</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2924179509363114</v>
+        <v>0.3186075623674746</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2632306464454551</v>
+        <v>0.2785048317762338</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08733756683676495</v>
+        <v>0.04339547681160522</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1210566532229699</v>
+        <v>0.0543505402432761</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09358049617486842</v>
+        <v>0.04540661128857858</v>
       </c>
       <c r="J3" t="n">
-        <v>0.370020645358986</v>
+        <v>0.3657398382008136</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2399437139047318</v>
+        <v>0.2780926196345105</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1151525828371354</v>
+        <v>0.05263315236243945</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008600482079852543</v>
+        <v>0.008600482079852608</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04322811635796091</v>
+        <v>0.04322811635796096</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03554909514324719</v>
+        <v>0.03554909514324721</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04329598857262817</v>
+        <v>0.04329598857262822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04329598857262817</v>
+        <v>0.04329598857262822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03952920863450045</v>
+        <v>0.03952920863450047</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05685180626922833</v>
+        <v>0.05685180626922835</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04330794899720073</v>
+        <v>0.04330794899720072</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07202616033246216</v>
+        <v>0.07202616033246217</v>
       </c>
       <c r="K4" t="n">
         <v>0.02710799594448644</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05380413743579843</v>
+        <v>0.0538041374357984</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02153338793598689</v>
+        <v>0.0215333879359869</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5464162557598635</v>
+        <v>0.5464162557598645</v>
       </c>
       <c r="D5" t="n">
         <v>0.4165424753689305</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5464162601891756</v>
+        <v>0.5464162601891761</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5464162601891756</v>
+        <v>0.5464162601891761</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5028026663233535</v>
+        <v>0.5028026663233541</v>
       </c>
       <c r="H5" t="n">
-        <v>0.783395188621075</v>
+        <v>0.7833951886210748</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5464170072950472</v>
+        <v>0.5464170072950473</v>
       </c>
       <c r="J5" t="n">
-        <v>1.079875319090255</v>
+        <v>1.079875319090254</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3075838865289374</v>
+        <v>0.307583886528937</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08668901419236812</v>
+        <v>0.08668901419236809</v>
       </c>
     </row>
     <row r="6">
@@ -6615,34 +6615,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.741864652492143</v>
+        <v>6.741864652492139</v>
       </c>
       <c r="C6" t="n">
-        <v>1.813948493077717</v>
+        <v>1.813948493077716</v>
       </c>
       <c r="D6" t="n">
-        <v>1.805963842316335</v>
+        <v>1.805963820270247</v>
       </c>
       <c r="E6" t="n">
-        <v>1.133845096598129</v>
+        <v>1.133845096598127</v>
       </c>
       <c r="F6" t="n">
-        <v>1.813882706802445</v>
+        <v>1.813882706802446</v>
       </c>
       <c r="G6" t="n">
-        <v>1.810043680260149</v>
+        <v>6.772793379046788</v>
       </c>
       <c r="H6" t="n">
-        <v>1.827505798751567</v>
+        <v>6.790779332611254</v>
       </c>
       <c r="I6" t="n">
-        <v>1.81382242062285</v>
+        <v>6.776572119409487</v>
       </c>
       <c r="J6" t="n">
-        <v>6.805786124430771</v>
+        <v>1.932841795581443</v>
       </c>
       <c r="K6" t="n">
-        <v>1.797256576884313</v>
+        <v>1.797256576884314</v>
       </c>
       <c r="L6" t="n">
         <v>1.824445877156914</v>
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01174019370595974</v>
+        <v>0.01174019370595971</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04644690908812455</v>
+        <v>0.04644690908812456</v>
       </c>
       <c r="D7" t="n">
         <v>0.03868869827266132</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04642833760936167</v>
+        <v>0.04642833760936171</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04642833760936167</v>
+        <v>0.04642833760936169</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04266892026060754</v>
+        <v>0.04266892026060758</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05999151789533541</v>
+        <v>0.05999151789533544</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0464476606233078</v>
+        <v>0.04644766062330782</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07516587195856921</v>
+        <v>0.07516587195856926</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03024770757059353</v>
+        <v>0.03024770757059354</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05694384906190555</v>
+        <v>0.05694384906190551</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01433926514840792</v>
+        <v>0.01433926514840802</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05339039176907204</v>
+        <v>0.05339039176907211</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04655341285533714</v>
+        <v>0.04655341285533722</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05219942462139778</v>
+        <v>0.05219942462139786</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04917321186109476</v>
+        <v>0.04917321186109477</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04962920115622137</v>
+        <v>0.04962920115622141</v>
       </c>
       <c r="H8" t="n">
         <v>0.06695179879095081</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05340794151892169</v>
+        <v>0.0534079415189217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08212700995175465</v>
+        <v>0.08212700995175461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03276576730882705</v>
+        <v>0.03276576730882708</v>
       </c>
       <c r="L8" t="n">
-        <v>0.06845977790508624</v>
+        <v>0.0684597779050863</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02650256491622304</v>
+        <v>0.02650256491622309</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06647133306396304</v>
+        <v>0.06647133306396311</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05871323220810687</v>
+        <v>0.05871323220810695</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07254362506280715</v>
+        <v>0.07254362506280726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06647132863659908</v>
+        <v>0.06647132863659912</v>
       </c>
       <c r="G9" t="n">
-        <v>0.062693344236446</v>
+        <v>0.06269334423644603</v>
       </c>
       <c r="H9" t="n">
         <v>0.08001594187117395</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06647208459914626</v>
+        <v>0.06647208459914636</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09519029593440771</v>
+        <v>0.09519029593440785</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04709958222968654</v>
+        <v>0.04722327812367834</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07696827303774391</v>
+        <v>0.07696827303774402</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01716545624915651</v>
+        <v>0.04979518697066179</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2328949865231142</v>
+        <v>0.2080176164306659</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03783095702799952</v>
+        <v>0.05088277123166175</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2422392691590551</v>
+        <v>0.2158181816601978</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2135013094081041</v>
+        <v>0.1918975623087867</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04879606439428327</v>
+        <v>0.05145984305389189</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08695911824166645</v>
+        <v>0.05347989759715631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04450754432649597</v>
+        <v>0.05123428807481374</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2721844017136908</v>
+        <v>0.2331840978913528</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1989204749192157</v>
+        <v>0.1961120154596294</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07549194951845811</v>
+        <v>0.05287876017073673</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02551597397807916</v>
+        <v>0.02191452534460129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.245350516370424</v>
+        <v>0.2909424613423972</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04928558071933842</v>
+        <v>0.02962423691487175</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2546971673256192</v>
+        <v>0.3038021062564364</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2259592075746683</v>
+        <v>0.2643167572066654</v>
       </c>
       <c r="G3" t="n">
-        <v>0.06189772560571279</v>
+        <v>0.0337376671417223</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1057931102627871</v>
+        <v>0.04811059246566078</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05696494564424148</v>
+        <v>0.03212643988129597</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2860984864015231</v>
+        <v>0.3352988693121265</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2082284955472556</v>
+        <v>0.265258568304108</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09260238440415762</v>
+        <v>0.04390656363555771</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006058230163947435</v>
+        <v>0.006058230163947417</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02276942422745956</v>
+        <v>0.02276942422745959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01834299470542046</v>
+        <v>0.01834299470542043</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02282972241259544</v>
+        <v>0.02282972241259548</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02282972241259544</v>
+        <v>0.02282972241259548</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02495552843641788</v>
+        <v>0.02495552843641786</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04753909032628494</v>
+        <v>0.04753909032628496</v>
       </c>
       <c r="I4" t="n">
         <v>0.02294144231920383</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0280765217198582</v>
+        <v>0.02807652171985822</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009847629690204507</v>
+        <v>0.009847629690204501</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04072594465404398</v>
+        <v>0.04072594465404396</v>
       </c>
     </row>
     <row r="5">
@@ -6974,34 +6974,34 @@
         <v>0.01936934883503676</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2769132218518115</v>
+        <v>0.2769132218518118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2094743743315473</v>
+        <v>0.2094743743315477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2769132272300552</v>
+        <v>0.2769132272300553</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2769132272300552</v>
+        <v>0.2769132272300553</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3221812509707604</v>
+        <v>0.3221812509707601</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7395393228618564</v>
+        <v>0.7395393228618565</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2769126690406507</v>
+        <v>0.2769126690406508</v>
       </c>
       <c r="J5" t="n">
         <v>0.3946898699524706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07642342719211424</v>
+        <v>0.07642342719211404</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6702522991913475</v>
+        <v>0.111495757644442</v>
       </c>
     </row>
     <row r="6">
@@ -7020,28 +7020,28 @@
         <v>1.787421044941238</v>
       </c>
       <c r="E6" t="n">
-        <v>1.112108317742203</v>
+        <v>1.112108317742204</v>
       </c>
       <c r="F6" t="n">
-        <v>1.79218551662162</v>
+        <v>1.792185516621621</v>
       </c>
       <c r="G6" t="n">
-        <v>6.756026029195684</v>
+        <v>1.794130850653127</v>
       </c>
       <c r="H6" t="n">
-        <v>6.779213450598364</v>
+        <v>6.779213450598373</v>
       </c>
       <c r="I6" t="n">
-        <v>1.792116764535915</v>
+        <v>1.792116764535914</v>
       </c>
       <c r="J6" t="n">
-        <v>6.759571804174092</v>
+        <v>1.887370019785221</v>
       </c>
       <c r="K6" t="n">
-        <v>1.778653312049667</v>
+        <v>1.778653312049669</v>
       </c>
       <c r="L6" t="n">
-        <v>1.810090989975511</v>
+        <v>1.810090989975513</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008260878935487289</v>
+        <v>0.008260878935487274</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02514464390190494</v>
+        <v>0.0251446439019049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02054556893636246</v>
+        <v>0.02054556893636243</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0251172161935394</v>
+        <v>0.02511721619353941</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0251172161935394</v>
+        <v>0.02511721619353941</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02715817720795773</v>
+        <v>0.02715817720795774</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04974173909782487</v>
+        <v>0.04974173909782484</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02514409109074371</v>
+        <v>0.02514409109074372</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03027917049139809</v>
+        <v>0.03027917049139808</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01205027846174437</v>
+        <v>0.01205027846174435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04292859342558386</v>
+        <v>0.04292859342558383</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01016049878197393</v>
+        <v>0.0101604987819739</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0301473143251932</v>
+        <v>0.03014731432519321</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02622260013773726</v>
+        <v>0.02622260013773729</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02929439089938735</v>
+        <v>0.02929439089938736</v>
       </c>
       <c r="F8" t="n">
         <v>0.02712712024958102</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03218639806794887</v>
+        <v>0.03218639806794885</v>
       </c>
       <c r="H8" t="n">
         <v>0.05476995995781742</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03017231195073487</v>
+        <v>0.03017231195073486</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03530800620713621</v>
+        <v>0.03530800620713622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01389178293850879</v>
+        <v>0.0138917829385088</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05122489964986868</v>
+        <v>0.05122489964986859</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0173390946101224</v>
+        <v>0.01733909461012238</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03756987358931689</v>
+        <v>0.0375698735893169</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03297087099163497</v>
+        <v>0.03297087099163494</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04143224813813776</v>
+        <v>0.04143224813813771</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03756986931324137</v>
+        <v>0.03756986931324136</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03958340689536972</v>
+        <v>0.0395834068953697</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06216696878523673</v>
+        <v>0.06216696878523677</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03756932077815565</v>
+        <v>0.03756932077815566</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04270440017881002</v>
+        <v>0.04270440017881003</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02245755546478094</v>
+        <v>0.0224575554647809</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05535382311299584</v>
+        <v>0.0553538231129958</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01979780953691412</v>
+        <v>0.05301326975747908</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2902892411082114</v>
+        <v>0.2157557545010365</v>
       </c>
       <c r="D2" t="n">
-        <v>0.03723350507848224</v>
+        <v>0.05393087578375098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2999209842714059</v>
+        <v>0.2238081268451043</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2703831544718832</v>
+        <v>0.1992217259032031</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06402912489206319</v>
+        <v>0.05534107603415241</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05112020846397512</v>
+        <v>0.05463914985742797</v>
       </c>
       <c r="I2" t="n">
-        <v>0.09977642088296704</v>
+        <v>0.05722298360905357</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3980916122419038</v>
+        <v>0.2454955377095543</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2809170973757862</v>
+        <v>0.2063530534356225</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03389987926884063</v>
+        <v>0.05372452169817193</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02861498416513087</v>
+        <v>0.0244723813324551</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3111213514093075</v>
+        <v>0.3160459321913731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04866964583137794</v>
+        <v>0.03098725659023818</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3207532259940344</v>
+        <v>0.3293243874132882</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2912153961945107</v>
+        <v>0.2887400401770067</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07949015931292773</v>
+        <v>0.04103085386209997</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0646442048877085</v>
+        <v>0.03620722178745651</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1206376489252603</v>
+        <v>0.05434536082884318</v>
       </c>
       <c r="J3" t="n">
-        <v>0.430487174555355</v>
+        <v>0.3875394827678116</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3020645772868688</v>
+        <v>0.3011596094021307</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0448371133103252</v>
+        <v>0.02977783135562644</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01021665349633829</v>
+        <v>0.01021665349633758</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05870172398365237</v>
+        <v>0.05870172398365033</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02058143568270302</v>
+        <v>0.02058143568270563</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05877259162064785</v>
+        <v>0.05877259162064892</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05877259162064814</v>
+        <v>0.05877259162064893</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03661874961262702</v>
+        <v>0.03661874961263004</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02883988653078432</v>
+        <v>0.02883988653078306</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05849159202270553</v>
+        <v>0.05849159202270334</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1035301371492208</v>
+        <v>0.1035301371492184</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05901489007670448</v>
+        <v>0.05901489007670443</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01860857662149577</v>
+        <v>0.01860857662149739</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0288945939933327</v>
+        <v>0.02889459399333132</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8330623320760563</v>
+        <v>0.8330623320760617</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2058923791870102</v>
+        <v>0.205892379187046</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8330623329699891</v>
+        <v>0.8330623329699882</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8330623329699891</v>
+        <v>0.8330623329699882</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4954628461380425</v>
+        <v>0.4954628461380455</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3757844753962024</v>
+        <v>0.3757844753961886</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8330672145018028</v>
+        <v>0.8330672145018065</v>
       </c>
       <c r="J5" t="n">
-        <v>1.802258012459806</v>
+        <v>1.802258012459798</v>
       </c>
       <c r="K5" t="n">
-        <v>0.879178477047353</v>
+        <v>0.8791784770473576</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2068656622695433</v>
+        <v>0.08700271667166397</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.911339594389983</v>
+        <v>1.911339594389985</v>
       </c>
       <c r="C6" t="n">
-        <v>1.959976149928346</v>
+        <v>1.959976149928351</v>
       </c>
       <c r="D6" t="n">
         <v>1.920728266810403</v>
       </c>
       <c r="E6" t="n">
-        <v>1.230021442584137</v>
+        <v>1.230021442584131</v>
       </c>
       <c r="F6" t="n">
-        <v>1.959545420792224</v>
+        <v>1.959545420792222</v>
       </c>
       <c r="G6" t="n">
-        <v>7.263248139689163</v>
+        <v>7.263248139689167</v>
       </c>
       <c r="H6" t="n">
-        <v>7.255971057199251</v>
+        <v>7.255971057199255</v>
       </c>
       <c r="I6" t="n">
-        <v>7.285120982099244</v>
+        <v>7.285120982099237</v>
       </c>
       <c r="J6" t="n">
-        <v>7.330551998460899</v>
+        <v>7.330551998460909</v>
       </c>
       <c r="K6" t="n">
-        <v>1.960503926005337</v>
+        <v>1.960503926005339</v>
       </c>
       <c r="L6" t="n">
         <v>1.919384437935466</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01366899924403183</v>
+        <v>0.01366899924403424</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0619390553446496</v>
+        <v>0.06193905534465555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02403362564250322</v>
+        <v>0.02403362564250812</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06194929162243225</v>
+        <v>0.06194929162243148</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06194929162243225</v>
+        <v>0.06194929162243148</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04007109536032279</v>
+        <v>0.04007109536032678</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03229223227847746</v>
+        <v>0.03229223227847972</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06194393777040136</v>
+        <v>0.06194393777040009</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1069824828969156</v>
+        <v>0.106982482896915</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06246723582439561</v>
+        <v>0.06246723582440113</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02206092236919295</v>
+        <v>0.02206092236919403</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01639465380364402</v>
+        <v>0.01639465380365124</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06942816651724384</v>
+        <v>0.06942816651714658</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03249747520627434</v>
+        <v>0.03249747520626882</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06812720957603602</v>
+        <v>0.06812720957604136</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06482155858412254</v>
+        <v>0.06482155858412267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04754931401217229</v>
+        <v>0.04754931401216751</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03977045093031818</v>
+        <v>0.03977045093032138</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06942215642223962</v>
+        <v>0.0694221564222408</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1144616355564134</v>
+        <v>0.1144616355564139</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06510460906665197</v>
+        <v>0.0651046090666535</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03450359161147552</v>
+        <v>0.03450359161147908</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03137307910714612</v>
+        <v>0.03137307910714926</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08585405873342655</v>
+        <v>0.08585405873343001</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04794879127908773</v>
+        <v>0.04794879127909472</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09302134015297769</v>
+        <v>0.09302134015297697</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08585406013153291</v>
+        <v>0.08585406013154122</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06398609874910186</v>
+        <v>0.06398609874910116</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05620723566724937</v>
+        <v>0.05620723566725417</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0858589411591734</v>
+        <v>0.08585894115917457</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1308974862856905</v>
+        <v>0.1308974862856894</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08278360844725265</v>
+        <v>0.08278360844724601</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04597592575796301</v>
+        <v>0.04597592575796845</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01805102996540172</v>
+        <v>0.05175754290233287</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2616236947793208</v>
+        <v>0.2122675794774466</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0351726774258959</v>
+        <v>0.05265862120184776</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2711579484458367</v>
+        <v>0.2202349427398827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2418973446750119</v>
+        <v>0.1958792957424585</v>
       </c>
       <c r="G2" t="n">
-        <v>0.06092888369975989</v>
+        <v>0.05401411918209518</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1664322782000052</v>
+        <v>0.05961400636327682</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07216705778848111</v>
+        <v>0.05460589222229703</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3503291536759161</v>
+        <v>0.2407125946444678</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2362122262516456</v>
+        <v>0.201270145079449</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0579817979688644</v>
+        <v>0.05384884160357541</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02659927271702879</v>
+        <v>0.02324110018655895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2782996423863848</v>
+        <v>0.3037055195634447</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0462927140351836</v>
+        <v>0.0296264676700113</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2878357480733749</v>
+        <v>0.3168392049711403</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2585751443025498</v>
+        <v>0.2766357597148767</v>
       </c>
       <c r="G3" t="n">
-        <v>0.07591768663218332</v>
+        <v>0.03926800248759481</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1972669718658002</v>
+        <v>0.07887759456341151</v>
       </c>
       <c r="I3" t="n">
-        <v>0.08885635358578164</v>
+        <v>0.04343835094439895</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3757568609472631</v>
+        <v>0.3676048915651662</v>
       </c>
       <c r="K3" t="n">
-        <v>0.25093990521911</v>
+        <v>0.2818147541055005</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07252838202691758</v>
+        <v>0.03829346230828452</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007866892241961252</v>
+        <v>0.007866892241961253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04068816477993921</v>
+        <v>0.04068816477993917</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01804498615147921</v>
+        <v>0.01804498615147924</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04075312010758896</v>
+        <v>0.04075312010758893</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04075312010758896</v>
+        <v>0.04075312010758895</v>
       </c>
       <c r="G4" t="n">
         <v>0.03345552548445853</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09604922696202428</v>
+        <v>0.09604922696202425</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04070441678960659</v>
+        <v>0.04070441678960654</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0746688151536065</v>
+        <v>0.07466881515360645</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03232253899814326</v>
+        <v>0.03232253899814325</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03160647075508453</v>
+        <v>0.03160647075508449</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01693417295862067</v>
+        <v>0.01693417295862072</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5184588693629141</v>
+        <v>0.5184588693629142</v>
       </c>
       <c r="D5" t="n">
         <v>0.1732815481163757</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5184588729393528</v>
+        <v>0.5184588729393523</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5184588729393528</v>
+        <v>0.5184588729393523</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4272236753177521</v>
+        <v>0.4272236753177514</v>
       </c>
       <c r="H5" t="n">
-        <v>1.508593619718544</v>
+        <v>1.508593619718547</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5184604197136238</v>
+        <v>0.5184604197136231</v>
       </c>
       <c r="J5" t="n">
-        <v>1.204777063789708</v>
+        <v>1.204777063789709</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3962378584006137</v>
+        <v>0.3962378584006142</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0537993778017588</v>
+        <v>0.469390933618443</v>
       </c>
     </row>
     <row r="6">
@@ -7803,13 +7803,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.740625487866248</v>
+        <v>6.740625487866245</v>
       </c>
       <c r="C6" t="n">
         <v>1.811284181727477</v>
       </c>
       <c r="D6" t="n">
-        <v>1.787908660474754</v>
+        <v>1.787908637513032</v>
       </c>
       <c r="E6" t="n">
         <v>1.131176561905283</v>
@@ -7818,10 +7818,10 @@
         <v>1.811167382364495</v>
       </c>
       <c r="G6" t="n">
-        <v>1.803962489951301</v>
+        <v>6.766214121108742</v>
       </c>
       <c r="H6" t="n">
-        <v>6.829635999693698</v>
+        <v>6.829635999693697</v>
       </c>
       <c r="I6" t="n">
         <v>6.773463012413888</v>
@@ -7833,7 +7833,7 @@
         <v>1.802660697151861</v>
       </c>
       <c r="L6" t="n">
-        <v>1.802017246644512</v>
+        <v>1.802017246644513</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01073731725831749</v>
+        <v>0.01073731725831751</v>
       </c>
       <c r="C7" t="n">
         <v>0.04357329145525349</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02091530085036369</v>
+        <v>0.02091530085036372</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0435639936591375</v>
+        <v>0.04356399365913746</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0435639936591375</v>
+        <v>0.04356399365913746</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03632595050081477</v>
+        <v>0.03632595050081478</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09891965197838051</v>
+        <v>0.0989196519783805</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04357484180596282</v>
+        <v>0.04357484180596281</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07753924016996271</v>
+        <v>0.07753924016996276</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03519296401449948</v>
+        <v>0.03519296401449951</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03447689577144075</v>
+        <v>0.03447689577144076</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01313376426129065</v>
+        <v>0.01313376426129067</v>
       </c>
       <c r="C8" t="n">
         <v>0.04998985766983517</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02817522215992186</v>
+        <v>0.02817522215992187</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04888905202808184</v>
+        <v>0.0488890520280818</v>
       </c>
       <c r="F8" t="n">
         <v>0.04609194397209316</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04275050679177562</v>
+        <v>0.04275050679177565</v>
       </c>
       <c r="H8" t="n">
         <v>0.1053442082693554</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04999939809692369</v>
+        <v>0.04999939809692364</v>
       </c>
       <c r="J8" t="n">
         <v>0.08396458809423692</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03751458681989295</v>
+        <v>0.03751458681989293</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04510914903354468</v>
+        <v>0.04510914903354463</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02375602343103947</v>
+        <v>0.02375602343103944</v>
       </c>
       <c r="C9" t="n">
         <v>0.06128289667255674</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03862500593634212</v>
+        <v>0.03862500593634208</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06669606592550562</v>
+        <v>0.06669606592550557</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0612828819191386</v>
+        <v>0.06128288191913855</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05403555571811808</v>
+        <v>0.05403555571811806</v>
       </c>
       <c r="H9" t="n">
         <v>0.1166292571956838</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06128444702326609</v>
+        <v>0.06128444702326601</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09524884538726605</v>
+        <v>0.09524884538726598</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04699589272026025</v>
+        <v>0.05018463950806779</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05218650098874406</v>
+        <v>0.05218650098874397</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia ionising radiation results.xlsx
+++ b/Results/Ammonia/ammonia ionising radiation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05281605903878067</v>
+        <v>0.05281605903877891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2146983751643948</v>
+        <v>0.2146983751643926</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05372495614201913</v>
+        <v>0.05372495614201934</v>
       </c>
       <c r="E2" t="n">
-        <v>0.222742896669805</v>
+        <v>0.2227428966698045</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1981659996308526</v>
+        <v>0.1981659996308565</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05509133713482981</v>
+        <v>0.05509133713483146</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05458120103296979</v>
+        <v>0.05458120103297411</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05642734389430149</v>
+        <v>0.05642734389429966</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2434696783317295</v>
+        <v>0.243469678331734</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2057019784851689</v>
+        <v>0.2057019784851682</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05317903924610821</v>
+        <v>0.05317903924611001</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02460740457325459</v>
+        <v>0.0246074045732547</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3115606567199884</v>
+        <v>0.3115606567199847</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0310786434762853</v>
+        <v>0.0310786434762823</v>
       </c>
       <c r="E3" t="n">
-        <v>0.324823384662034</v>
+        <v>0.3248233846620326</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2842547225391923</v>
+        <v>0.2842547225391953</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04082600003730675</v>
+        <v>0.04082600003730244</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03738767176358291</v>
+        <v>0.0373876717635814</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05028936616175839</v>
+        <v>0.05028936616175809</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3763046577404752</v>
+        <v>0.3763046577404698</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2989303979150117</v>
+        <v>0.2989303979150128</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02744351687733085</v>
+        <v>0.02744351687733146</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01045831254482078</v>
+        <v>0.01045831254482168</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05209750074859884</v>
+        <v>0.05209750074859954</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02072472343922379</v>
+        <v>0.02072472343921356</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05218238499887266</v>
+        <v>0.05218238499886937</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05218238499887269</v>
+        <v>0.05218238499887067</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03626347823342776</v>
+        <v>0.03626347823342711</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03063145745416017</v>
+        <v>0.03063145745415924</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05194933703032473</v>
+        <v>0.05194933703032464</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08657899088653012</v>
+        <v>0.08657899088652855</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05581025814060086</v>
+        <v>0.05581025814059935</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01496410006008265</v>
+        <v>0.01496410006008307</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03916241339422161</v>
+        <v>0.03916241339421382</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8066488549544586</v>
+        <v>0.8066488549545409</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2366309993991056</v>
+        <v>0.236630999399027</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8066488561148217</v>
+        <v>0.8066488561148872</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8066488561148217</v>
+        <v>0.8066488561148872</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5448236548711061</v>
+        <v>0.5448236548710966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4778880786918643</v>
+        <v>0.4778880786918663</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8066523251349048</v>
+        <v>0.8066523251350425</v>
       </c>
       <c r="J5" t="n">
-        <v>1.581369162756337</v>
+        <v>1.58136916275633</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9100786833420168</v>
+        <v>0.9100786833420261</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1447862087725537</v>
+        <v>0.1447862087725476</v>
       </c>
     </row>
     <row r="6">
@@ -681,31 +681,31 @@
         <v>2.083477149525574</v>
       </c>
       <c r="D6" t="n">
-        <v>2.051113817684984</v>
+        <v>2.051113817684983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.303412383421295</v>
+        <v>1.303412383421288</v>
       </c>
       <c r="F6" t="n">
-        <v>2.083167075928157</v>
+        <v>2.083167075928166</v>
       </c>
       <c r="G6" t="n">
-        <v>7.759036211281911</v>
+        <v>7.759036211281906</v>
       </c>
       <c r="H6" t="n">
-        <v>7.753995027464667</v>
+        <v>7.753995027464676</v>
       </c>
       <c r="I6" t="n">
-        <v>7.774722070078809</v>
+        <v>7.774722070078822</v>
       </c>
       <c r="J6" t="n">
-        <v>7.809793347752276</v>
+        <v>7.809793347752279</v>
       </c>
       <c r="K6" t="n">
-        <v>2.087478299133199</v>
+        <v>2.087478299133204</v>
       </c>
       <c r="L6" t="n">
-        <v>2.045915171799181</v>
+        <v>2.045915171799182</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01414429418526</v>
+        <v>0.01414429418525878</v>
       </c>
       <c r="C7" t="n">
-        <v>0.05563184849031714</v>
+        <v>0.05563184849032575</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02441054864808326</v>
+        <v>0.02441054864807831</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05564496034812405</v>
+        <v>0.05564496034812292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.05564496034812408</v>
+        <v>0.05564496034812292</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03994945987386697</v>
+        <v>0.03994945987387381</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03431743909459944</v>
+        <v>0.03431743909461138</v>
       </c>
       <c r="I7" t="n">
-        <v>0.05563531867076401</v>
+        <v>0.05563531867076175</v>
       </c>
       <c r="J7" t="n">
-        <v>0.09026497252696941</v>
+        <v>0.09026497252696046</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05949623978104013</v>
+        <v>0.05949623978104517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01865008170052193</v>
+        <v>0.01865008170052255</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0171285532149878</v>
+        <v>0.0171285532149871</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06379291294530057</v>
+        <v>0.06379291294530848</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03362864213850787</v>
+        <v>0.03362864213851172</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06237938132892341</v>
+        <v>0.06237938132892101</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05878768482922069</v>
+        <v>0.05878768482921586</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04809679870265597</v>
+        <v>0.0480967987026567</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04246477792338988</v>
+        <v>0.04246477792339479</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06378265749955306</v>
+        <v>0.06378265749956333</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09841332604025342</v>
+        <v>0.09841332604025296</v>
       </c>
       <c r="K8" t="n">
-        <v>0.06238459195350263</v>
+        <v>0.06238459195350179</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03219068910112251</v>
+        <v>0.03219068910113162</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03506552584772501</v>
+        <v>0.03506552584772572</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08376088262259475</v>
+        <v>0.0837608826226028</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05253974643291679</v>
+        <v>0.05253974643290751</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09207854070275275</v>
+        <v>0.09207854070275744</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08376088312065399</v>
+        <v>0.08376088312066408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0680784940061446</v>
+        <v>0.06807849400614298</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06244647322687701</v>
+        <v>0.06244647322687159</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08376435280304162</v>
+        <v>0.08376435280303798</v>
       </c>
       <c r="J9" t="n">
-        <v>0.118394006659247</v>
+        <v>0.1183940066592425</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07854936214411144</v>
+        <v>0.07854936214410473</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04677911583279949</v>
+        <v>0.04677911583278707</v>
       </c>
     </row>
   </sheetData>
@@ -911,28 +911,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05074594911150737</v>
+        <v>0.05074594911150746</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2082535752130411</v>
+        <v>0.2082535752130415</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05364752039835595</v>
+        <v>0.053647520398356</v>
       </c>
       <c r="E2" t="n">
         <v>0.2161759362550037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.191940894352004</v>
+        <v>0.1919408943520043</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05312065971566791</v>
+        <v>0.05312065971566792</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05548306134496601</v>
+        <v>0.05548306134496599</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05170046969791797</v>
+        <v>0.05170046969791803</v>
       </c>
       <c r="J2" t="n">
         <v>0.2363025912653332</v>
@@ -941,7 +941,7 @@
         <v>0.1974034640884806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05275639618337474</v>
+        <v>0.05275639618337477</v>
       </c>
     </row>
     <row r="3">
@@ -951,13 +951,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02240669646625519</v>
+        <v>0.02240669646625521</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2876263071507316</v>
+        <v>0.2876263071507319</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04297964292592538</v>
+        <v>0.04297964292592539</v>
       </c>
       <c r="E3" t="n">
         <v>0.3006759914179798</v>
@@ -966,22 +966,22 @@
         <v>0.2606716222783153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03928144322956396</v>
+        <v>0.03928144322956398</v>
       </c>
       <c r="H3" t="n">
-        <v>0.05614994320747617</v>
+        <v>0.05614994320747621</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02917930302739458</v>
+        <v>0.02917930302739462</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3488929351660976</v>
+        <v>0.3488929351660978</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2680583434616159</v>
+        <v>0.2680583434616162</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03689920256557198</v>
+        <v>0.03689920256557194</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.005866446728956331</v>
+        <v>0.005866446728956282</v>
       </c>
       <c r="C4" t="n">
         <v>0.0168544333197975</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03864102920264861</v>
+        <v>0.03864102920264865</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01693309220289491</v>
+        <v>0.01693309220289492</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0169330922028949</v>
+        <v>0.01693309220289492</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03277590361771768</v>
+        <v>0.03277590361771763</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05923303472231566</v>
+        <v>0.05923303472231569</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01722058440244157</v>
+        <v>0.01722058440244159</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04744399078012384</v>
+        <v>0.0474439907801238</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01328418382936233</v>
+        <v>0.01328418382936227</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02872810562682728</v>
+        <v>0.0287281056268273</v>
       </c>
     </row>
     <row r="5">
@@ -1031,13 +1031,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01345060197441657</v>
+        <v>0.01345060197441658</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1840661080355476</v>
+        <v>0.1840661080355477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.522793627639172</v>
+        <v>0.5227936276391724</v>
       </c>
       <c r="E5" t="n">
         <v>0.1840661156857015</v>
@@ -1046,22 +1046,22 @@
         <v>0.1840661156857015</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4497701450683654</v>
+        <v>0.449770145068366</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9630259474827799</v>
+        <v>0.9630259474827797</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1840624562521264</v>
+        <v>0.1840624562521268</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7468602615571688</v>
+        <v>0.7468602615571658</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1258177659538775</v>
+        <v>0.1258177659538776</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4493366841190563</v>
+        <v>0.4493366841190554</v>
       </c>
     </row>
     <row r="6">
@@ -1077,10 +1077,10 @@
         <v>1.786270314257632</v>
       </c>
       <c r="D6" t="n">
-        <v>6.770618213909937</v>
+        <v>6.770618213909938</v>
       </c>
       <c r="E6" t="n">
-        <v>1.106235900330732</v>
+        <v>1.106235900330734</v>
       </c>
       <c r="F6" t="n">
         <v>1.786625951947176</v>
@@ -1089,16 +1089,16 @@
         <v>6.76457566693927</v>
       </c>
       <c r="H6" t="n">
-        <v>6.791763542585405</v>
+        <v>6.791763542585402</v>
       </c>
       <c r="I6" t="n">
         <v>1.786685080789572</v>
       </c>
       <c r="J6" t="n">
-        <v>1.907086706600375</v>
+        <v>1.907086706600374</v>
       </c>
       <c r="K6" t="n">
-        <v>1.78229271941591</v>
+        <v>1.782292719415911</v>
       </c>
       <c r="L6" t="n">
         <v>1.798249194250525</v>
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008447042066590141</v>
+        <v>0.008447042066590117</v>
       </c>
       <c r="C7" t="n">
         <v>0.01980483152349646</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04122156533080015</v>
+        <v>0.04122156533080016</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01976504989574101</v>
+        <v>0.01976504989574104</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01976504989574101</v>
+        <v>0.01976504989574104</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03535649895535155</v>
+        <v>0.03535649895535152</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06181363005994951</v>
+        <v>0.06181363005994942</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01980117974007545</v>
+        <v>0.01980117974007544</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05002458611775773</v>
+        <v>0.05002458611775767</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01586477916699613</v>
+        <v>0.01586477916699614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03130870096446112</v>
+        <v>0.03130870096446108</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01090116981845189</v>
+        <v>0.01090116981845192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02606504058166822</v>
+        <v>0.02606504058166824</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04831601709462712</v>
+        <v>0.04831601709462718</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02501789376964374</v>
+        <v>0.02501789376964377</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02235709351705705</v>
+        <v>0.02235709351705709</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04165395280645438</v>
+        <v>0.04165395280645441</v>
       </c>
       <c r="H8" t="n">
         <v>0.06811108391106531</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02609863359117834</v>
+        <v>0.02609863359117839</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05632279528754842</v>
+        <v>0.05632279528754837</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01824751516382844</v>
+        <v>0.01824751516382841</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04162083029526854</v>
+        <v>0.04162083029526862</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01911162039559009</v>
+        <v>0.01911162039559007</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03441287278870132</v>
+        <v>0.03441287278870135</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05582966601452688</v>
+        <v>0.05582966601452696</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03896353755700165</v>
+        <v>0.03896353755700169</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03441286789142971</v>
+        <v>0.03441286789142976</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04996454022055635</v>
+        <v>0.04996454022055638</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07642167132515439</v>
+        <v>0.07642167132515437</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03440922100528029</v>
+        <v>0.03440922100528035</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06463262738296253</v>
+        <v>0.06463262738296265</v>
       </c>
       <c r="K9" t="n">
         <v>0.02818796260771145</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04591674222966597</v>
+        <v>0.04591674222966598</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1436808362891242</v>
+        <v>0.1436808362891243</v>
       </c>
       <c r="C2" t="n">
         <v>0.1878938257795089</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1423219816454466</v>
+        <v>0.1423219816454467</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2095239861144814</v>
+        <v>0.2095239861144813</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2095239769010055</v>
+        <v>0.2095239769010054</v>
       </c>
       <c r="G2" t="n">
         <v>0.1427317872644495</v>
       </c>
       <c r="H2" t="n">
-        <v>0.143188325558563</v>
+        <v>0.1431883255585629</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1434780767326242</v>
+        <v>0.1434780767326241</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1573030519428574</v>
+        <v>0.1573030519428575</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1679393014130293</v>
+        <v>0.1679393014130295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1416503180812263</v>
+        <v>0.1416503180812262</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.163422769839544</v>
+        <v>0.1634227698395441</v>
       </c>
       <c r="C3" t="n">
         <v>0.2246525011221368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1537143950153086</v>
+        <v>0.1537143950153087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2709777539186409</v>
+        <v>0.2709777539186413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2709777447051649</v>
+        <v>0.2709777447051652</v>
       </c>
       <c r="G3" t="n">
         <v>0.1566515842529247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1600255062110063</v>
+        <v>0.1600255062110064</v>
       </c>
       <c r="I3" t="n">
         <v>0.1619571203267502</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1905576548180482</v>
+        <v>0.1905576548180483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2023377546754492</v>
+        <v>0.2023377546754491</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1491011195235413</v>
+        <v>0.1491011195235412</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03705371910639652</v>
+        <v>0.03705371910639654</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01239664516810084</v>
+        <v>0.01239664516810086</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02170483080203833</v>
+        <v>0.0217048308020383</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03538379879164207</v>
+        <v>0.03538379879164205</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03538379879164207</v>
+        <v>0.03538379879164204</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02641127294374252</v>
+        <v>0.02641127294374253</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03155958114309246</v>
+        <v>0.0315595811430924</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03528059939226183</v>
+        <v>0.03528059939226182</v>
       </c>
       <c r="J4" t="n">
-        <v>0.046578179181934</v>
+        <v>0.04657817918193401</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03478038209903814</v>
+        <v>0.03478038209903812</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01436214986268506</v>
+        <v>0.01436214986268504</v>
       </c>
     </row>
     <row r="5">
@@ -1427,34 +1427,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5689832798848787</v>
+        <v>0.5689832798848785</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1213159676516535</v>
+        <v>0.1213159676516538</v>
       </c>
       <c r="D5" t="n">
         <v>0.2776695561780035</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5167139362205154</v>
+        <v>0.5167139362205153</v>
       </c>
       <c r="F5" t="n">
         <v>0.5167139362205154</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3707020062965682</v>
+        <v>0.3707020062965684</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5106439725608547</v>
+        <v>0.510643972560855</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5167158862801439</v>
+        <v>0.5167158862801441</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7587537544198752</v>
+        <v>0.7587537544198747</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5136053070959252</v>
+        <v>0.5136053070959258</v>
       </c>
       <c r="L5" t="n">
         <v>0.1671291836892641</v>
@@ -1467,16 +1467,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.143840164653845</v>
+        <v>7.143840164653835</v>
       </c>
       <c r="C6" t="n">
         <v>1.880354610468241</v>
       </c>
       <c r="D6" t="n">
-        <v>1.889578126619456</v>
+        <v>1.889578126619455</v>
       </c>
       <c r="E6" t="n">
-        <v>1.185628655815902</v>
+        <v>1.185628655815901</v>
       </c>
       <c r="F6" t="n">
         <v>1.903453034810752</v>
@@ -1485,16 +1485,16 @@
         <v>1.894576944121538</v>
       </c>
       <c r="H6" t="n">
-        <v>7.139194350179353</v>
+        <v>7.139194350179354</v>
       </c>
       <c r="I6" t="n">
         <v>1.903446270570057</v>
       </c>
       <c r="J6" t="n">
-        <v>7.15386189047469</v>
+        <v>7.153861890474695</v>
       </c>
       <c r="K6" t="n">
-        <v>1.903091797187616</v>
+        <v>1.903091797187615</v>
       </c>
       <c r="L6" t="n">
         <v>1.882396410240654</v>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03990049650451415</v>
+        <v>0.03990049650451411</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01563672784116874</v>
+        <v>0.01563672784116876</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02455153215267129</v>
+        <v>0.02455153215267126</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03813273016678274</v>
+        <v>0.03813273016678275</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03813273016678274</v>
+        <v>0.03813273016678275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02925805034186013</v>
+        <v>0.02925805034186015</v>
       </c>
       <c r="H7" t="n">
         <v>0.03440635854121003</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03812737679037945</v>
+        <v>0.03812737679037944</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0494249565800516</v>
+        <v>0.04942495658005164</v>
       </c>
       <c r="K7" t="n">
         <v>0.03762715949715576</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01720892726080265</v>
+        <v>0.01720892726080264</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04228015477453224</v>
+        <v>0.04228015477453222</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02212554538568727</v>
+        <v>0.02212554538568728</v>
       </c>
       <c r="D8" t="n">
         <v>0.03188298506924678</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04349173803835849</v>
+        <v>0.04349173803835847</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04063949176983993</v>
+        <v>0.04063949176983994</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03573899811546456</v>
+        <v>0.03573899811546453</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04088730631483446</v>
+        <v>0.04088730631483445</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04460832456398388</v>
+        <v>0.04460832456398382</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05590671036686339</v>
+        <v>0.05590671036686343</v>
       </c>
       <c r="K8" t="n">
-        <v>0.039930634209696</v>
+        <v>0.03993063420969598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02797401485805466</v>
+        <v>0.0279740148580546</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0522142111126252</v>
+        <v>0.05221421111262515</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03248285147979051</v>
+        <v>0.03248285147979054</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0413977373660956</v>
+        <v>0.04139773736609563</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06020185862290678</v>
+        <v>0.06020185862290674</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05497154984004508</v>
+        <v>0.05497154984004506</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04610417398048185</v>
+        <v>0.0461041739804819</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05125248217983186</v>
+        <v>0.05125248217983184</v>
       </c>
       <c r="I9" t="n">
         <v>0.05497350042900118</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06627108021867344</v>
+        <v>0.06627108021867342</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05184718986812424</v>
+        <v>0.05184718986812428</v>
       </c>
       <c r="L9" t="n">
         <v>0.03405505089942439</v>
@@ -1706,7 +1706,7 @@
         <v>0.1395165209271445</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1861955145728773</v>
+        <v>0.1861955145728772</v>
       </c>
       <c r="D2" t="n">
         <v>0.1394193587199891</v>
@@ -1715,13 +1715,13 @@
         <v>0.2062580748412107</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2062580601548897</v>
+        <v>0.2062580601548895</v>
       </c>
       <c r="G2" t="n">
         <v>0.1391730146240009</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1398496625201453</v>
+        <v>0.1398496625201452</v>
       </c>
       <c r="I2" t="n">
         <v>0.1392100332569564</v>
@@ -1730,7 +1730,7 @@
         <v>0.1543718052934508</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1644656538749742</v>
+        <v>0.1644656538749741</v>
       </c>
       <c r="L2" t="n">
         <v>0.1384823690891003</v>
@@ -1743,22 +1743,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1516402928266306</v>
+        <v>0.1516402928266307</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2222027687531175</v>
+        <v>0.2222027687531174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1509306984262632</v>
+        <v>0.150930698426263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2601192248849177</v>
+        <v>0.2601192248849171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2601192101985964</v>
+        <v>0.260119210198596</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1491890401585999</v>
+        <v>0.1491890401585998</v>
       </c>
       <c r="H3" t="n">
         <v>0.1540860413015714</v>
@@ -1767,13 +1767,13 @@
         <v>0.1494443618220662</v>
       </c>
       <c r="J3" t="n">
-        <v>0.18167000771668</v>
+        <v>0.1816700077166802</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1914062536685993</v>
+        <v>0.1914062536685991</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1443717310253963</v>
+        <v>0.1443717310253962</v>
       </c>
     </row>
     <row r="4">
@@ -1783,22 +1783,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.02229566482425933</v>
+        <v>0.02229566482425938</v>
       </c>
       <c r="C4" t="n">
-        <v>0.008576949365356301</v>
+        <v>0.008576949365356299</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02119817299761605</v>
+        <v>0.02119817299761592</v>
       </c>
       <c r="E4" t="n">
         <v>0.01930507073282422</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01930507073282422</v>
+        <v>0.01930507073282424</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01848864823946991</v>
+        <v>0.0184886482394699</v>
       </c>
       <c r="H4" t="n">
         <v>0.02606315995668545</v>
@@ -1807,13 +1807,13 @@
         <v>0.0193204993701022</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03360563101616958</v>
+        <v>0.03360563101616961</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01940238093695291</v>
+        <v>0.0194023809369529</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01077122162303009</v>
+        <v>0.01077122162302999</v>
       </c>
     </row>
     <row r="5">
@@ -1823,34 +1823,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.3120919819314838</v>
+        <v>0.3120919819314836</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0770396661153262</v>
+        <v>0.07703966611532638</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2843153870209972</v>
+        <v>0.2843153870209978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2469370945708571</v>
+        <v>0.2469370945708573</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2469370945708571</v>
+        <v>0.2469370945708573</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2437309278595795</v>
+        <v>0.2437309278595788</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4127484510373059</v>
+        <v>0.4127484510373057</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2469372191318755</v>
+        <v>0.2469372191318754</v>
       </c>
       <c r="J5" t="n">
         <v>0.5198675231416202</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2547831394019977</v>
+        <v>0.2547831394019976</v>
       </c>
       <c r="L5" t="n">
         <v>0.1222817034157058</v>
@@ -1869,25 +1869,25 @@
         <v>1.777440446935831</v>
       </c>
       <c r="D6" t="n">
-        <v>6.751584657428268</v>
+        <v>6.751584657428255</v>
       </c>
       <c r="E6" t="n">
         <v>1.108185768942862</v>
       </c>
       <c r="F6" t="n">
-        <v>1.788223725618657</v>
+        <v>1.788223725618656</v>
       </c>
       <c r="G6" t="n">
-        <v>6.748792333171367</v>
+        <v>6.748792333171361</v>
       </c>
       <c r="H6" t="n">
-        <v>6.757123733874685</v>
+        <v>6.757123733874683</v>
       </c>
       <c r="I6" t="n">
-        <v>1.788242623687138</v>
+        <v>1.788242623687139</v>
       </c>
       <c r="J6" t="n">
-        <v>1.89257666949382</v>
+        <v>1.892576669493821</v>
       </c>
       <c r="K6" t="n">
         <v>1.788308739446628</v>
@@ -1903,13 +1903,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02434356438618391</v>
+        <v>0.02434356438618386</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01093459663477718</v>
+        <v>0.01093459663477717</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02324600538102059</v>
+        <v>0.02324600538102053</v>
       </c>
       <c r="E7" t="n">
         <v>0.02136610331845873</v>
@@ -1918,22 +1918,22 @@
         <v>0.02136610331845873</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02053654780139448</v>
+        <v>0.02053654780139438</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02811105951861002</v>
+        <v>0.02811105951860995</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02136839893202675</v>
+        <v>0.02136839893202674</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03565353057809417</v>
+        <v>0.03565353057809414</v>
       </c>
       <c r="K7" t="n">
-        <v>0.02145028049887746</v>
+        <v>0.02145028049887736</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01281912118495464</v>
+        <v>0.01281912118495461</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02615172730008471</v>
+        <v>0.02615172730008482</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01578808815526087</v>
+        <v>0.01578808815526084</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02873272503225022</v>
+        <v>0.02873272503225012</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02538865184181406</v>
+        <v>0.02538865184181412</v>
       </c>
       <c r="F8" t="n">
         <v>0.02327175886861864</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02539144091915212</v>
+        <v>0.02539144091915204</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03296595263638979</v>
+        <v>0.03296595263638978</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02622329204978438</v>
+        <v>0.02622329204978436</v>
       </c>
       <c r="J8" t="n">
         <v>0.04050902245937642</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02320184883559838</v>
+        <v>0.02320184883559834</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0208565787583153</v>
+        <v>0.02085657875831526</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03203618420609768</v>
+        <v>0.03203618420609754</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02158069018337476</v>
+        <v>0.02158069018337477</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03389216896921713</v>
+        <v>0.0338921689692171</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03542261362137261</v>
+        <v>0.0354226136213726</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03201436556462117</v>
+        <v>0.03201436556462115</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03118264134999206</v>
+        <v>0.031182641349992</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03875715306720761</v>
+        <v>0.03875715306720755</v>
       </c>
       <c r="I9" t="n">
         <v>0.03201449248062432</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04629962412669173</v>
+        <v>0.04629962412669174</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03038512097324798</v>
+        <v>0.03038512097324791</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02346521473355225</v>
+        <v>0.0234652147335522</v>
       </c>
     </row>
   </sheetData>
@@ -2099,19 +2099,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1380095999779861</v>
+        <v>0.1380095999779863</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1850493322574388</v>
+        <v>0.1850493322574386</v>
       </c>
       <c r="D2" t="n">
         <v>0.1388272268523764</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2042502645692883</v>
+        <v>0.2042502645692882</v>
       </c>
       <c r="F2" t="n">
-        <v>0.204250244626598</v>
+        <v>0.2042502446265982</v>
       </c>
       <c r="G2" t="n">
         <v>0.1380990219714503</v>
@@ -2123,7 +2123,7 @@
         <v>0.1376701123018704</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1524492261481283</v>
+        <v>0.1524492261481284</v>
       </c>
       <c r="K2" t="n">
         <v>0.1623793939828282</v>
@@ -2142,16 +2142,16 @@
         <v>0.1457466200268941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2205142216242967</v>
+        <v>0.2205142216242965</v>
       </c>
       <c r="D3" t="n">
         <v>0.1515611387645114</v>
       </c>
       <c r="E3" t="n">
-        <v>0.253224201963405</v>
+        <v>0.2532242019634049</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2532241820207146</v>
+        <v>0.2532241820207151</v>
       </c>
       <c r="G3" t="n">
         <v>0.1463838526027302</v>
@@ -2160,13 +2160,13 @@
         <v>0.1512670029944093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1433216537646501</v>
+        <v>0.14332165376465</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1765608712802064</v>
+        <v>0.1765608712802065</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1844671198162784</v>
+        <v>0.1844671198162785</v>
       </c>
       <c r="L3" t="n">
         <v>0.142339372573392</v>
@@ -2182,34 +2182,34 @@
         <v>0.01211863948833552</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00593185289199596</v>
+        <v>0.005931852891995968</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02135411116151738</v>
+        <v>0.02135411116151736</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008637942881690753</v>
+        <v>0.008637942881690756</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008637942881690758</v>
+        <v>0.008637942881690754</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01319892032395166</v>
+        <v>0.01319892032395131</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0207714141429022</v>
+        <v>0.02077141414290218</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008751389548753772</v>
+        <v>0.008751389548753754</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02646636643958675</v>
+        <v>0.02646636643958676</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009025269769755807</v>
+        <v>0.009025269769754941</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006720824168870257</v>
+        <v>0.006720824168870244</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.1541483258380568</v>
+        <v>0.1541483258380571</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04960511243277117</v>
+        <v>0.04960511243277123</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3066490176657545</v>
+        <v>0.3066490176657539</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08574454645259103</v>
+        <v>0.08574454645259115</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08574454645259103</v>
+        <v>0.08574454645259115</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1715770432848085</v>
+        <v>0.1715770432848036</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3337638375939319</v>
+        <v>0.3337638375939326</v>
       </c>
       <c r="I5" t="n">
-        <v>0.08574347177495699</v>
+        <v>0.08574347177495674</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4131498883590679</v>
+        <v>0.413149888359068</v>
       </c>
       <c r="K5" t="n">
-        <v>0.09746119562337477</v>
+        <v>0.09746119562336857</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06601993286254852</v>
+        <v>0.06601993286254845</v>
       </c>
     </row>
     <row r="6">
@@ -2262,34 +2262,34 @@
         <v>1.780637009698386</v>
       </c>
       <c r="C6" t="n">
-        <v>1.774445928802275</v>
+        <v>1.774445928802276</v>
       </c>
       <c r="D6" t="n">
         <v>1.790155316074383</v>
       </c>
       <c r="E6" t="n">
-        <v>1.097115511928608</v>
+        <v>1.097115511928609</v>
       </c>
       <c r="F6" t="n">
-        <v>1.777234875751854</v>
+        <v>1.777234875751853</v>
       </c>
       <c r="G6" t="n">
         <v>6.742686627778162</v>
       </c>
       <c r="H6" t="n">
-        <v>6.750965256820641</v>
+        <v>6.750965256820646</v>
       </c>
       <c r="I6" t="n">
-        <v>6.738239097002976</v>
+        <v>6.738239097002968</v>
       </c>
       <c r="J6" t="n">
-        <v>6.756396807921612</v>
+        <v>6.756396807921609</v>
       </c>
       <c r="K6" t="n">
-        <v>1.777420668654959</v>
+        <v>1.777420668654782</v>
       </c>
       <c r="L6" t="n">
-        <v>1.775213659526593</v>
+        <v>1.775213659526592</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01369550115470132</v>
+        <v>0.01369550115470135</v>
       </c>
       <c r="C7" t="n">
-        <v>0.007732468768409089</v>
+        <v>0.00773246876840907</v>
       </c>
       <c r="D7" t="n">
         <v>0.02293090048544136</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01031357939966148</v>
+        <v>0.01031357939966143</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01031357939966148</v>
+        <v>0.01031357939966143</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01477578199031748</v>
+        <v>0.01477578199031718</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02234827580926802</v>
+        <v>0.02234827580926804</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0103282512151196</v>
+        <v>0.01032825121511962</v>
       </c>
       <c r="J7" t="n">
-        <v>0.02804322810595258</v>
+        <v>0.02804322810595253</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01060213143612163</v>
+        <v>0.01060213143612137</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00829768583523607</v>
+        <v>0.00829768583523602</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01516713341211528</v>
+        <v>0.01516713341211524</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01159605550048766</v>
+        <v>0.0115960555004876</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02730804604678851</v>
+        <v>0.02730804604678837</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01353628992418294</v>
+        <v>0.01353628992418285</v>
       </c>
       <c r="F8" t="n">
         <v>0.01186788845485686</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0186538624899753</v>
+        <v>0.01865386248997497</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02622635630895332</v>
+        <v>0.02622635630895329</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01420633171477746</v>
+        <v>0.01420633171477738</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03192178153677568</v>
+        <v>0.03192178153677563</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0120290626824044</v>
+        <v>0.01202906268240389</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01468950274336676</v>
+        <v>0.01468950274336664</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01906413846253212</v>
+        <v>0.01906413846253214</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01522625615677012</v>
+        <v>0.01522625615677007</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03042476182375058</v>
+        <v>0.03042476182375039</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0202754888530816</v>
+        <v>0.0202754888530815</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01782311007018946</v>
+        <v>0.01782311007018943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02226956937867854</v>
+        <v>0.02226956937867827</v>
       </c>
       <c r="H9" t="n">
-        <v>0.02984206319762909</v>
+        <v>0.02984206319762891</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01782203860348065</v>
+        <v>0.01782203860348054</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03553701549431362</v>
+        <v>0.03553701549431348</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0168146429399645</v>
+        <v>0.01681464293996324</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01579147322359712</v>
+        <v>0.01579147322359709</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1407358286884038</v>
+        <v>0.1407358286884048</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1875273748556359</v>
+        <v>0.1875273748556361</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1395253811570412</v>
+        <v>0.1395253811570394</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2089829807603862</v>
+        <v>0.2089829807603849</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2089829722593713</v>
+        <v>0.2089829722593691</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1398317012363062</v>
+        <v>0.1398317012363071</v>
       </c>
       <c r="H2" t="n">
-        <v>0.142337823218478</v>
+        <v>0.1423378232184764</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1403830721037047</v>
+        <v>0.1403830721037015</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1570992124612353</v>
+        <v>0.1570992124612358</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1671877552825347</v>
+        <v>0.1671877552825327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1384443692684749</v>
+        <v>0.1384443692684734</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1582844195574591</v>
+        <v>0.1582844195574588</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2234282716156251</v>
+        <v>0.2234282716156242</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1496338267412929</v>
+        <v>0.1496338267412899</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2689869904345643</v>
+        <v>0.268986990434559</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2689869819335493</v>
+        <v>0.2689869819335484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1518336929225964</v>
+        <v>0.1518336929225931</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1697552135995485</v>
+        <v>0.1697552135995453</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1557505080944301</v>
+        <v>0.1557505080944251</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1901198500428224</v>
+        <v>0.1901198500428204</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1996945335436249</v>
+        <v>0.199694533543622</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1421130860690435</v>
+        <v>0.1421130860690404</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03601008743637744</v>
+        <v>0.03601008743637515</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01062384245425472</v>
+        <v>0.01062384245425238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02233752573626261</v>
+        <v>0.02233752573626076</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03259030752101746</v>
+        <v>0.0325903075210096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03259030752101746</v>
+        <v>0.03259030752100848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02587357649177036</v>
+        <v>0.02587357649176922</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05391012617825294</v>
+        <v>0.05391012617825073</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03253273460038468</v>
+        <v>0.03253273460038435</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04589724037616965</v>
+        <v>0.04589724037616619</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03141216882729088</v>
+        <v>0.03141216882728626</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01041894661541993</v>
+        <v>0.01041894661541849</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5535749114634223</v>
+        <v>0.553574911463417</v>
       </c>
       <c r="C5" t="n">
-        <v>0.09299385646142469</v>
+        <v>0.09299385646143041</v>
       </c>
       <c r="D5" t="n">
-        <v>0.292700002543467</v>
+        <v>0.2927000025434767</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4709975254931988</v>
+        <v>0.4709975254931949</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4709975254931988</v>
+        <v>0.4709975254931949</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3646574634048955</v>
+        <v>0.3646574634048951</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9652547035355169</v>
+        <v>0.9652547035355132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4709989699210033</v>
+        <v>0.4709989699209952</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7498682545191453</v>
+        <v>0.7498682545191518</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4568356685103546</v>
+        <v>0.456835668510358</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09043649541579976</v>
+        <v>0.09043649541579782</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.904098493198749</v>
+        <v>1.904098493198748</v>
       </c>
       <c r="C6" t="n">
-        <v>1.878496304308208</v>
+        <v>1.878496304308207</v>
       </c>
       <c r="D6" t="n">
-        <v>1.890191284604096</v>
+        <v>1.890191284604095</v>
       </c>
       <c r="E6" t="n">
-        <v>1.182742017669176</v>
+        <v>1.182742017669171</v>
       </c>
       <c r="F6" t="n">
-        <v>1.900611877680745</v>
+        <v>1.900611877680739</v>
       </c>
       <c r="G6" t="n">
         <v>1.893961982254141</v>
       </c>
       <c r="H6" t="n">
-        <v>7.161540400353768</v>
+        <v>7.161540400353775</v>
       </c>
       <c r="I6" t="n">
-        <v>7.139196445257922</v>
+        <v>7.139196445257912</v>
       </c>
       <c r="J6" t="n">
-        <v>2.009082858826294</v>
+        <v>2.009082858826292</v>
       </c>
       <c r="K6" t="n">
         <v>1.899569939721661</v>
       </c>
       <c r="L6" t="n">
-        <v>1.878359239355194</v>
+        <v>1.878359239355189</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03882064919887877</v>
+        <v>0.03882064919888466</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01384976764886997</v>
+        <v>0.01384976764886334</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02514801539042229</v>
+        <v>0.02514801539041491</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0353432530821973</v>
+        <v>0.03534325308218702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0353432530821973</v>
+        <v>0.03534325308218702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0286841382542717</v>
+        <v>0.02868413825426717</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05672068794075435</v>
+        <v>0.05672068794075424</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03534329636288602</v>
+        <v>0.03534329636287871</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04870780213867099</v>
+        <v>0.04870780213866329</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03422273058979221</v>
+        <v>0.03422273058979033</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01322950837792127</v>
+        <v>0.01322950837792118</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04118402711230784</v>
+        <v>0.04118402711230729</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02028329234143524</v>
+        <v>0.02028329234143595</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03242290628643418</v>
+        <v>0.03242290628642645</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04066259199204697</v>
+        <v>0.04066259199203918</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0378350557972402</v>
+        <v>0.03783505579723847</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03511544541327974</v>
+        <v>0.0351154454132843</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0631519950997854</v>
+        <v>0.06315199509978327</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04177460352189409</v>
+        <v>0.04177460352188873</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05513990875456161</v>
+        <v>0.05513990875456119</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03651054462966985</v>
+        <v>0.03651054462966603</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02391010778147807</v>
+        <v>0.02391010778147951</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05080364623131949</v>
+        <v>0.05080364623131792</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03026369978747556</v>
+        <v>0.0302636997874743</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04156201970880971</v>
+        <v>0.04156201970880215</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05686898136595534</v>
+        <v>0.05686898136594432</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05175577772662546</v>
+        <v>0.05175577772662213</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04509807039287729</v>
+        <v>0.04509807039287341</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07313462007935992</v>
+        <v>0.07313462007935935</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05175722850149164</v>
+        <v>0.05175722850149084</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06512173427727661</v>
+        <v>0.06512173427727236</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04806936155630868</v>
+        <v>0.04806936155630702</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02964344051652689</v>
+        <v>0.02964344051652354</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1351864179340257</v>
+        <v>0.1351864179340258</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1857609533439978</v>
+        <v>0.1857609533439979</v>
       </c>
       <c r="D2" t="n">
         <v>0.135392943832648</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2054868522324847</v>
+        <v>0.2054868522324851</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2054868402916271</v>
+        <v>0.2054868402916274</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1350299968339786</v>
+        <v>0.1350299968339785</v>
       </c>
       <c r="H2" t="n">
         <v>0.1403355328460227</v>
       </c>
       <c r="I2" t="n">
-        <v>0.134742698377938</v>
+        <v>0.1347426983779381</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1539009050704105</v>
+        <v>0.1539009050704104</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1634473982267688</v>
+        <v>0.163447398226769</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1339583721132143</v>
+        <v>0.1339583721132142</v>
       </c>
     </row>
     <row r="3">
@@ -2931,34 +2931,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1434794166621348</v>
+        <v>0.1434794166621349</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2205188548552463</v>
+        <v>0.2205188548552464</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1449350628420477</v>
+        <v>0.1449350628420476</v>
       </c>
       <c r="E3" t="n">
         <v>0.2570832200100877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2570832080692297</v>
+        <v>0.2570832080692301</v>
       </c>
       <c r="G3" t="n">
         <v>0.1423627520800683</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1801168739572833</v>
+        <v>0.1801168739572834</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1403072471829507</v>
+        <v>0.1403072471829508</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1789476986025908</v>
+        <v>0.1789476986025907</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1877525700877754</v>
+        <v>0.1877525700877755</v>
       </c>
       <c r="L3" t="n">
         <v>0.1348436615274745</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01976163016818128</v>
+        <v>0.01976163016818132</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006062840823982305</v>
+        <v>0.006062840823982298</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02209443519972746</v>
+        <v>0.02209443519972754</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01515179859742495</v>
+        <v>0.01515179859742496</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01515179859742495</v>
+        <v>0.01515179859742496</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01806509560610291</v>
+        <v>0.0180650956061028</v>
       </c>
       <c r="H4" t="n">
-        <v>0.07733186658218236</v>
+        <v>0.07733186658218241</v>
       </c>
       <c r="I4" t="n">
         <v>0.01521801860090017</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0291575592464833</v>
+        <v>0.02915755924648328</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01488352025537268</v>
+        <v>0.01488352025537277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.006107850838933462</v>
+        <v>0.006107850838933545</v>
       </c>
     </row>
     <row r="5">
@@ -3014,34 +3014,34 @@
         <v>0.271004067229403</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03775109033464192</v>
+        <v>0.0377510903346419</v>
       </c>
       <c r="D5" t="n">
-        <v>0.302759615860651</v>
+        <v>0.3027596158606505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1800699924198091</v>
+        <v>0.1800699924198093</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1800699924198091</v>
+        <v>0.1800699924198093</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2396799651312062</v>
+        <v>0.2396799651312077</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39768219912357</v>
+        <v>1.397682199123572</v>
       </c>
       <c r="I5" t="n">
         <v>0.1800692747967146</v>
       </c>
       <c r="J5" t="n">
-        <v>0.443849638869353</v>
+        <v>0.4438496388693529</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1808915719423253</v>
+        <v>0.180891571942326</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03504011873104655</v>
+        <v>0.03504011873104673</v>
       </c>
     </row>
     <row r="6">
@@ -3051,34 +3051,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.788591326163127</v>
+        <v>1.788591326163126</v>
       </c>
       <c r="C6" t="n">
         <v>1.774843429140964</v>
       </c>
       <c r="D6" t="n">
-        <v>6.752495929491246</v>
+        <v>6.75249592949125</v>
       </c>
       <c r="E6" t="n">
-        <v>1.103885766974776</v>
+        <v>1.103885766974777</v>
       </c>
       <c r="F6" t="n">
-        <v>1.784012115953953</v>
+        <v>1.784012115953954</v>
       </c>
       <c r="G6" t="n">
         <v>1.786894791601048</v>
       </c>
       <c r="H6" t="n">
-        <v>6.809200430024012</v>
+        <v>6.809200430024014</v>
       </c>
       <c r="I6" t="n">
-        <v>6.745473103479606</v>
+        <v>6.745473103479601</v>
       </c>
       <c r="J6" t="n">
-        <v>6.759931983494837</v>
+        <v>6.759931983494842</v>
       </c>
       <c r="K6" t="n">
-        <v>1.783592014314607</v>
+        <v>1.783592014314594</v>
       </c>
       <c r="L6" t="n">
         <v>1.774862632834323</v>
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02187826274591453</v>
+        <v>0.02187826274591416</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00856112216454505</v>
+        <v>0.008561122164545047</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0242110211544451</v>
+        <v>0.02421102115444504</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01733141808479156</v>
+        <v>0.01733141808479157</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01733141808479156</v>
+        <v>0.01733141808479157</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02018172818383621</v>
+        <v>0.02018172818383609</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07944849915991552</v>
+        <v>0.0794484991599153</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01733465117863346</v>
+        <v>0.01733465117863348</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03127419182421656</v>
+        <v>0.03127419182421616</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01700015283310597</v>
+        <v>0.01700015283310562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.008224483416666754</v>
+        <v>0.008224483416667041</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02379226422805628</v>
+        <v>0.02379226422805622</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01367356535639065</v>
+        <v>0.01367356535639063</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02999047256130519</v>
+        <v>0.0299904725613051</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02157254588369865</v>
+        <v>0.02157254588369869</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0193485252630377</v>
+        <v>0.01934852526303774</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02529727225600057</v>
+        <v>0.02529727225600049</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08456404323228442</v>
+        <v>0.08456404323228421</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02245019525079786</v>
+        <v>0.02245019525079785</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03639036508426661</v>
+        <v>0.03639036508426633</v>
       </c>
       <c r="K8" t="n">
         <v>0.01885468401857267</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01668430642628105</v>
+        <v>0.01668430642628108</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02918835290961298</v>
+        <v>0.02918835290961308</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01875701970938131</v>
+        <v>0.01875701970938133</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03440695646086009</v>
+        <v>0.03440695646086022</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03086140035880803</v>
+        <v>0.03086140035880805</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0275312515417337</v>
+        <v>0.02753125154173372</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03037762572867249</v>
+        <v>0.03037762572867245</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08964439670475186</v>
+        <v>0.08964439670475217</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02753054872346974</v>
+        <v>0.02753054872346976</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04147008936905284</v>
+        <v>0.04147008936905305</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0255239985207855</v>
+        <v>0.02552399852078558</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01842038096150304</v>
+        <v>0.01842038096150303</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1311442780659153</v>
+        <v>0.1311442780659154</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1847344005448989</v>
+        <v>0.184734400544899</v>
       </c>
       <c r="D2" t="n">
         <v>0.1320823014756923</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2038377042649967</v>
+        <v>0.2038377042649968</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2038376899974067</v>
+        <v>0.2038376899974069</v>
       </c>
       <c r="G2" t="n">
         <v>0.1312852272460565</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1352282249018053</v>
+        <v>0.1352282249018054</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1308132784392819</v>
+        <v>0.1308132784392818</v>
       </c>
       <c r="J2" t="n">
         <v>0.1516225070422605</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1617900787396571</v>
+        <v>0.161790078739657</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1305939707188783</v>
+        <v>0.1305939707188785</v>
       </c>
     </row>
     <row r="3">
@@ -3330,34 +3330,34 @@
         <v>0.1335000650997541</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2192117274100929</v>
+        <v>0.2192117274100932</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1401741870103721</v>
+        <v>0.1401741870103722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.251677054219188</v>
+        <v>0.2516770542191878</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2516770399515981</v>
+        <v>0.2516770399515978</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1345049602140584</v>
+        <v>0.1345049602140585</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1625503764288466</v>
+        <v>0.1625503764288467</v>
       </c>
       <c r="I3" t="n">
         <v>0.1311370389874921</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1708361068355516</v>
+        <v>0.1708361068355518</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1821953630544569</v>
+        <v>0.1821953630544572</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1296500958225889</v>
+        <v>0.1296500958225891</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0098800224342578</v>
+        <v>0.009880022434257535</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003761230028049852</v>
+        <v>0.003761230028049784</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02047542835977605</v>
+        <v>0.02047542835977585</v>
       </c>
       <c r="E4" t="n">
-        <v>0.006408234082052671</v>
+        <v>0.006408234082052662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.006408234082052672</v>
+        <v>0.00640823408205266</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01154132712958626</v>
+        <v>0.01154132712958568</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0555582961973519</v>
+        <v>0.05555829619735213</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006602150244301039</v>
+        <v>0.006602150244301135</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01714044625600903</v>
+        <v>0.01714044625600886</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00598841761582361</v>
+        <v>0.005988417615823588</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003800284599575912</v>
+        <v>0.00380028459957606</v>
       </c>
     </row>
     <row r="5">
@@ -3407,34 +3407,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.116540321931672</v>
+        <v>0.1165403219316717</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01686524249459576</v>
+        <v>0.01686524249459575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2932632053067399</v>
+        <v>0.29326320530674</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05053094665395885</v>
+        <v>0.05053094665395859</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05053094665395885</v>
+        <v>0.05053094665395855</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1442156690130631</v>
+        <v>0.1442156690130615</v>
       </c>
       <c r="H5" t="n">
-        <v>1.001362649353192</v>
+        <v>1.001362649353191</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05052975580256103</v>
+        <v>0.05052975580256085</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2483130554583715</v>
+        <v>0.248313055458372</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04719359663658881</v>
+        <v>0.04719359663658886</v>
       </c>
       <c r="L5" t="n">
         <v>0.01086615076380221</v>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739303506813126</v>
+        <v>6.739303506813131</v>
       </c>
       <c r="C6" t="n">
-        <v>1.772350466841374</v>
+        <v>1.772350466841373</v>
       </c>
       <c r="D6" t="n">
         <v>1.789222888413735</v>
@@ -3459,25 +3459,25 @@
         <v>1.094849763463062</v>
       </c>
       <c r="F6" t="n">
-        <v>1.77501264396228</v>
+        <v>1.775012643962281</v>
       </c>
       <c r="G6" t="n">
-        <v>6.740964811508469</v>
+        <v>6.740964811508468</v>
       </c>
       <c r="H6" t="n">
         <v>1.824298175278179</v>
       </c>
       <c r="I6" t="n">
-        <v>6.736025634623179</v>
+        <v>6.736025634623188</v>
       </c>
       <c r="J6" t="n">
-        <v>1.875601525052564</v>
+        <v>1.875601525052566</v>
       </c>
       <c r="K6" t="n">
         <v>1.774255648193969</v>
       </c>
       <c r="L6" t="n">
-        <v>1.772212375805203</v>
+        <v>1.772212375805204</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01149052442027313</v>
+        <v>0.01149052442027312</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00579823059753149</v>
+        <v>0.005798230597531417</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02208590899985858</v>
+        <v>0.02208590899985875</v>
       </c>
       <c r="E7" t="n">
-        <v>0.008180063556450672</v>
+        <v>0.008180063556450661</v>
       </c>
       <c r="F7" t="n">
-        <v>0.008180063556450673</v>
+        <v>0.008180063556450684</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01315182911560125</v>
+        <v>0.01315182911560127</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0571687981833675</v>
+        <v>0.05716879818336767</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008212652230316728</v>
+        <v>0.008212652230316723</v>
       </c>
       <c r="J7" t="n">
-        <v>0.01875094824202446</v>
+        <v>0.0187509482420244</v>
       </c>
       <c r="K7" t="n">
-        <v>0.007598919601838948</v>
+        <v>0.007598919601839175</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005410786585591436</v>
+        <v>0.005410786585591625</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01308830410969025</v>
+        <v>0.0130883041096904</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009962114744319375</v>
+        <v>0.009962114744319362</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02682027651819461</v>
+        <v>0.0268202765181947</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01167060681917115</v>
+        <v>0.01167060681917116</v>
       </c>
       <c r="F8" t="n">
-        <v>0.009873833144916458</v>
+        <v>0.009873833144916466</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01734748809425768</v>
+        <v>0.01734748809425781</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06136445716231013</v>
+        <v>0.06136445716231025</v>
       </c>
       <c r="I8" t="n">
         <v>0.01240831120897324</v>
       </c>
       <c r="J8" t="n">
-        <v>0.02294711777119401</v>
+        <v>0.02294711777119427</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009148442350350436</v>
+        <v>0.009148442350350608</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0123201477061995</v>
+        <v>0.01232014770619971</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01631089463980989</v>
+        <v>0.01631089463980992</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01264056773757105</v>
+        <v>0.01264056773757107</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02892826053790524</v>
+        <v>0.02892826053790562</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01738946652414954</v>
+        <v>0.01738946652414958</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01505616872538303</v>
+        <v>0.01505616872538305</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01999416625564071</v>
+        <v>0.01999416625564088</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06401113532340724</v>
+        <v>0.06401113532340721</v>
       </c>
       <c r="I9" t="n">
         <v>0.0150549893703563</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02559328538206392</v>
+        <v>0.02559328538206403</v>
       </c>
       <c r="K9" t="n">
         <v>0.01326971824499258</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01225312372563114</v>
+        <v>0.01225312372563121</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1389093270834231</v>
+        <v>0.1389093270834229</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1869293637966171</v>
+        <v>0.1869293637966172</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1380680257897933</v>
+        <v>0.138068025789793</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2086854499063055</v>
+        <v>0.2086854499063052</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2086854433419983</v>
+        <v>0.208685443341998</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1381788980798321</v>
+        <v>0.1381788980798315</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1405692565580535</v>
+        <v>0.1405692565580534</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1384359685789946</v>
+        <v>0.1384359685789941</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1579552666804541</v>
+        <v>0.1579552666804539</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1670161556565128</v>
+        <v>0.1670161556565127</v>
       </c>
       <c r="L2" t="n">
-        <v>0.13659613867882</v>
+        <v>0.1365961386788196</v>
       </c>
     </row>
     <row r="3">
@@ -3723,34 +3723,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1549378604162769</v>
+        <v>0.1549378604162768</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2220112541957051</v>
+        <v>0.2220112541957102</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1489169860319089</v>
+        <v>0.148916986031909</v>
       </c>
       <c r="E3" t="n">
-        <v>0.267504447105756</v>
+        <v>0.2675044471057557</v>
       </c>
       <c r="F3" t="n">
-        <v>0.267504440541449</v>
+        <v>0.2675044405414487</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1497261387466142</v>
+        <v>0.1497261387466141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1668341311364151</v>
+        <v>0.1668341311364152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1515450412814565</v>
+        <v>0.1515450412814564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1953763308679589</v>
+        <v>0.1953763308679593</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1993599686906884</v>
+        <v>0.1993599686906888</v>
       </c>
       <c r="L3" t="n">
         <v>0.1386282120148054</v>
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03535563174397727</v>
+        <v>0.03535563174397705</v>
       </c>
       <c r="C4" t="n">
-        <v>0.009737675013889623</v>
+        <v>0.009737675013893887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02585274661471082</v>
+        <v>0.02585274661471124</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03051766819780702</v>
+        <v>0.03051766819780692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03051766819780704</v>
+        <v>0.03051766819780691</v>
       </c>
       <c r="G4" t="n">
-        <v>0.027179155347309</v>
+        <v>0.02717915534730921</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0539320359990069</v>
+        <v>0.05393203599900701</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03050270621133673</v>
+        <v>0.03050270621133699</v>
       </c>
       <c r="J4" t="n">
-        <v>0.05383344985720769</v>
+        <v>0.05383344985720801</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03133500570571633</v>
+        <v>0.03133500570571653</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009555426172240505</v>
+        <v>0.009555426172240257</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.5424090235832203</v>
+        <v>0.5424090235832195</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07810064277688929</v>
+        <v>0.07810064277671142</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3564829378590215</v>
+        <v>0.3564829378590217</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4354612147990624</v>
+        <v>0.4354612147990626</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4354612147990624</v>
+        <v>0.4354612147990626</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3896394709569964</v>
+        <v>0.3896394709569945</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9667130491368444</v>
+        <v>0.9667130491368433</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4354618959877379</v>
+        <v>0.4354618959877374</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8999398181486725</v>
+        <v>0.8999398181486746</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4563497215382932</v>
+        <v>0.4563497215382891</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07373873834775604</v>
+        <v>0.07373873834775589</v>
       </c>
     </row>
     <row r="6">
@@ -3843,13 +3843,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.903500385984301</v>
+        <v>1.9035003859843</v>
       </c>
       <c r="C6" t="n">
-        <v>1.877638655450762</v>
+        <v>1.877638655450751</v>
       </c>
       <c r="D6" t="n">
-        <v>1.893867451482709</v>
+        <v>1.893867451482708</v>
       </c>
       <c r="E6" t="n">
         <v>1.180672842932283</v>
@@ -3858,22 +3858,22 @@
         <v>1.898622273676799</v>
       </c>
       <c r="G6" t="n">
-        <v>1.895323909587635</v>
+        <v>1.895323909587634</v>
       </c>
       <c r="H6" t="n">
-        <v>7.161677068484738</v>
+        <v>7.161677068484741</v>
       </c>
       <c r="I6" t="n">
-        <v>1.898647460451663</v>
+        <v>1.898647460451661</v>
       </c>
       <c r="J6" t="n">
         <v>2.017129188393661</v>
       </c>
       <c r="K6" t="n">
-        <v>1.899532783954711</v>
+        <v>1.899532783954748</v>
       </c>
       <c r="L6" t="n">
-        <v>1.877551018962962</v>
+        <v>1.877551018962963</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.03822740130173174</v>
+        <v>0.03822740130173136</v>
       </c>
       <c r="C7" t="n">
-        <v>0.013048152929652</v>
+        <v>0.01304815292964903</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02872444442337524</v>
+        <v>0.02872444442337554</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0333727216253688</v>
+        <v>0.03337272162536875</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03337272162536881</v>
+        <v>0.03337272162536875</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03005092490506319</v>
+        <v>0.03005092490506347</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05680380555676132</v>
+        <v>0.05680380555676125</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03337447576909115</v>
+        <v>0.03337447576909128</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05670521941496202</v>
+        <v>0.0567052194149622</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03420677526347048</v>
+        <v>0.03420677526347071</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01242719572999472</v>
+        <v>0.01242719572999456</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.04064394549367862</v>
+        <v>0.04064394549367849</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01961618453294159</v>
+        <v>0.01961618453294255</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0361535436195797</v>
+        <v>0.03615354361957981</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03880640129480677</v>
+        <v>0.03880640129480679</v>
       </c>
       <c r="F8" t="n">
-        <v>0.03592134139473486</v>
+        <v>0.03592134139473483</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03661908727764565</v>
+        <v>0.03661908727764557</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06337196792936824</v>
+        <v>0.06337196792936826</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03994263814167359</v>
+        <v>0.03994263814167338</v>
       </c>
       <c r="J8" t="n">
-        <v>0.06327419769176046</v>
+        <v>0.06327419769176013</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03654620101692677</v>
+        <v>0.0365462010169278</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02333207043780073</v>
+        <v>0.02333207043780091</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05048902535650612</v>
+        <v>0.05048902535650584</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02983948934336739</v>
+        <v>0.02983948934336248</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04551585362484115</v>
+        <v>0.04551585362484149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05539231577156552</v>
+        <v>0.0553923157715652</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05016512445149549</v>
+        <v>0.05016512445149507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0468422613187772</v>
+        <v>0.04684226131877699</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07359514197047472</v>
+        <v>0.07359514197047468</v>
       </c>
       <c r="I9" t="n">
-        <v>0.05016581218280441</v>
+        <v>0.05016581218280475</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07349655582867533</v>
+        <v>0.07349655582867588</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04837357898371902</v>
+        <v>0.04837357898371901</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02921853214370881</v>
+        <v>0.02921853214370809</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1224904751126655</v>
+        <v>0.1224904751126652</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1845599617795874</v>
+        <v>0.184559961779587</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1230780504176428</v>
+        <v>0.1230780504176426</v>
       </c>
       <c r="E2" t="n">
-        <v>0.204386554093022</v>
+        <v>0.2043865540930215</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2043865418445479</v>
+        <v>0.2043865418445475</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1224906293419883</v>
+        <v>0.122490629341988</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1270786953932721</v>
+        <v>0.127078695393272</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1220473687456476</v>
+        <v>0.1220473687456475</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1536824384944548</v>
+        <v>0.1536824384944546</v>
       </c>
       <c r="K2" t="n">
-        <v>0.162049778631497</v>
+        <v>0.1620497786314968</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1212771473715471</v>
+        <v>0.121277147371547</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.1222466948919728</v>
+        <v>0.1222466948919726</v>
       </c>
       <c r="C3" t="n">
-        <v>0.218721972623887</v>
+        <v>0.2187219726238852</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1264172505220725</v>
+        <v>0.1264172505220722</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2549953313037225</v>
+        <v>0.2549953313037221</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2549953190552484</v>
+        <v>0.2549953190552481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.122246909439984</v>
+        <v>0.1222469094399837</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1549117324452637</v>
+        <v>0.1549117324452638</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1190796274978545</v>
+        <v>0.1190796274978542</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1790090271258112</v>
+        <v>0.179009027125811</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1854748449428884</v>
+        <v>0.1854748449428883</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1137262818773561</v>
+        <v>0.1137262818773559</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01857891309187837</v>
+        <v>0.01857891309187821</v>
       </c>
       <c r="C4" t="n">
-        <v>0.005840233343893382</v>
+        <v>0.005840233343893263</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02521584645959139</v>
+        <v>0.02521584645959113</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01394002704063855</v>
+        <v>0.01394002704063822</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01394002704063855</v>
+        <v>0.01394002704063822</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01864968956844072</v>
+        <v>0.01864968956844062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06990828737249584</v>
+        <v>0.06990828737249574</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01403355162477565</v>
+        <v>0.01403355162477541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02941166479714069</v>
+        <v>0.02941166479714042</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01432847826829636</v>
+        <v>0.01432847826829622</v>
       </c>
       <c r="L4" t="n">
-        <v>0.005116410102876399</v>
+        <v>0.005116410102876202</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2526784704885252</v>
+        <v>0.252678470488525</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03606970162355627</v>
+        <v>0.03606970162343623</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3581451399325977</v>
+        <v>0.3581451399325964</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1622347158495003</v>
+        <v>0.1622347158494994</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1622347158495003</v>
+        <v>0.1622347158494994</v>
       </c>
       <c r="G5" t="n">
-        <v>0.252319068846978</v>
+        <v>0.2523190688469776</v>
       </c>
       <c r="H5" t="n">
-        <v>1.258228878025494</v>
+        <v>1.258228878025492</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1622335922538263</v>
+        <v>0.1622335922538252</v>
       </c>
       <c r="J5" t="n">
-        <v>0.450836169071609</v>
+        <v>0.4508361690716072</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1737581196566145</v>
+        <v>0.1737581196566143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01838729932408905</v>
+        <v>0.01838729932408863</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.748766597740022</v>
+        <v>6.748766597740016</v>
       </c>
       <c r="C6" t="n">
-        <v>1.774564965023808</v>
+        <v>1.774564965023807</v>
       </c>
       <c r="D6" t="n">
-        <v>1.794220398815249</v>
+        <v>1.794220398815248</v>
       </c>
       <c r="E6" t="n">
-        <v>1.102629918807634</v>
+        <v>1.102629918807633</v>
       </c>
       <c r="F6" t="n">
-        <v>1.782783987476738</v>
+        <v>1.782783987476737</v>
       </c>
       <c r="G6" t="n">
-        <v>1.787440149632245</v>
+        <v>1.787440149632246</v>
       </c>
       <c r="H6" t="n">
-        <v>6.80162380971721</v>
+        <v>6.801623809717208</v>
       </c>
       <c r="I6" t="n">
-        <v>6.744221236272914</v>
+        <v>6.744221236272904</v>
       </c>
       <c r="J6" t="n">
-        <v>1.888244288478707</v>
+        <v>1.888244288478706</v>
       </c>
       <c r="K6" t="n">
         <v>1.782977163339979</v>
       </c>
       <c r="L6" t="n">
-        <v>1.773834272456122</v>
+        <v>1.773834272456121</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02064723577858243</v>
+        <v>0.02064723577858224</v>
       </c>
       <c r="C7" t="n">
-        <v>0.008278458360108668</v>
+        <v>0.008278458360108381</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02728411976116094</v>
+        <v>0.02728411976116089</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01609559391843524</v>
+        <v>0.01609559391843483</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01609559391843523</v>
+        <v>0.01609559391843483</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02071801225514478</v>
+        <v>0.0207180122551446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07197661005919984</v>
+        <v>0.07197661005919956</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01610187431147971</v>
+        <v>0.01610187431147939</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03147998748384467</v>
+        <v>0.03147998748384442</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01639680095500043</v>
+        <v>0.01639680095500027</v>
       </c>
       <c r="L7" t="n">
-        <v>0.007184732789580452</v>
+        <v>0.007184732789580429</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0225235490039464</v>
+        <v>0.02252354900394626</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01326430007839307</v>
+        <v>0.01326430007839259</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03292253623427251</v>
+        <v>0.03292253623427226</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02023733326081246</v>
+        <v>0.02023733326081226</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01807369433428941</v>
+        <v>0.01807369433428922</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02571026830119688</v>
+        <v>0.02571026830119659</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07696886610544412</v>
+        <v>0.07696886610544401</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02109413035753184</v>
+        <v>0.02109413035753156</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03647285589563671</v>
+        <v>0.03647285589563638</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01821523394329469</v>
+        <v>0.01821523394329428</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01543185165688441</v>
+        <v>0.0154318516568841</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02810015228096385</v>
+        <v>0.02810015228096366</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01862984474499537</v>
+        <v>0.01862984474499467</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03763554879213298</v>
+        <v>0.03763554879213268</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02979913448192635</v>
+        <v>0.02979913448192581</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02645437108797711</v>
+        <v>0.02645437108797676</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03106939864003144</v>
+        <v>0.03106939864003093</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08232799644408653</v>
+        <v>0.08232799644408592</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02645326069636636</v>
+        <v>0.026453260696366</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04183137386873152</v>
+        <v>0.04183137386873106</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02309849812938545</v>
+        <v>0.02309849812938519</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01753611917446713</v>
+        <v>0.01753611917446718</v>
       </c>
     </row>
   </sheetData>
@@ -4478,31 +4478,31 @@
         <v>0.1328066845206161</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1831754591314401</v>
+        <v>0.1831754591314403</v>
       </c>
       <c r="D2" t="n">
         <v>0.1341848960930268</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2032588950251423</v>
+        <v>0.2032588950251427</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2032588751940088</v>
+        <v>0.2032588751940091</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1330771801571011</v>
+        <v>0.1330771801571013</v>
       </c>
       <c r="H2" t="n">
         <v>0.1366716444679718</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1324429635349033</v>
+        <v>0.1324429635349034</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1512715802159503</v>
+        <v>0.1512715802159504</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1610480018928633</v>
+        <v>0.1610480018928634</v>
       </c>
       <c r="L2" t="n">
         <v>0.1322470524881405</v>
@@ -4518,31 +4518,31 @@
         <v>0.1363941626983889</v>
       </c>
       <c r="C3" t="n">
-        <v>0.216776586126822</v>
+        <v>0.2167765861268218</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1462032651046812</v>
+        <v>0.1462032651046813</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2506924360985603</v>
+        <v>0.2506924360985602</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2506924162674266</v>
+        <v>0.2506924162674271</v>
       </c>
       <c r="G3" t="n">
         <v>0.1383230742905133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1639039862870334</v>
+        <v>0.1639039862870335</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1337979456350989</v>
+        <v>0.133797945635099</v>
       </c>
       <c r="J3" t="n">
         <v>0.1703930501283391</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1814792739013788</v>
+        <v>0.1814792739013789</v>
       </c>
       <c r="L3" t="n">
         <v>0.132492013837867</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009762135336627533</v>
+        <v>0.009762135336627526</v>
       </c>
       <c r="C4" t="n">
-        <v>0.003714019776055621</v>
+        <v>0.003714019776055598</v>
       </c>
       <c r="D4" t="n">
         <v>0.02532966905565345</v>
       </c>
       <c r="E4" t="n">
-        <v>0.005977735078666526</v>
+        <v>0.00597773507866653</v>
       </c>
       <c r="F4" t="n">
-        <v>0.005977735078666526</v>
+        <v>0.00597773507866653</v>
       </c>
       <c r="G4" t="n">
         <v>0.01288571046178452</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05302018158916837</v>
+        <v>0.05302018158916834</v>
       </c>
       <c r="I4" t="n">
-        <v>0.006107627989892729</v>
+        <v>0.00610762798989274</v>
       </c>
       <c r="J4" t="n">
-        <v>0.01699407480039921</v>
+        <v>0.01699407480039919</v>
       </c>
       <c r="K4" t="n">
-        <v>0.006611266052763433</v>
+        <v>0.006611266052763416</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003603486697059156</v>
+        <v>0.003603486697059145</v>
       </c>
     </row>
     <row r="5">
@@ -4598,31 +4598,31 @@
         <v>0.1177586940928086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01762539486654031</v>
+        <v>0.01762539486654029</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3789682236034766</v>
+        <v>0.3789682236034775</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04538343216911966</v>
+        <v>0.04538343216911969</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04538343216911966</v>
+        <v>0.04538343216911969</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1710218859545834</v>
+        <v>0.171021885954584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9563846995877717</v>
+        <v>0.9563846995877723</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04538182153986797</v>
+        <v>0.04538182153986793</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2490567155538493</v>
+        <v>0.2490567155538497</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06102973185453141</v>
+        <v>0.06102973185453148</v>
       </c>
       <c r="L5" t="n">
         <v>0.01069866210074572</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.739075773942343</v>
+        <v>6.739075773942338</v>
       </c>
       <c r="C6" t="n">
-        <v>1.772126648638815</v>
+        <v>1.772126648638814</v>
       </c>
       <c r="D6" t="n">
         <v>1.794138329575179</v>
@@ -4650,22 +4650,22 @@
         <v>1.774448536454205</v>
       </c>
       <c r="G6" t="n">
-        <v>1.781266932856549</v>
+        <v>1.781266932856548</v>
       </c>
       <c r="H6" t="n">
-        <v>6.783899207313984</v>
+        <v>6.783899207313985</v>
       </c>
       <c r="I6" t="n">
         <v>1.774488850384655</v>
       </c>
       <c r="J6" t="n">
-        <v>6.746810036268188</v>
+        <v>6.746810036268181</v>
       </c>
       <c r="K6" t="n">
         <v>1.77481439191339</v>
       </c>
       <c r="L6" t="n">
-        <v>1.771950431809225</v>
+        <v>1.771950431809226</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01134271367916358</v>
+        <v>0.01134271367916356</v>
       </c>
       <c r="C7" t="n">
-        <v>0.005622775578224166</v>
+        <v>0.005622775578224226</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02691020950871685</v>
+        <v>0.02691020950871682</v>
       </c>
       <c r="E7" t="n">
-        <v>0.007678829048092932</v>
+        <v>0.007678829048092941</v>
       </c>
       <c r="F7" t="n">
-        <v>0.007678829048092932</v>
+        <v>0.007678829048092941</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01446628880432055</v>
+        <v>0.01446628880432054</v>
       </c>
       <c r="H7" t="n">
-        <v>0.05460075993170442</v>
+        <v>0.05460075993170439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.007688206332428765</v>
+        <v>0.007688206332428772</v>
       </c>
       <c r="J7" t="n">
         <v>0.01857465314293523</v>
       </c>
       <c r="K7" t="n">
-        <v>0.008191844395299472</v>
+        <v>0.008191844395299441</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005184065039595188</v>
+        <v>0.005184065039595172</v>
       </c>
     </row>
     <row r="8">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01284457664843487</v>
+        <v>0.01284457664843485</v>
       </c>
       <c r="C8" t="n">
-        <v>0.009535074819648687</v>
+        <v>0.009535074819648737</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0313344316455228</v>
+        <v>0.03133443164552278</v>
       </c>
       <c r="E8" t="n">
         <v>0.01094120971298983</v>
@@ -4733,19 +4733,19 @@
         <v>0.01838858123542653</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05852305236303999</v>
+        <v>0.05852305236303991</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01161049876353474</v>
+        <v>0.01161049876353476</v>
       </c>
       <c r="J8" t="n">
         <v>0.0224974212531991</v>
       </c>
       <c r="K8" t="n">
-        <v>0.009648746645064619</v>
+        <v>0.009648746645064587</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01163469843231543</v>
+        <v>0.01163469843231542</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01654113165161901</v>
+        <v>0.01654113165161902</v>
       </c>
       <c r="C9" t="n">
-        <v>0.01289700079613295</v>
+        <v>0.01289700079613296</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03418446695609108</v>
+        <v>0.0341844669560911</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01735946097049735</v>
+        <v>0.01735946097049737</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01496403126791276</v>
+        <v>0.01496403126791279</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02174051402222933</v>
+        <v>0.02174051402222935</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06187498514961322</v>
+        <v>0.06187498514961324</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01496243155033753</v>
+        <v>0.01496243155033756</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02584887836084399</v>
+        <v>0.02584887836084402</v>
       </c>
       <c r="K9" t="n">
         <v>0.01421454018465625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01245829025750394</v>
+        <v>0.01245829025750396</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05245785222007529</v>
+        <v>0.05245785222007517</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2150212026685658</v>
+        <v>0.2150212026685655</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05320868877573073</v>
+        <v>0.05320868877573071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2230061924127099</v>
+        <v>0.22300619241271</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1985832438525178</v>
+        <v>0.198583243852518</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05450012940190422</v>
+        <v>0.05450012940190413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05362671707244108</v>
+        <v>0.05362671707244102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05656197961718942</v>
+        <v>0.05656197961718939</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2424797685289345</v>
+        <v>0.2424797685289344</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2052618110328198</v>
+        <v>0.2052618110328196</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05285492320166672</v>
+        <v>0.05285492320166665</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02395418449712587</v>
+        <v>0.0239541844971255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3146602777847723</v>
+        <v>0.3146602777847716</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0292970111177111</v>
+        <v>0.02929701111771107</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3278305310776138</v>
+        <v>0.327830531077614</v>
       </c>
       <c r="F3" t="n">
         <v>0.2875159934651594</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03850416529891205</v>
+        <v>0.03850416529891193</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03247229910750011</v>
+        <v>0.03247229910750006</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05308413958727998</v>
+        <v>0.05308413958727996</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3719355316848285</v>
+        <v>0.3719355316848281</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2977037269509709</v>
+        <v>0.2977037269509705</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02700097227765878</v>
+        <v>0.02700097227765876</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.009750342947968072</v>
+        <v>0.009750342947967824</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05710781672883896</v>
+        <v>0.05710781672883899</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01823138724597666</v>
+        <v>0.01823138724597649</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05717382483524548</v>
+        <v>0.0571738248352455</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05717382483524548</v>
+        <v>0.05717382483524545</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03292842405318082</v>
+        <v>0.03292842405318062</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02321593538928612</v>
+        <v>0.023215935389286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05684047822870563</v>
+        <v>0.05684047822870558</v>
       </c>
       <c r="J4" t="n">
-        <v>0.08037229141290653</v>
+        <v>0.08037229141290649</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0542218950888786</v>
+        <v>0.05422189508887854</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01458587582861467</v>
+        <v>0.01458587582861452</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02583555384675987</v>
+        <v>0.02583555384675518</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8133283772644144</v>
+        <v>0.8133283772644158</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1773340968447528</v>
+        <v>0.177334096844752</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8133283770800517</v>
+        <v>0.8133283770800536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8133283770800517</v>
+        <v>0.8133283770800537</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4477430716688514</v>
+        <v>0.4477430716688508</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2988633777980306</v>
+        <v>0.2988633777980299</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8133337275974568</v>
+        <v>0.8133337275974577</v>
       </c>
       <c r="J5" t="n">
         <v>1.368542498923496</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8211864276017888</v>
+        <v>0.8211864276017899</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0519041248534149</v>
+        <v>0.05190412485341747</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.910526106604959</v>
+        <v>1.91052610660496</v>
       </c>
       <c r="C6" t="n">
-        <v>1.958057432082716</v>
+        <v>1.958057432082715</v>
       </c>
       <c r="D6" t="n">
         <v>1.91807787943616</v>
       </c>
       <c r="E6" t="n">
-        <v>1.228124867544877</v>
+        <v>1.228124867544876</v>
       </c>
       <c r="F6" t="n">
         <v>1.957572864864899</v>
       </c>
       <c r="G6" t="n">
-        <v>1.933704187710171</v>
+        <v>1.933704187710174</v>
       </c>
       <c r="H6" t="n">
-        <v>7.249870914929827</v>
+        <v>7.249870914929829</v>
       </c>
       <c r="I6" t="n">
-        <v>7.283007652924576</v>
+        <v>7.283007652924566</v>
       </c>
       <c r="J6" t="n">
-        <v>2.077885219275891</v>
+        <v>2.077885219275889</v>
       </c>
       <c r="K6" t="n">
-        <v>1.955325051025179</v>
+        <v>1.955325051025181</v>
       </c>
       <c r="L6" t="n">
-        <v>1.915018837481797</v>
+        <v>1.915018837481796</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01302928996929699</v>
+        <v>0.01302928996929665</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06011407491699193</v>
+        <v>0.06011407491699192</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02151017209359871</v>
+        <v>0.02151017209359849</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06013388946923191</v>
+        <v>0.060133889469232</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06013388946923191</v>
+        <v>0.06013388946923194</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03620737107450985</v>
+        <v>0.0362073710745097</v>
       </c>
       <c r="H7" t="n">
         <v>0.02649488241061505</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06011942525003463</v>
+        <v>0.06011942525003465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08365123843423551</v>
+        <v>0.08365123843423546</v>
       </c>
       <c r="K7" t="n">
         <v>0.0575008421102076</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01786482284994357</v>
+        <v>0.01786482284994356</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01556422843293401</v>
+        <v>0.01556422843293322</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06716106907758392</v>
+        <v>0.06716106907758396</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02946877148595814</v>
+        <v>0.02946877148595804</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0659303897050698</v>
+        <v>0.06593038970506979</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06280332126038686</v>
+        <v>0.06280332126038682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04323435367832647</v>
+        <v>0.04323435367832616</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03352186501443462</v>
+        <v>0.03352186501443444</v>
       </c>
       <c r="I8" t="n">
-        <v>0.06714640785385124</v>
+        <v>0.0671464078538512</v>
       </c>
       <c r="J8" t="n">
-        <v>0.09067910384596121</v>
+        <v>0.09067910384596106</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05995233854835307</v>
+        <v>0.05995233854835293</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02958412116985864</v>
+        <v>0.02958412116985866</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02945908326098809</v>
+        <v>0.02945908326098754</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08234173304138423</v>
+        <v>0.08234173304138416</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04373799839272356</v>
+        <v>0.04373799839272338</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08903235337343202</v>
+        <v>0.08903235337343197</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08234173446443345</v>
+        <v>0.08234173446443342</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05843502919890216</v>
+        <v>0.05843502919890193</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04872254053500738</v>
+        <v>0.04872254053500725</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08234708337442696</v>
+        <v>0.08234708337442692</v>
       </c>
       <c r="J9" t="n">
-        <v>0.105878896558628</v>
+        <v>0.1058788965586278</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07636919710456863</v>
+        <v>0.07636919710456845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04009248097433591</v>
+        <v>0.04009248097433579</v>
       </c>
     </row>
   </sheetData>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05095363763171468</v>
+        <v>0.05095363763171466</v>
       </c>
       <c r="C2" t="n">
         <v>0.2118087618371562</v>
@@ -5282,22 +5282,22 @@
         <v>0.1954878672265158</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0523767714997615</v>
+        <v>0.05237677149976152</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05181315256764357</v>
+        <v>0.05181315256764355</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0539015288759668</v>
+        <v>0.05390152887596682</v>
       </c>
       <c r="J2" t="n">
         <v>0.2389406916872009</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2008904008586716</v>
+        <v>0.2008904008586715</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05114153362447888</v>
+        <v>0.05114153362447885</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02350642298044697</v>
+        <v>0.023506422980447</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3050757245751854</v>
+        <v>0.3050757245751855</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02688037589767226</v>
+        <v>0.02688037589767227</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3181297024125346</v>
+        <v>0.3181297024125348</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2781267179765323</v>
+        <v>0.2781267179765321</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03363940208996532</v>
+        <v>0.03363940208996533</v>
       </c>
       <c r="H3" t="n">
         <v>0.02977487784858236</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04441275070203542</v>
+        <v>0.04441275070203543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3611343943025654</v>
+        <v>0.3611343943025651</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2831768149368157</v>
+        <v>0.2831768149368156</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02501115075408503</v>
+        <v>0.02501115075408506</v>
       </c>
     </row>
     <row r="4">
@@ -5350,34 +5350,34 @@
         <v>0.009184049809669189</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04332208447653225</v>
+        <v>0.04332208447653224</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01454460208044596</v>
+        <v>0.01454460208044593</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04337767117907376</v>
+        <v>0.04337767117907372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04337767117907374</v>
+        <v>0.0433776711790737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02536506551963609</v>
+        <v>0.02536506551963604</v>
       </c>
       <c r="H4" t="n">
-        <v>0.01908116464829602</v>
+        <v>0.01908116464829598</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04318982764268269</v>
+        <v>0.04318982764268266</v>
       </c>
       <c r="J4" t="n">
-        <v>0.06540251551038084</v>
+        <v>0.06540251551038083</v>
       </c>
       <c r="K4" t="n">
         <v>0.03445003389077973</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01156798254024599</v>
+        <v>0.01156798254024597</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0436086345318849</v>
+        <v>0.04360863453188455</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5643570440093661</v>
+        <v>0.5643570440093685</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1316205623487251</v>
+        <v>0.1316205623487253</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5643570455747163</v>
+        <v>0.5643570455747179</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5643570455747164</v>
+        <v>0.5643570455747179</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3155902585551306</v>
+        <v>0.3155902585551307</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2350515780195381</v>
+        <v>0.2350515780195385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5643610156079132</v>
+        <v>0.5643610156079152</v>
       </c>
       <c r="J5" t="n">
         <v>1.04559960900969</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4387940286319189</v>
+        <v>0.4387940286319169</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0543440615428719</v>
+        <v>0.05434406154287146</v>
       </c>
     </row>
     <row r="6">
@@ -5427,28 +5427,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.779506149775817</v>
+        <v>1.779506149775818</v>
       </c>
       <c r="C6" t="n">
         <v>1.813884165360349</v>
       </c>
       <c r="D6" t="n">
-        <v>1.784299340907997</v>
+        <v>1.784299340907995</v>
       </c>
       <c r="E6" t="n">
-        <v>1.133777471739666</v>
+        <v>1.133777471739667</v>
       </c>
       <c r="F6" t="n">
         <v>1.813546455716426</v>
       </c>
       <c r="G6" t="n">
-        <v>1.795687165485784</v>
+        <v>1.795687165485783</v>
       </c>
       <c r="H6" t="n">
-        <v>6.751508772818712</v>
+        <v>6.751508772818704</v>
       </c>
       <c r="I6" t="n">
-        <v>6.775170547334802</v>
+        <v>6.775170547334798</v>
       </c>
       <c r="J6" t="n">
         <v>1.925905908125776</v>
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01165520620694733</v>
+        <v>0.0116552062069473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04565701244141478</v>
+        <v>0.04565701244141473</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01701563802105195</v>
+        <v>0.01701563802105193</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04565863636019524</v>
+        <v>0.04565863636019522</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04565863636019524</v>
+        <v>0.04565863636019522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02783622191691417</v>
+        <v>0.02783622191691418</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02155232104557415</v>
+        <v>0.0215523210455741</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04566098403996078</v>
+        <v>0.04566098403996077</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06787367190765897</v>
+        <v>0.06787367190765893</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0369211902880579</v>
+        <v>0.03692119028805781</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01403913893752414</v>
+        <v>0.01403913893752412</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01363569422159774</v>
+        <v>0.01363569422159773</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05107222938689557</v>
+        <v>0.05107222938689548</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02314034766937753</v>
+        <v>0.02314034766937744</v>
       </c>
       <c r="E8" t="n">
         <v>0.05013324740590409</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0477473427058398</v>
+        <v>0.04774734270583982</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03324908564498822</v>
+        <v>0.03324908564498823</v>
       </c>
       <c r="H8" t="n">
-        <v>0.02696518477365504</v>
+        <v>0.02696518477365497</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0510738477680348</v>
+        <v>0.05107384776803477</v>
       </c>
       <c r="J8" t="n">
-        <v>0.07328721019009832</v>
+        <v>0.0732872101900983</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03883792016214727</v>
+        <v>0.03883792016214724</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02303740610345394</v>
+        <v>0.0230374061034539</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02280347070656075</v>
+        <v>0.02280347070656072</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06083462236113979</v>
+        <v>0.06083462236113978</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03219337184510293</v>
+        <v>0.03219337184510299</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0654844064135095</v>
+        <v>0.06548440641350955</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06083462407971182</v>
+        <v>0.06083462407971185</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04301383183663916</v>
+        <v>0.0430138318366392</v>
       </c>
       <c r="H9" t="n">
         <v>0.03672993096529911</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06083859395968578</v>
+        <v>0.06083859395968579</v>
       </c>
       <c r="J9" t="n">
-        <v>0.08305128182738392</v>
+        <v>0.08305128182738394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04976418309697956</v>
+        <v>0.04976418309697953</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0292167488572491</v>
+        <v>0.02921674885724912</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04925165517045921</v>
+        <v>0.04925165517045847</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2066824304178564</v>
+        <v>0.206682430417855</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04970595749561792</v>
+        <v>0.04970595749561759</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2145695910278213</v>
+        <v>0.2145695910278202</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1904036762771004</v>
+        <v>0.190403676277101</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05027775906342487</v>
+        <v>0.05027775906342459</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05129785723810271</v>
+        <v>0.05129785723810188</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04989442350380863</v>
+        <v>0.049894423503808</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2348624345797985</v>
+        <v>0.2348624345797982</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1959500151649253</v>
+        <v>0.1959500151649245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04926051440018524</v>
+        <v>0.04926051440018468</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02291930786600753</v>
+        <v>0.02291930786600682</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2862953689732991</v>
+        <v>0.2862953689732904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0261430696760726</v>
+        <v>0.02614306967607245</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2993001052957645</v>
+        <v>0.2993001052957653</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2594098509547549</v>
+        <v>0.2594098509547431</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03021782760224097</v>
+        <v>0.03021782760224081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0375331838265929</v>
+        <v>0.0375331838265926</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02747376257743452</v>
+        <v>0.02747376257742644</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3489945714903734</v>
+        <v>0.3489945714903729</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2674792107955621</v>
+        <v>0.2674792107955616</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02312072527501691</v>
+        <v>0.02312072527501685</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.007893542131570879</v>
+        <v>0.007893542131570503</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01552386078712798</v>
+        <v>0.01552386078711994</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01302509588363754</v>
+        <v>0.0130250958836372</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01559241581479711</v>
+        <v>0.01559241581478605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01559241581479427</v>
+        <v>0.01559241581478605</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01957717454637822</v>
+        <v>0.01957717454637752</v>
       </c>
       <c r="H4" t="n">
-        <v>0.03097105875861795</v>
+        <v>0.03097105875861769</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01577560350324201</v>
+        <v>0.01577560350322558</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04839029827137005</v>
+        <v>0.04839029827136862</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01292111478101993</v>
+        <v>0.01292111478101948</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008206027075947782</v>
+        <v>0.008206027075947024</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0608611076288763</v>
+        <v>0.06086110762887497</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1727861268249403</v>
+        <v>0.1727861268247632</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1419735569329843</v>
+        <v>0.1419735569329831</v>
       </c>
       <c r="E5" t="n">
-        <v>0.172786133947038</v>
+        <v>0.1727861339469625</v>
       </c>
       <c r="F5" t="n">
-        <v>0.172786133947038</v>
+        <v>0.1727861339469625</v>
       </c>
       <c r="G5" t="n">
-        <v>0.253078221081235</v>
+        <v>0.2530782210812332</v>
       </c>
       <c r="H5" t="n">
-        <v>0.4841554232486085</v>
+        <v>0.4841554232486078</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1727851732448446</v>
+        <v>0.1727851732447561</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7879116859147319</v>
+        <v>0.7879116859147294</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1318719813879677</v>
+        <v>0.1318719813879664</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1710715880843186</v>
+        <v>0.1710715880843179</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>1.777070591652889</v>
       </c>
       <c r="C6" t="n">
-        <v>1.784806969196503</v>
+        <v>1.784806969196499</v>
       </c>
       <c r="D6" t="n">
-        <v>1.782015716615159</v>
+        <v>1.782015716615158</v>
       </c>
       <c r="E6" t="n">
-        <v>1.104774602927551</v>
+        <v>1.10477460292755</v>
       </c>
       <c r="F6" t="n">
-        <v>1.784929571121496</v>
+        <v>1.78492957112149</v>
       </c>
       <c r="G6" t="n">
-        <v>6.750040992375405</v>
+        <v>6.750040992375406</v>
       </c>
       <c r="H6" t="n">
         <v>6.762004311567773</v>
       </c>
       <c r="I6" t="n">
-        <v>1.784952653024555</v>
+        <v>1.784952653024542</v>
       </c>
       <c r="J6" t="n">
-        <v>6.779237381741876</v>
+        <v>6.779237381741875</v>
       </c>
       <c r="K6" t="n">
         <v>1.781936040867582</v>
       </c>
       <c r="L6" t="n">
-        <v>1.777344997112392</v>
+        <v>1.777344997112391</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.009805531064718912</v>
+        <v>0.009805531064718239</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01768854601637871</v>
+        <v>0.01768854601638044</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01493702981045563</v>
+        <v>0.01493702981045431</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01764717882432424</v>
+        <v>0.01764717882432323</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0176471788243243</v>
+        <v>0.01764717882432323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02148916347952653</v>
+        <v>0.0214891634795257</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03288304769176693</v>
+        <v>0.03288304769176541</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01768759243638042</v>
+        <v>0.01768759243637355</v>
       </c>
       <c r="J7" t="n">
-        <v>0.05030228720451699</v>
+        <v>0.05030228720451652</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01483310371416871</v>
+        <v>0.01483310371416722</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01011801600909564</v>
+        <v>0.01011801600909475</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01156719902197271</v>
+        <v>0.01156719902197116</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02225647372302763</v>
+        <v>0.0222564737230183</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02013394833110178</v>
+        <v>0.02013394833110139</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02148248123925994</v>
+        <v>0.0214824812392508</v>
       </c>
       <c r="F8" t="n">
-        <v>0.01951576122393065</v>
+        <v>0.0195157612239164</v>
       </c>
       <c r="G8" t="n">
-        <v>0.02609605197975589</v>
+        <v>0.02609605197975527</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03748993619200752</v>
+        <v>0.03748993619200635</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02229448093662324</v>
+        <v>0.02229448093660322</v>
       </c>
       <c r="J8" t="n">
-        <v>0.05490973486708666</v>
+        <v>0.05490973486708498</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01654192023952565</v>
+        <v>0.01654192023952462</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01769697527527493</v>
+        <v>0.01769697527527489</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01735529676964027</v>
+        <v>0.01735529676963733</v>
       </c>
       <c r="C9" t="n">
-        <v>0.02807743149779404</v>
+        <v>0.02807743149777646</v>
       </c>
       <c r="D9" t="n">
-        <v>0.02532597070045614</v>
+        <v>0.02532597070045356</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03135371543232818</v>
+        <v>0.03135371543232374</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02807743256055288</v>
+        <v>0.02807743256054408</v>
       </c>
       <c r="G9" t="n">
-        <v>0.03187804896092251</v>
+        <v>0.03187804896092169</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04327193317316292</v>
+        <v>0.04327193317316161</v>
       </c>
       <c r="I9" t="n">
-        <v>0.02807647791777497</v>
+        <v>0.02807647791776956</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06069117268591451</v>
+        <v>0.06069117268591268</v>
       </c>
       <c r="K9" t="n">
-        <v>0.02357699221618521</v>
+        <v>0.02357699221618352</v>
       </c>
       <c r="L9" t="n">
-        <v>0.02050690149049148</v>
+        <v>0.02050690149049095</v>
       </c>
     </row>
   </sheetData>
@@ -6062,31 +6062,31 @@
         <v>0.05496248088187215</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2176794863021475</v>
+        <v>0.2176794863021474</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05733197840277411</v>
+        <v>0.05733197840277414</v>
       </c>
       <c r="E2" t="n">
         <v>0.2257874529718037</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2010840475831433</v>
+        <v>0.2010840475831432</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05840193582340864</v>
+        <v>0.0584019358234087</v>
       </c>
       <c r="H2" t="n">
         <v>0.06001816807398092</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05931900152721158</v>
+        <v>0.05931900152721155</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2482788345921639</v>
+        <v>0.248278834592164</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2086950598934083</v>
+        <v>0.2086950598934084</v>
       </c>
       <c r="L2" t="n">
         <v>0.05853336227537067</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02614614288524719</v>
+        <v>0.02614614288524715</v>
       </c>
       <c r="C3" t="n">
         <v>0.3184893199773836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0429250086901914</v>
+        <v>0.04292500869019139</v>
       </c>
       <c r="E3" t="n">
         <v>0.3318462729316656</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2910687810246579</v>
+        <v>0.2910687810246577</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05057264417174227</v>
+        <v>0.05057264417174224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.062164885799307</v>
+        <v>0.06216488579930698</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0570598643288264</v>
+        <v>0.05705986432882636</v>
       </c>
       <c r="J3" t="n">
-        <v>0.395002400743425</v>
+        <v>0.3950024007434254</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3056747625091604</v>
+        <v>0.3056747625091605</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05178793728312132</v>
+        <v>0.05178793728312136</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.01157144526941795</v>
+        <v>0.01157144526941793</v>
       </c>
       <c r="C4" t="n">
         <v>0.06147286337472986</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0383360097907187</v>
+        <v>0.03833600979071874</v>
       </c>
       <c r="E4" t="n">
         <v>0.06155980285241801</v>
       </c>
       <c r="F4" t="n">
-        <v>0.061559802852418</v>
+        <v>0.06155980285241798</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05052331046754972</v>
+        <v>0.05052331046754971</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06870760393418189</v>
+        <v>0.06870760393418184</v>
       </c>
       <c r="I4" t="n">
-        <v>0.06145870313612174</v>
+        <v>0.06145870313612168</v>
       </c>
       <c r="J4" t="n">
         <v>0.1139663936304169</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06504872002949753</v>
+        <v>0.06504872002949749</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05203003631911836</v>
+        <v>0.05203003631911839</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0346634582735553</v>
+        <v>0.03466345827355449</v>
       </c>
       <c r="C5" t="n">
-        <v>0.86623458882006</v>
+        <v>0.8662345888200609</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4671151309935195</v>
+        <v>0.467115130993519</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8662345925382305</v>
+        <v>0.8662345925382303</v>
       </c>
       <c r="F5" t="n">
-        <v>0.866234592538231</v>
+        <v>0.8662345925382303</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7020136126922946</v>
+        <v>0.7020136126922953</v>
       </c>
       <c r="H5" t="n">
-        <v>1.070404769768044</v>
+        <v>1.070404769768043</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8662369610639927</v>
+        <v>0.8662369610639943</v>
       </c>
       <c r="J5" t="n">
         <v>1.980487842116606</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9291123121712459</v>
+        <v>0.9291123121712455</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8491200878543473</v>
+        <v>0.849120087854347</v>
       </c>
     </row>
     <row r="6">
@@ -6219,13 +6219,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.239816573530209</v>
+        <v>7.239816573530216</v>
       </c>
       <c r="C6" t="n">
-        <v>1.963159960011389</v>
+        <v>1.96315996001139</v>
       </c>
       <c r="D6" t="n">
-        <v>7.266694175205051</v>
+        <v>7.266694175205048</v>
       </c>
       <c r="E6" t="n">
         <v>1.23318939587667</v>
@@ -6234,16 +6234,16 @@
         <v>1.962978150527392</v>
       </c>
       <c r="G6" t="n">
-        <v>7.278768438728334</v>
+        <v>7.278768438728339</v>
       </c>
       <c r="H6" t="n">
-        <v>1.970259849288449</v>
+        <v>1.970259849288448</v>
       </c>
       <c r="I6" t="n">
         <v>7.28970383139691</v>
       </c>
       <c r="J6" t="n">
-        <v>7.342728829523048</v>
+        <v>7.342728829523051</v>
       </c>
       <c r="K6" t="n">
         <v>1.966897687320364</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01579727838893353</v>
+        <v>0.01579727838893355</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06568216401170444</v>
+        <v>0.06568216401170447</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04256170009490695</v>
+        <v>0.04256170009490697</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06567140130074531</v>
+        <v>0.06567140130074535</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06567140130074532</v>
+        <v>0.06567140130074535</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05474914358706532</v>
+        <v>0.05474914358706534</v>
       </c>
       <c r="H7" t="n">
         <v>0.07293343705369747</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06568453625563737</v>
+        <v>0.06568453625563732</v>
       </c>
       <c r="J7" t="n">
         <v>0.1181922267499325</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06927455314901308</v>
+        <v>0.06927455314901312</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05625586943863401</v>
+        <v>0.05625586943863397</v>
       </c>
     </row>
     <row r="8">
@@ -6308,19 +6308,19 @@
         <v>0.05302978913801275</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07333770890591321</v>
+        <v>0.07333770890591325</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0692872224409196</v>
+        <v>0.06928722244091967</v>
       </c>
       <c r="G8" t="n">
-        <v>0.06400776612462682</v>
+        <v>0.06400776612462687</v>
       </c>
       <c r="H8" t="n">
         <v>0.08219205959126477</v>
       </c>
       <c r="I8" t="n">
-        <v>0.07494315879319881</v>
+        <v>0.07494315879319886</v>
       </c>
       <c r="J8" t="n">
         <v>0.1274519954549008</v>
@@ -6329,7 +6329,7 @@
         <v>0.07259274259883841</v>
       </c>
       <c r="L8" t="n">
-        <v>0.07160660689878987</v>
+        <v>0.07160660689878989</v>
       </c>
     </row>
     <row r="9">
@@ -6339,10 +6339,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03797780556427624</v>
+        <v>0.03797780556427627</v>
       </c>
       <c r="C9" t="n">
-        <v>0.09558764434264169</v>
+        <v>0.09558764434264162</v>
       </c>
       <c r="D9" t="n">
         <v>0.07246732673470685</v>
@@ -6351,25 +6351,25 @@
         <v>0.1045020718129649</v>
       </c>
       <c r="F9" t="n">
-        <v>0.09558763881919473</v>
+        <v>0.09558763881919483</v>
       </c>
       <c r="G9" t="n">
         <v>0.08465462391800252</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1028389173846348</v>
+        <v>0.1028389173846347</v>
       </c>
       <c r="I9" t="n">
-        <v>0.09559001658657465</v>
+        <v>0.09559001658657452</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1480977070808698</v>
+        <v>0.1480977070808697</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09470416675273463</v>
+        <v>0.09470416675273458</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08616134976957122</v>
+        <v>0.0861613497695712</v>
       </c>
     </row>
   </sheetData>
@@ -6455,34 +6455,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05247150091951334</v>
+        <v>0.05247150091951333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2130426218748179</v>
+        <v>0.2130426218748178</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05485729246843399</v>
+        <v>0.05485729246843401</v>
       </c>
       <c r="E2" t="n">
         <v>0.2209945340792428</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1966999022173798</v>
+        <v>0.19669990221738</v>
       </c>
       <c r="G2" t="n">
         <v>0.05520101741585116</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0567442488475727</v>
+        <v>0.05674424884757269</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05548658776920515</v>
+        <v>0.05548658776920512</v>
       </c>
       <c r="J2" t="n">
         <v>0.2408886388614142</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2009823807196588</v>
+        <v>0.2009823807196587</v>
       </c>
       <c r="L2" t="n">
         <v>0.05648184944259298</v>
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02403852699993365</v>
+        <v>0.02403852699993362</v>
       </c>
       <c r="C3" t="n">
         <v>0.3055044943039322</v>
       </c>
       <c r="D3" t="n">
-        <v>0.04090853787341652</v>
+        <v>0.04090853787341647</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3186075623674746</v>
+        <v>0.3186075623674748</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2785048317762338</v>
+        <v>0.2785048317762339</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04339547681160522</v>
+        <v>0.04339547681160523</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0543505402432761</v>
+        <v>0.05435054024327607</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04540661128857858</v>
+        <v>0.04540661128857851</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3657398382008136</v>
+        <v>0.3657398382008134</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2780926196345105</v>
+        <v>0.2780926196345106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05263315236243945</v>
+        <v>0.05263315236243943</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.008600482079852608</v>
+        <v>0.008600482079852633</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04322811635796096</v>
+        <v>0.04322811635796091</v>
       </c>
       <c r="D4" t="n">
-        <v>0.03554909514324721</v>
+        <v>0.03554909514324722</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04329598857262822</v>
+        <v>0.04329598857262816</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04329598857262822</v>
+        <v>0.04329598857262816</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03952920863450047</v>
+        <v>0.03952920863450043</v>
       </c>
       <c r="H4" t="n">
         <v>0.05685180626922835</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04330794899720072</v>
+        <v>0.04330794899720068</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07202616033246217</v>
+        <v>0.07202616033246224</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02710799594448644</v>
+        <v>0.02710799594448647</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0538041374357984</v>
+        <v>0.05380413743579843</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0215333879359869</v>
+        <v>0.02153338793598695</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5464162557598645</v>
+        <v>0.5464162557598639</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4165424753689305</v>
+        <v>0.4165424753689302</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5464162601891761</v>
+        <v>0.5464162601891758</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5464162601891761</v>
+        <v>0.5464162601891758</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5028026663233541</v>
+        <v>0.5028026663233531</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7833951886210748</v>
+        <v>0.783395188621075</v>
       </c>
       <c r="I5" t="n">
         <v>0.5464170072950473</v>
       </c>
       <c r="J5" t="n">
-        <v>1.079875319090254</v>
+        <v>1.079875319090253</v>
       </c>
       <c r="K5" t="n">
-        <v>0.307583886528937</v>
+        <v>0.3075838865289374</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08668901419236809</v>
+        <v>0.08668901419236814</v>
       </c>
     </row>
     <row r="6">
@@ -6618,34 +6618,34 @@
         <v>6.741864652492139</v>
       </c>
       <c r="C6" t="n">
-        <v>1.813948493077716</v>
+        <v>1.813948493077717</v>
       </c>
       <c r="D6" t="n">
-        <v>1.805963820270247</v>
+        <v>1.805963820270248</v>
       </c>
       <c r="E6" t="n">
-        <v>1.133845096598127</v>
+        <v>1.133845096598128</v>
       </c>
       <c r="F6" t="n">
-        <v>1.813882706802446</v>
+        <v>1.813882706802445</v>
       </c>
       <c r="G6" t="n">
-        <v>6.772793379046788</v>
+        <v>6.772793379046791</v>
       </c>
       <c r="H6" t="n">
-        <v>6.790779332611254</v>
+        <v>6.790779332611246</v>
       </c>
       <c r="I6" t="n">
-        <v>6.776572119409487</v>
+        <v>6.776572119409492</v>
       </c>
       <c r="J6" t="n">
-        <v>1.932841795581443</v>
+        <v>1.932841795581444</v>
       </c>
       <c r="K6" t="n">
-        <v>1.797256576884314</v>
+        <v>1.797256576884313</v>
       </c>
       <c r="L6" t="n">
-        <v>1.824445877156914</v>
+        <v>1.824445877156913</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01174019370595971</v>
+        <v>0.01174019370595976</v>
       </c>
       <c r="C7" t="n">
-        <v>0.04644690908812456</v>
+        <v>0.04644690908812453</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03868869827266132</v>
+        <v>0.0386886982726613</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04642833760936171</v>
+        <v>0.04642833760936166</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04642833760936169</v>
+        <v>0.04642833760936166</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04266892026060758</v>
+        <v>0.04266892026060756</v>
       </c>
       <c r="H7" t="n">
         <v>0.05999151789533544</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04644766062330782</v>
+        <v>0.04644766062330775</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07516587195856926</v>
+        <v>0.07516587195856923</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03024770757059354</v>
+        <v>0.03024770757059356</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05694384906190551</v>
+        <v>0.05694384906190554</v>
       </c>
     </row>
     <row r="8">
@@ -6695,34 +6695,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01433926514840802</v>
+        <v>0.01433926514840799</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05339039176907211</v>
+        <v>0.05339039176907206</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04655341285533722</v>
+        <v>0.04655341285533721</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05219942462139786</v>
+        <v>0.05219942462139782</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04917321186109477</v>
+        <v>0.04917321186109472</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04962920115622141</v>
+        <v>0.04962920115622142</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06695179879095081</v>
+        <v>0.0669517987909508</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0534079415189217</v>
+        <v>0.05340794151892167</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08212700995175461</v>
+        <v>0.08212700995175466</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03276576730882708</v>
+        <v>0.03276576730882707</v>
       </c>
       <c r="L8" t="n">
         <v>0.0684597779050863</v>
@@ -6738,34 +6738,34 @@
         <v>0.02650256491622309</v>
       </c>
       <c r="C9" t="n">
-        <v>0.06647133306396311</v>
+        <v>0.06647133306396301</v>
       </c>
       <c r="D9" t="n">
-        <v>0.05871323220810695</v>
+        <v>0.0587132322081069</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07254362506280726</v>
+        <v>0.0725436250628072</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06647132863659912</v>
+        <v>0.06647132863659906</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06269334423644603</v>
+        <v>0.062693344236446</v>
       </c>
       <c r="H9" t="n">
-        <v>0.08001594187117395</v>
+        <v>0.08001594187117386</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06647208459914636</v>
+        <v>0.06647208459914623</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09519029593440785</v>
+        <v>0.09519029593440774</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04722327812367834</v>
+        <v>0.04722327812367833</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07696827303774402</v>
+        <v>0.07696827303774399</v>
       </c>
     </row>
   </sheetData>
@@ -6851,10 +6851,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04979518697066179</v>
+        <v>0.04979518697066176</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2080176164306659</v>
+        <v>0.2080176164306658</v>
       </c>
       <c r="D2" t="n">
         <v>0.05088277123166175</v>
@@ -6866,22 +6866,22 @@
         <v>0.1918975623087867</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05145984305389189</v>
+        <v>0.0514598430538919</v>
       </c>
       <c r="H2" t="n">
         <v>0.05347989759715631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05123428807481374</v>
+        <v>0.05123428807481375</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2331840978913528</v>
+        <v>0.2331840978913525</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1961120154596294</v>
+        <v>0.1961120154596293</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05287876017073673</v>
+        <v>0.05287876017073672</v>
       </c>
     </row>
     <row r="3">
@@ -6894,34 +6894,34 @@
         <v>0.02191452534460129</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2909424613423972</v>
+        <v>0.2909424613423974</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02962423691487175</v>
+        <v>0.02962423691487171</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3038021062564364</v>
+        <v>0.3038021062564366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2643167572066654</v>
+        <v>0.2643167572066651</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0337376671417223</v>
+        <v>0.03373766714172226</v>
       </c>
       <c r="H3" t="n">
-        <v>0.04811059246566078</v>
+        <v>0.04811059246566079</v>
       </c>
       <c r="I3" t="n">
         <v>0.03212643988129597</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3352988693121265</v>
+        <v>0.3352988693121264</v>
       </c>
       <c r="K3" t="n">
-        <v>0.265258568304108</v>
+        <v>0.2652585683041082</v>
       </c>
       <c r="L3" t="n">
-        <v>0.04390656363555771</v>
+        <v>0.04390656363555762</v>
       </c>
     </row>
     <row r="4">
@@ -6931,34 +6931,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.006058230163947417</v>
+        <v>0.006058230163947382</v>
       </c>
       <c r="C4" t="n">
         <v>0.02276942422745959</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01834299470542043</v>
+        <v>0.01834299470542041</v>
       </c>
       <c r="E4" t="n">
-        <v>0.02282972241259548</v>
+        <v>0.02282972241259546</v>
       </c>
       <c r="F4" t="n">
-        <v>0.02282972241259548</v>
+        <v>0.02282972241259546</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02495552843641786</v>
+        <v>0.02495552843641785</v>
       </c>
       <c r="H4" t="n">
-        <v>0.04753909032628496</v>
+        <v>0.04753909032628491</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02294144231920383</v>
+        <v>0.02294144231920384</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02807652171985822</v>
+        <v>0.02807652171985818</v>
       </c>
       <c r="K4" t="n">
-        <v>0.009847629690204501</v>
+        <v>0.00984762969020447</v>
       </c>
       <c r="L4" t="n">
         <v>0.04072594465404396</v>
@@ -6971,34 +6971,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01936934883503676</v>
+        <v>0.01936934883503673</v>
       </c>
       <c r="C5" t="n">
         <v>0.2769132218518118</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2094743743315477</v>
+        <v>0.209474374331547</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2769132272300553</v>
+        <v>0.2769132272300555</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2769132272300553</v>
+        <v>0.2769132272300555</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3221812509707601</v>
+        <v>0.3221812509707603</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7395393228618565</v>
+        <v>0.7395393228618562</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2769126690406508</v>
+        <v>0.2769126690406509</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3946898699524706</v>
+        <v>0.3946898699524715</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07642342719211404</v>
+        <v>0.07642342719211419</v>
       </c>
       <c r="L5" t="n">
         <v>0.111495757644442</v>
@@ -7011,7 +7011,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.775233552380657</v>
+        <v>1.775233552380658</v>
       </c>
       <c r="C6" t="n">
         <v>1.792126735488011</v>
@@ -7023,25 +7023,25 @@
         <v>1.112108317742204</v>
       </c>
       <c r="F6" t="n">
-        <v>1.792185516621621</v>
+        <v>1.79218551662162</v>
       </c>
       <c r="G6" t="n">
-        <v>1.794130850653127</v>
+        <v>1.794130850653128</v>
       </c>
       <c r="H6" t="n">
         <v>6.779213450598373</v>
       </c>
       <c r="I6" t="n">
-        <v>1.792116764535914</v>
+        <v>1.792116764535916</v>
       </c>
       <c r="J6" t="n">
         <v>1.887370019785221</v>
       </c>
       <c r="K6" t="n">
-        <v>1.778653312049669</v>
+        <v>1.778653312049668</v>
       </c>
       <c r="L6" t="n">
-        <v>1.810090989975513</v>
+        <v>1.810090989975512</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.008260878935487274</v>
+        <v>0.008260878935487232</v>
       </c>
       <c r="C7" t="n">
         <v>0.0251446439019049</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02054556893636243</v>
+        <v>0.02054556893636245</v>
       </c>
       <c r="E7" t="n">
-        <v>0.02511721619353941</v>
+        <v>0.02511721619353939</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02511721619353941</v>
+        <v>0.02511721619353939</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02715817720795774</v>
+        <v>0.02715817720795771</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04974173909782484</v>
+        <v>0.04974173909782482</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02514409109074372</v>
+        <v>0.0251440910907437</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03027917049139808</v>
+        <v>0.03027917049139806</v>
       </c>
       <c r="K7" t="n">
         <v>0.01205027846174435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04292859342558383</v>
+        <v>0.04292859342558385</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0101604987819739</v>
+        <v>0.01016049878197389</v>
       </c>
       <c r="C8" t="n">
-        <v>0.03014731432519321</v>
+        <v>0.03014731432519319</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02622260013773729</v>
+        <v>0.02622260013773724</v>
       </c>
       <c r="E8" t="n">
-        <v>0.02929439089938736</v>
+        <v>0.02929439089938735</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02712712024958102</v>
+        <v>0.02712712024958101</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03218639806794885</v>
+        <v>0.03218639806794883</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05476995995781742</v>
+        <v>0.05476995995781737</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03017231195073486</v>
+        <v>0.03017231195073478</v>
       </c>
       <c r="J8" t="n">
         <v>0.03530800620713622</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0138917829385088</v>
+        <v>0.01389178293850878</v>
       </c>
       <c r="L8" t="n">
-        <v>0.05122489964986859</v>
+        <v>0.05122489964986856</v>
       </c>
     </row>
     <row r="9">
@@ -7131,34 +7131,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01733909461012238</v>
+        <v>0.01733909461012235</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0375698735893169</v>
+        <v>0.03756987358931688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03297087099163494</v>
+        <v>0.03297087099163493</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04143224813813771</v>
+        <v>0.0414322481381377</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03756986931324136</v>
+        <v>0.03756986931324133</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0395834068953697</v>
+        <v>0.03958340689536969</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06216696878523677</v>
+        <v>0.06216696878523673</v>
       </c>
       <c r="I9" t="n">
-        <v>0.03756932077815566</v>
+        <v>0.03756932077815565</v>
       </c>
       <c r="J9" t="n">
-        <v>0.04270440017881003</v>
+        <v>0.04270440017881005</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0224575554647809</v>
+        <v>0.02245755546478089</v>
       </c>
       <c r="L9" t="n">
         <v>0.0553538231129958</v>
@@ -7247,28 +7247,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.05301326975747908</v>
+        <v>0.05301326975747907</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2157557545010365</v>
+        <v>0.2157557545010363</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05393087578375098</v>
+        <v>0.05393087578375094</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2238081268451043</v>
+        <v>0.2238081268451042</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1992217259032031</v>
+        <v>0.199221725903203</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05534107603415241</v>
+        <v>0.05534107603415238</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05463914985742797</v>
+        <v>0.0546391498574279</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05722298360905357</v>
+        <v>0.05722298360905356</v>
       </c>
       <c r="J2" t="n">
         <v>0.2454955377095543</v>
@@ -7277,7 +7277,7 @@
         <v>0.2063530534356225</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05372452169817193</v>
+        <v>0.05372452169817183</v>
       </c>
     </row>
     <row r="3">
@@ -7293,31 +7293,31 @@
         <v>0.3160459321913731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03098725659023818</v>
+        <v>0.03098725659023819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3293243874132882</v>
+        <v>0.3293243874132883</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2887400401770067</v>
+        <v>0.2887400401770065</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04103085386209997</v>
+        <v>0.04103085386210003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03620722178745651</v>
+        <v>0.03620722178745648</v>
       </c>
       <c r="I3" t="n">
-        <v>0.05434536082884318</v>
+        <v>0.05434536082884312</v>
       </c>
       <c r="J3" t="n">
         <v>0.3875394827678116</v>
       </c>
       <c r="K3" t="n">
-        <v>0.3011596094021307</v>
+        <v>0.3011596094021311</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02977783135562644</v>
+        <v>0.02977783135562645</v>
       </c>
     </row>
     <row r="4">
@@ -7330,31 +7330,31 @@
         <v>0.01021665349633758</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05870172398365033</v>
+        <v>0.05870172398365035</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02058143568270563</v>
+        <v>0.02058143568270561</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05877259162064892</v>
+        <v>0.05877259162064891</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05877259162064893</v>
+        <v>0.05877259162064891</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03661874961263004</v>
+        <v>0.03661874961263016</v>
       </c>
       <c r="H4" t="n">
-        <v>0.02883988653078306</v>
+        <v>0.02883988653078308</v>
       </c>
       <c r="I4" t="n">
-        <v>0.05849159202270334</v>
+        <v>0.05849159202270335</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1035301371492184</v>
+        <v>0.1035301371492183</v>
       </c>
       <c r="K4" t="n">
-        <v>0.05901489007670443</v>
+        <v>0.0590148900767045</v>
       </c>
       <c r="L4" t="n">
         <v>0.01860857662149739</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02889459399333132</v>
+        <v>0.02889459399333136</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8330623320760617</v>
+        <v>0.8330623320760606</v>
       </c>
       <c r="D5" t="n">
-        <v>0.205892379187046</v>
+        <v>0.2058923791870463</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8330623329699882</v>
+        <v>0.8330623329699869</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8330623329699882</v>
+        <v>0.8330623329699869</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4954628461380455</v>
+        <v>0.4954628461380463</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3757844753961886</v>
+        <v>0.3757844753961884</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8330672145018065</v>
+        <v>0.8330672145018053</v>
       </c>
       <c r="J5" t="n">
-        <v>1.802258012459798</v>
+        <v>1.802258012459799</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8791784770473576</v>
+        <v>0.8791784770473583</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08700271667166397</v>
+        <v>0.0870027166716649</v>
       </c>
     </row>
     <row r="6">
@@ -7407,7 +7407,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.911339594389985</v>
+        <v>1.911339594389986</v>
       </c>
       <c r="C6" t="n">
         <v>1.959976149928351</v>
@@ -7416,28 +7416,28 @@
         <v>1.920728266810403</v>
       </c>
       <c r="E6" t="n">
-        <v>1.230021442584131</v>
+        <v>1.230021442584132</v>
       </c>
       <c r="F6" t="n">
         <v>1.959545420792222</v>
       </c>
       <c r="G6" t="n">
-        <v>7.263248139689167</v>
+        <v>7.263248139689172</v>
       </c>
       <c r="H6" t="n">
-        <v>7.255971057199255</v>
+        <v>7.25597105719925</v>
       </c>
       <c r="I6" t="n">
-        <v>7.285120982099237</v>
+        <v>7.28512098209924</v>
       </c>
       <c r="J6" t="n">
-        <v>7.330551998460909</v>
+        <v>7.3305519984609</v>
       </c>
       <c r="K6" t="n">
-        <v>1.960503926005339</v>
+        <v>1.960503926005341</v>
       </c>
       <c r="L6" t="n">
-        <v>1.919384437935466</v>
+        <v>1.919384437935465</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01366899924403424</v>
+        <v>0.01366899924403429</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06193905534465555</v>
+        <v>0.06193905534465557</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02403362564250812</v>
+        <v>0.0240336256425082</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06194929162243148</v>
+        <v>0.06194929162243144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06194929162243148</v>
+        <v>0.06194929162243142</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04007109536032678</v>
+        <v>0.04007109536032682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03229223227847972</v>
+        <v>0.0322922322784798</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06194393777040009</v>
+        <v>0.06194393777040003</v>
       </c>
       <c r="J7" t="n">
         <v>0.106982482896915</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06246723582440113</v>
+        <v>0.06246723582440115</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02206092236919403</v>
+        <v>0.02206092236919412</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01639465380365124</v>
+        <v>0.0163946538036513</v>
       </c>
       <c r="C8" t="n">
-        <v>0.06942816651714658</v>
+        <v>0.06942816651714659</v>
       </c>
       <c r="D8" t="n">
-        <v>0.03249747520626882</v>
+        <v>0.03249747520626884</v>
       </c>
       <c r="E8" t="n">
-        <v>0.06812720957604136</v>
+        <v>0.06812720957604133</v>
       </c>
       <c r="F8" t="n">
-        <v>0.06482155858412267</v>
+        <v>0.06482155858412261</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04754931401216751</v>
+        <v>0.04754931401216757</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03977045093032138</v>
+        <v>0.03977045093032141</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0694221564222408</v>
+        <v>0.06942215642224078</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1144616355564139</v>
+        <v>0.114461635556414</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0651046090666535</v>
+        <v>0.06510460906665365</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03450359161147908</v>
+        <v>0.03450359161147922</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.03137307910714926</v>
+        <v>0.03137307910714932</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08585405873343001</v>
+        <v>0.08585405873343006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.04794879127909472</v>
+        <v>0.04794879127909477</v>
       </c>
       <c r="E9" t="n">
-        <v>0.09302134015297697</v>
+        <v>0.09302134015297708</v>
       </c>
       <c r="F9" t="n">
-        <v>0.08585406013154122</v>
+        <v>0.08585406013154125</v>
       </c>
       <c r="G9" t="n">
-        <v>0.06398609874910116</v>
+        <v>0.06398609874910126</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05620723566725417</v>
+        <v>0.05620723566725423</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08585894115917457</v>
+        <v>0.08585894115917443</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1308974862856894</v>
+        <v>0.1308974862856896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.08278360844724601</v>
+        <v>0.08278360844724612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04597592575796845</v>
+        <v>0.04597592575796854</v>
       </c>
     </row>
   </sheetData>
@@ -7649,31 +7649,31 @@
         <v>0.2122675794774466</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05265862120184776</v>
+        <v>0.05265862120184775</v>
       </c>
       <c r="E2" t="n">
         <v>0.2202349427398827</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1958792957424585</v>
+        <v>0.1958792957424587</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05401411918209518</v>
+        <v>0.05401411918209514</v>
       </c>
       <c r="H2" t="n">
-        <v>0.05961400636327682</v>
+        <v>0.05961400636327677</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05460589222229703</v>
+        <v>0.05460589222229701</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2407125946444678</v>
+        <v>0.2407125946444677</v>
       </c>
       <c r="K2" t="n">
         <v>0.201270145079449</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05384884160357541</v>
+        <v>0.05384884160357544</v>
       </c>
     </row>
     <row r="3">
@@ -7686,34 +7686,34 @@
         <v>0.02324110018655895</v>
       </c>
       <c r="C3" t="n">
-        <v>0.3037055195634447</v>
+        <v>0.303705519563445</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0296264676700113</v>
+        <v>0.02962646767001131</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3168392049711403</v>
+        <v>0.3168392049711404</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2766357597148767</v>
+        <v>0.276635759714877</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03926800248759481</v>
+        <v>0.03926800248759482</v>
       </c>
       <c r="H3" t="n">
-        <v>0.07887759456341151</v>
+        <v>0.07887759456341152</v>
       </c>
       <c r="I3" t="n">
-        <v>0.04343835094439895</v>
+        <v>0.04343835094439897</v>
       </c>
       <c r="J3" t="n">
-        <v>0.3676048915651662</v>
+        <v>0.3676048915651667</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2818147541055005</v>
+        <v>0.2818147541055002</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03829346230828452</v>
+        <v>0.03829346230828451</v>
       </c>
     </row>
     <row r="4">
@@ -7726,31 +7726,31 @@
         <v>0.007866892241961253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04068816477993917</v>
+        <v>0.0406881647799392</v>
       </c>
       <c r="D4" t="n">
-        <v>0.01804498615147924</v>
+        <v>0.01804498615147915</v>
       </c>
       <c r="E4" t="n">
         <v>0.04075312010758893</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04075312010758895</v>
+        <v>0.04075312010758896</v>
       </c>
       <c r="G4" t="n">
-        <v>0.03345552548445853</v>
+        <v>0.03345552548445852</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09604922696202425</v>
+        <v>0.09604922696202434</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04070441678960654</v>
+        <v>0.04070441678960658</v>
       </c>
       <c r="J4" t="n">
-        <v>0.07466881515360645</v>
+        <v>0.07466881515360653</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03232253899814325</v>
+        <v>0.03232253899814328</v>
       </c>
       <c r="L4" t="n">
         <v>0.03160647075508449</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01693417295862072</v>
+        <v>0.01693417295862071</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5184588693629142</v>
+        <v>0.5184588693629146</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1732815481163757</v>
+        <v>0.1732815481163751</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5184588729393523</v>
+        <v>0.5184588729393524</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5184588729393523</v>
+        <v>0.5184588729393524</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4272236753177514</v>
+        <v>0.4272236753177512</v>
       </c>
       <c r="H5" t="n">
-        <v>1.508593619718547</v>
+        <v>1.508593619718548</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5184604197136231</v>
+        <v>0.5184604197136237</v>
       </c>
       <c r="J5" t="n">
-        <v>1.204777063789709</v>
+        <v>1.20477706378971</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3962378584006142</v>
+        <v>0.3962378584006145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.469390933618443</v>
+        <v>0.4693909336184421</v>
       </c>
     </row>
     <row r="6">
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.740625487866245</v>
+        <v>6.740625487866247</v>
       </c>
       <c r="C6" t="n">
         <v>1.811284181727477</v>
@@ -7818,13 +7818,13 @@
         <v>1.811167382364495</v>
       </c>
       <c r="G6" t="n">
-        <v>6.766214121108742</v>
+        <v>6.766214121108738</v>
       </c>
       <c r="H6" t="n">
         <v>6.829635999693697</v>
       </c>
       <c r="I6" t="n">
-        <v>6.773463012413888</v>
+        <v>6.773463012413889</v>
       </c>
       <c r="J6" t="n">
         <v>1.935382348682194</v>
@@ -7833,7 +7833,7 @@
         <v>1.802660697151861</v>
       </c>
       <c r="L6" t="n">
-        <v>1.802017246644513</v>
+        <v>1.802017246644511</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01073731725831751</v>
+        <v>0.01073731725831748</v>
       </c>
       <c r="C7" t="n">
         <v>0.04357329145525349</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02091530085036372</v>
+        <v>0.02091530085036371</v>
       </c>
       <c r="E7" t="n">
         <v>0.04356399365913746</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04356399365913746</v>
+        <v>0.04356399365913748</v>
       </c>
       <c r="G7" t="n">
-        <v>0.03632595050081478</v>
+        <v>0.03632595050081473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0989196519783805</v>
+        <v>0.09891965197838043</v>
       </c>
       <c r="I7" t="n">
-        <v>0.04357484180596281</v>
+        <v>0.04357484180596282</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07753924016996276</v>
+        <v>0.07753924016996271</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03519296401449951</v>
+        <v>0.03519296401449947</v>
       </c>
       <c r="L7" t="n">
-        <v>0.03447689577144076</v>
+        <v>0.03447689577144073</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01313376426129067</v>
+        <v>0.01313376426129066</v>
       </c>
       <c r="C8" t="n">
-        <v>0.04998985766983517</v>
+        <v>0.04998985766983522</v>
       </c>
       <c r="D8" t="n">
-        <v>0.02817522215992187</v>
+        <v>0.02817522215992189</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0488890520280818</v>
+        <v>0.04888905202808182</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04609194397209316</v>
+        <v>0.04609194397209322</v>
       </c>
       <c r="G8" t="n">
         <v>0.04275050679177565</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1053442082693554</v>
+        <v>0.1053442082693555</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04999939809692364</v>
+        <v>0.0499993980969237</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08396458809423692</v>
+        <v>0.08396458809423689</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03751458681989293</v>
+        <v>0.03751458681989294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.04510914903354463</v>
+        <v>0.04510914903354465</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02375602343103944</v>
+        <v>0.02375602343103943</v>
       </c>
       <c r="C9" t="n">
         <v>0.06128289667255674</v>
       </c>
       <c r="D9" t="n">
-        <v>0.03862500593634208</v>
+        <v>0.0386250059363421</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06669606592550557</v>
+        <v>0.06669606592550555</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06128288191913855</v>
+        <v>0.06128288191913852</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05403555571811806</v>
+        <v>0.05403555571811802</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1166292571956838</v>
+        <v>0.1166292571956837</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06128444702326601</v>
+        <v>0.06128444702326603</v>
       </c>
       <c r="J9" t="n">
-        <v>0.09524884538726598</v>
+        <v>0.09524884538726602</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05018463950806779</v>
+        <v>0.05018463950806772</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05218650098874397</v>
+        <v>0.05218650098874394</v>
       </c>
     </row>
   </sheetData>
